--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -450,4004 +450,5067 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="58" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
-    <col width="38" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-  </cols>
+  <sheetPr/>
+  <dimension ref="A1:S51"/>
+  <sheetViews/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>story_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>feature_area</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>code_basis</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>expected_story</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>acceptance_criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>validation_method</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>production_equivalent_check</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>first_test_result</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>documented_errors</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>fix_status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>retest_result</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>android_device_result</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>iphone_device_result</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>US-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>URL保存</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>手動貼り付け保存</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>UrlRules.kt; URLRules.swift; DefaultUrlRepository.kt; URLRepository.swift; MainListViewModel.kt; URLSaverAppModel.swift</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ユーザーとして、URLを手動入力して保存し、一覧に戻ったとき保存済みリンクを確認できる。</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https URLはnormalizedUrlで保存され、metadata PENDINGになり、重複時は既存扱いになる。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Android unit: UrlRulesTest/RepositoryBehaviorTest/MainListViewModelTest; iOS: URLRulesTests/URLRepositoryTests; 実機: 入力欄から保存</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>release buildで同じ保存契約が残ること</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>US-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>共有保存</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>単一URL共有保存</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>AndroidManifest.xml; ShareReceiverActivity.kt; ShareReceiverEntrypointRouter.kt; ShareHandoffStore.swift; URLSaverAppModel.swift</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ユーザーとして、他アプリの共有からURLをURL Saverへ送り、保存結果を通知で理解できる。</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>ACTION_SEND/Share Extension相当から1件保存し、created/duplicate/invalid/no URLを明示する。</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Android unit: ShareReceiverActivityTest/EntrypointTest; iOS: URLRepositoryTests + handoff source確認; 実機: share intent/共有シート</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>debug/releaseで受信IDと正準アプリIDが一致すること</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>US-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>共有保存</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>複数URL共有保存</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>ShareReceiverActivity.kt; UrlRules.kt; URLRules.swift</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ユーザーとして、複数URLを共有したとき、可能な範囲で順次保存され件数サマリを確認できる。</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>最大50件、created/duplicate/restored/failedの集計が通知される。</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Android unit: ShareReceiverActivityTest; iOS: URLRulesTests extractAll; 実機: 非破壊範囲で複数テキスト共有</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>上限/切り詰め文言がreleaseでも残ること</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>US-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>URLルール</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>URL正規化と重複判定</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>UrlRules.kt; URLRules.swift; AppDatabase.kt; SQLiteDatabase.swift</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>ユーザーとして、同じURLの表記違いを重複として扱ってもらえる。</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>normalizedUrlが主キー、openUrl=normalizedUrl、表示用URLは別扱い。</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Android: UrlRulesTest/UrlNormalizationVectorTest/MigrationDedupTest; iOS: URLRulesTests</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>DB schemaのunique制約がreleaseにもあること</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>US-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>一覧</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Active一覧表示とフィルター</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>UrlSaverRoot.kt; MainListViewModel.kt; ListFilterState.kt; RootView.swift; URLSaverAppModel.swift</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ユーザーとして、保存済みURLを新しい順に見て、サービス/コレクションで絞り込める。</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>activeのみ表示、サービス選択とコレクション選択は競合しない。</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Android: MainListViewModelTest/ListFilterStateTest; iOS: ServiceFilterTests; 実機: ホーム表示</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>release buildで正準IDのホームが表示されること</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>US-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>一覧</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>カード表示モード切替</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>EntryCardDisplayMode.kt; EntryCard.kt; MainListViewModel.kt; ArchiveViewModel.kt</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ユーザーとして、リンクカードの情報量を切り替えて再発見しやすくできる。</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>表示モードが保存され、Main/Archiveで反映される。</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Android: MainListViewModelTest/ArchiveViewModelTest/EntryCardMetadataTextTest; iOS: 該当UI source確認</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>release buildで設定保存が有効</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>US-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>一覧操作</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>スワイプでアーカイブ</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>DefaultUrlRepository.kt; URLRepository.swift; SwipeThresholds.kt; RootView.swift</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ユーザーとして、Activeカードをスワイプしてアーカイブし、Undoできる。</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>ACTIVE -&gt; ARCHIVED、UndoでACTIVE復帰、iOSは横スワイプ意図判定あり。</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Android: RepositoryBehaviorTest/MainListViewModelTest/Phase1aFlowTest; iOS: URLRepositoryTests/ServiceFilterTests; 実機: 主要カードで操作</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>release buildでDB状態遷移一致</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>US-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>一覧操作</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>削除猶予とUndo</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>DefaultUrlRepository.kt; URLRepository.swift; MainActivityViewModelSnackbarUndoTest.swift?; URLSaverAppModel.swift</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ユーザーとして、誤削除しても猶予中に元に戻せる。</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>ACTIVE -&gt; PENDING_DELETE、猶予後削除、UndoでACTIVE復帰。共有参照があるiOS行はローカル由来だけ落とす。</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Android: RepositoryBehaviorTest/MainActivityViewModelSnackbarUndoTest; iOS: URLRepositoryTests; 実機: 非破壊の一時テストデータのみ</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>release buildで猶予ロジック一致</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>通常端末の既存データは消さない</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>US-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>詳細画面と外部で開く</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>DetailViewModel.kt; DetailView.kt; ExternalActions.kt; URLRepository.swift</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ユーザーとして、一覧カードタップで詳細へ進み、必要なときだけ外部ブラウザで開ける。</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>カードタップは直接外部起動せず、詳細のopenUrlがnormalizedUrl。</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Android: ExternalActionsTest/Phase1aFlowTest; iOS: manual/device確認</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>release buildでIntent/URL open動作保持</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>US-010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>タイトル編集とUndo</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>DetailViewModel.kt; DefaultUrlRepository.kt; URLSaverAppModel.swift; URLRepository.swift</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ユーザーとして、タイトルを自分用に編集し、直後なら元に戻せる。</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>空白はnull、最大120文字、Undo通知は対象詳細に紐づく。</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Android: MainActivityViewModelSnackbarUndoTest/RepositoryBehaviorTest; iOS: URLRepositoryTests</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>release buildで入力制約一致</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>US-011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>メモ編集</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>DetailViewModel.kt; DefaultUrlRepository.kt; URLRepository.swift</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ユーザーとして、保存URLにメモを付けられる。</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>空白のみは空文字、最大2000文字、updatedAt更新。</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Android: RepositoryBehaviorTest; iOS: URLRepositoryTests</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>release buildで制約一致</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>US-012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>メタデータ</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>metadata取得と状態表示</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>FetchMetadataWorker.kt; MetadataFetcher.kt; MetadataCoordinator.swift; MetadataStatusTextTests.swift; MetadataUiText.kt</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ユーザーとして、保存URLのタイトル/本文/サムネイルが取得され、失敗時も理由を理解できる。</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>READY/PENDING/FAILED/UNAVAILABLEをUI文言へ分離し、部分成功をREADY扱いする。</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Android: FetchMetadataWorkerTest/MetadataFetcherTest/MetadataUiTextTest; iOS: MetadataFetcherTests/MetadataStatusTextTests</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>release buildでAPIキー未設定でもgraceful fallback</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>US-013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>メタデータ</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>metadata再取得/リトライ</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>DefaultUrlRepository.kt; DetailViewModel.kt; URLRepository.swift; URLSaverAppModel.swift</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ユーザーとして、失敗/不足したmetadataを手動で再取得できる。</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>FAILED/UNAVAILABLE/不足READYで再enqueueし、metadata更新だけではupdatedAtを変えない。</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Android: FetchMetadataWorkerTest/RepositoryBehaviorTest; iOS: URLRepositoryTests</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>release buildでWorkManager/BGTask登録可能</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>US-014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>タグ</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>ローカルタグ作成/割当/削除</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>TagRepository.kt; DefaultTagRepository.kt; DetailViewModel.kt; URLRepository.swift; SharedTagManagementSheets.swift</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ユーザーとして、リンクにローカルタグを付け、タグ別に見返せる。</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>タグ名検証、重複処理、URL件数表示、削除時関連付け解除。</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Android: TagRepositoryTest/TagDaoTest/DetailTagUiStateTest; iOS: SharedTagStoreTests/URLRepositoryTests; 実機: タグ画面表示</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>release buildでDB migration後も保持</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>US-015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>タグ</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>タグ詳細とURL一覧</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>TagDetailScreen.kt; TagDetailViewModel.kt; SharedTagCloudSheet.swift</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ユーザーとして、タグを開いて含まれるURLだけを確認できる。</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>タグ別URL一覧、戻る、詳細遷移、ローカル/共有タグの区別。</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Android: TagRepositoryTest + 実機; iOS: SharedTagStoreTests + 実機</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>release buildで正準ID画面を確認</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>US-016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>共有タグ</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>ローカルタグをクラウド共有タグへ移行</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>DefaultTagRepository.kt; SharedTagSyncCoordinator.kt; SharedTagCloud.swift</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ユーザーとして、必要なタグだけクラウド共有へ移行できる。</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>未設定時は無効、サインイン済み/設定済みでremote tag作成と同期操作を記録。</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Android: SharedTagSyncRepositoryTest; iOS: SharedTagCloudLiveSyncTests(環境依存)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>本番Supabase設定時のみ有効、未設定releaseでは非表示/無効</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>外部Supabaseは資格情報なしでは未検証</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>US-017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>共有タグ</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>招待リンク作成/参加</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>ShareReceiverEntrypointRouter.kt; SharedTagInviteViewModel.kt; PendingInviteStore.swift; URLSaverAppModel.swift</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>ユーザーとして、招待リンクから共有タグ/グループに参加できる。</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>urlsaver://invite と https://miyamibu.xyz/invite を解釈し、invalid時は明示する。</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Android: MainActivityViewModelSecondaryIntentTest/ShareReceiverActivityEntrypointTest; iOS: PendingInviteStoreTests/URLSaverAppModel source + live tests</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>app links/deep linksがrelease manifest/plistに残ること</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>US-018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>共有タグ</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>共有タグ同期</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SharedTagSyncWorker.kt; SharedTagSyncCoordinator.kt; SharedTagSyncExecutor.swift; SharedTagCloud.swift</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ユーザーとして、共有タグのURL変更がクラウドと同期される。</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>起動/変更時に同期、失敗時は状態表示、リアルタイムpushは必須でない。</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Android: SharedTagSyncRepositoryTest; iOS: SharedTagSyncExecutorTests; Supabase SQL validation</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>本番相当はproduction Supabase値が必要</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>US-019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>グループ</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>共有タググループ作成/編集</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>DefaultTagRepository.kt; SharedTagCloudScreens.kt; SharedTagManagementSheets.swift; SharedTagCloud.swift</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ユーザーとして、共有タグをグループで整理し、メンバーと共有できる。</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>グループ作成、タグ追加/削除、招待、名前変更、削除、権限変更/移譲の結果文言。</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Android: TagRepositoryTest/SharedTagSyncRepositoryTest + 実機; iOS: SharedTagCloudLiveSyncTests + 実機</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>本番Supabase RPCが適用済みであること</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>US-020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>サインイン/サインアップ/サインアウト</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SharedTagAuthViewModel.kt; SharedTagAuthRemoteDataSource.kt; SharedTagCloudSheet.swift</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ユーザーとして、共有機能のためにメール/パスワードまたはGoogleでサインインできる。</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>未設定時は説明、OAuth callbackを処理、サインアウトで状態更新。</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Android: SharedTagAuthViewModelTest; iOS: source/live env確認; 実機: 画面表示と非秘密操作</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>本番URL/key/OAuth設定が必要</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>秘密値入力はユーザー操作のみ</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>US-021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>プロフィール名/画像/テーマ</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SharedTagCloudScreens.kt; UserProfileStore.kt; RootView.swift; UserProfileStore.swift</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ユーザーとして、プロフィール名・画像・テーマを設定できる。</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>ローカル保存し、共有プロフィールへ反映可能な場合は同期する。</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Android: UserProfileStore source/実機; iOS: UserProfileStoreTests; 実機: 画面表示</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>release buildで保存先が正しいこと</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>US-022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>アカウント</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>アカウント削除/問い合わせ</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>SharedTagCloudScreens.kt; SharedTagAuthRemoteDataSource.kt; account-deletion docs; SharedTagCloud.swift</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>ユーザーとして、アカウント削除や問い合わせ導線を使える。</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>削除は確認ダイアログ経由、問い合わせはメール作成、外部削除URL/文書と整合。</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Android/iOS source + 実機画面確認; Supabase RPC validation</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>本番削除URL/設定が必要</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>破壊的な実削除は承認なしに実行しない</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>US-023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>優待/プラン</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>優待コード適用</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>EntitlementGrantRepository.kt; SharedTagCloudScreens.kt; URLSaverAppModel.swift; SharedTagCloud.swift</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>ユーザーとして、受け取った優待コードを入力してPro権限を受け取れる。</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>空/未サインイン/失敗/成功を明示し、使用状況に反映する。</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Android: EntitlementResolverTest/SharedTagAuthViewModelTest; iOS: URLRulesTests entitlement tests</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>本番Supabase RPC/migration適用が必要</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>US-024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>プラン制限</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>保存数/タグ数/共有制限</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>PlanModels.kt; Models.swift; EntitlementResolver.kt</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>ユーザーとして、上限に達したとき理由を理解できる。</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>LaunchStandard/Free/Pro/PromoProの制限が保存/タグ/共有URLで適用される。</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Android: EntitlementResolverTest/RepositoryBehaviorTest/TagRepositoryTest; iOS: URLRulesTests</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>release buildでdebug overrideに依存しない</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>US-025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>エクスポート</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>AI-friendly ZIP/JSONエクスポート</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>ExportRepository.kt; ExportScreen.kt; ExportArchiveBuilder.swift; ExportSheet.swift</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>ユーザーとして、保存URLをAI/Codexで読みやすいZIP/JSONとして出力できる。</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>manifest、entries.jsonl、entries/*.md またはJSONを生成し、範囲/タグ/状態/サービス/メモ/日付フィルタ対応。</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Android: ExportRepositoryTest/ExportScreenTest; iOS: ExportArchiveBuilderTests/ServiceFilterTests; 実機: 画面表示</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>release buildでFileProvider/share sheetが機能</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>US-026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>使い方</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>使い方リストと初回オンボーディング分離</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>UrlSaverRoot.kt; RootView.swift; AGENTS.md; artifacts/ui-review/2026-06-25</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>ユーザーとして、ブック/使い方ボタンからイラスト付き使い方リストを開ける。</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>初回spotlightとは別画面、下部バー非表示、戻るでホーム、既存デザインサイズは維持。</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>実機: Android/iPhoneのブックボタン確認; source inspection</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>release buildでも同一導線</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>大きさデザイン変更は禁止</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>US-027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>ユーザー</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>下部ナビ</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>ホーム下部5アクション</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>UrlSaverRoot.kt; RootView.swift; artifacts/ui-review/2026-06-25</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>ユーザーとして、ホーム下部に グループ/エクスポート/＋/タグ/アーカイブ を常に見られる。</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>5アクション表示、iOS中央＋は突出、使い方画面では非表示。</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>実機: Android/iPhoneホーム画面確認</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>release buildで正準IDを確認</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>サイズ変更は禁止。必要時は不具合記録のみ</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>US-028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>本番同等local-only releaseビルド</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>app/build.gradle.kts; ios/README.md; APP_STORE_REVIEW.md</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>従業員として、契約前/本番同等のローカル専用ビルドが安全に作れる。</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Android releaseは広告無効、cloud未設定なら無効。iOS Release generic buildで署名なしcompile可能。</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>./gradlew assembleRelease; xcodebuild Release CODE_SIGNING_ALLOWED=NO</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>本番値なしでcloudを公開しない</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>US-029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>正準アプリID運用</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>app/build.gradle.kts; ios project.pbxproj; AGENTS.md</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>従業員として、実機確認時に古い開発IDではなく正準アプリを操作できる。</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Android jp.miyamibu.urlalbum、iOS com.mibu.codebridge.iosを確認してから証跡化する。</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>adb package確認; xcodebuild settings/devicectl/Appium capability確認</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>ストア/実機で正準ID一致</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>PARTIAL(iPhone physical 00008101-00066D96340A001E): com.mibu.codebridge.ios インストールとdevicectl launch成功。Appium/WDA UI取得はRemoteXPC tunnel未起動/port 8100 refusedで失敗。NOT VERIFIED on physical iPhone for UI operations.</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>US-030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Android/iOS</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>非破壊の実機検証</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>AGENTS.md; iphone-real-device-verification skill; scripts/install_on_device.sh</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>従業員として、ユーザー端末データを消さずに主要導線を確認できる。</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>connectedDebugAndroidTest/pm clear/uninstallは承認なし禁止。iPhoneはAppium/WDA優先。</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>adb devices; Appium status; screenshots/source capture</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>実機操作範囲を証跡に明記</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>PARTIAL(iPhone physical 00008101-00066D96340A001E): com.mibu.codebridge.ios インストールとdevicectl launch成功。Appium/WDA UI取得はRemoteXPC tunnel未起動/port 8100 refusedで失敗。NOT VERIFIED on physical iPhone for UI operations.</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>AS-001</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Web/Supabase</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>管理画面</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>管理者ログイン</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>web/admin/app/page.tsx; web/admin/lib/auth.ts</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>管理者として、Supabase Authの管理者アカウントで優待管理画面に入れる。</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>未ログイン時はログインフォーム、非管理者/APIエラーは拒否。</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>web/admin npm run typecheck/build; API source inspection</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>本番環境変数とservice keyが必要</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr">
+      <c r="P32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>秘密値は扱わない</t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>AS-002</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Web/Supabase</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>優待コード</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>優待コード一覧</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>web/admin/app/api/admin/promo-codes/route.ts; supabase/migrations/*promo*</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>管理者として、発行済み優待コードを状態付きで一覧できる。</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>最新100件、sent/delivered/redeemed/revoked/expired等のstatus_labelを返す。</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Next build/typecheck; Supabase migration/RPC inspection</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>本番DBマイグレーション適用が必要</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="P33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>AS-003</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Web/Supabase</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>優待コード</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>優待コード送信</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>web/admin/app/api/admin/promo-codes/send/route.ts; lib/promo.ts; Resend webhook route</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>管理者として、対象メールに優待コードを送信し、結果を一度だけ確認できる。</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>targetEmail/note/expiresInDaysを受け、コードとredeemLinkを返す。送信状態を記録。</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Next build/typecheck; API source; Resend webhook route check</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Resend/Supabase本番設定が必要</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr">
+      <c r="P34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>実送信は承認なしにしない</t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>AS-004</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Web/Supabase</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>優待コード</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>優待コード取消</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>web/admin/app/api/admin/promo-codes/[id]/revoke/route.ts</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>管理者として、誤発行した優待コードを取消できる。</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>確認後POST、revoked_reasonを保存し一覧に反映。</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Next build/typecheck; API source</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>本番DB/RLS/RPCが必要</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="P35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>AS-005</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Web/Supabase</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>ユーザー検索</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>web/admin/app/api/admin/users/route.ts; page.tsx</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>管理者として、メール断片から対象ユーザーを検索し、優待送信先を選べる。</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2文字未満は検索しない。APIは管理者認証必須。</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Next build/typecheck; API source</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>本番Auth管理API権限が必要</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="P36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>AS-006</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>配信監査</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Resend webhookで配信状態追跡</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>web/admin/app/api/webhooks/resend/route.ts; 20260627020000_resend_webhook_delivery_events.sql</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>管理者として、送信後のdelivered/bounced等を優待コードに反映できる。</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>署名検証後、delivery_event_type/at/errorを更新する。</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Next build/typecheck; migration SQL validation</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>本番Webhook secret/Resendが必要</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。 / PASS: web/admin npm run typecheck と npm run build 成功。</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="P37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ES-001</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Android/iOS/Supabase</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>品質管理</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>単一正準ストーリー台帳維持</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>docs/qa/rinbam_canonical_story_status.xlsx; docs/qa/rinbam_canonical_story_status.csv</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>従業員として、機能ごとの期待動作、テスト結果、未検証項目を一つの台帳で追跡できる。</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>この台帳を正本にし、テスト/修正/再テスト結果を同じ行に更新する。</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>ファイル存在確認、行数確認、Excel/CSV生成確認</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>本番同等結果欄を分離</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>PASS: 正準スプレッドシート/CSV作成済み</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。 / PASS: xlsx/csvを生成。</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>PASS: 既存45件に今回追加5件を追記し、CSV/XLSXを同一内容で更新。共有保存タグ選択、コレクション、ChatGPT連携、問い合わせ監査、公開Web/リンクを追加。</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。 Supabase local lint: ローカルPostgres 127.0.0.1:55422 が接続拒否。</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>PASS: CSV/XLSX更新後に行数/ID/XLSX dimension確認予定。</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q38" s="3" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>US-034/US-035/US-036/AS-008/ES-006を追加。</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>ES-002</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Android</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>品質管理</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Androidローカル検証</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>README.md; build.gradle.kts; app/src/test</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>従業員として、Androidのビルド/単体/lintで退行を検出できる。</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>assembleDebug/testDebugUnitTest/lintDebugが実行され、失敗は台帳に記録。</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>./gradlew assembleDebug testDebugUnitTest lintDebug</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>assembleReleaseも別行で確認</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>PASS: Androidローカル検証成功、実機代表導線成功</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PASS: Androidローカル検証成功、release buildも成功、実機共有系は未検証</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PASS: 2026-06-29 ./gradlew assembleDebug testDebugUnitTest lintDebug 成功。PASS: ./gradlew assembleRelease 成功。対象追加確認として SharedTagAuthViewModelTest/TagRepositoryTest 単独実行も成功。</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Release manifestで広告/AD_ID削除指定の対象なしwarning、MenuBook deprecated warningあり。どちらもbuild失敗ではない。物理共有/購入操作は未検証。</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>PASS local retest。connectedDebugAndroidTestは実機データ保護のため未実施。</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr">
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>connectedDebugAndroidTestは承認なし実行しない</t>
         </is>
       </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:39:51 +0900</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>ES-003</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>iOS</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>品質管理</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>iOSローカル検証</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>ios/README.md; ios/URLSaveriOSTests</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>従業員として、iOSのbuild/test/release compileで退行を検出できる。</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>xcodebuild build/test/Release compileを実行し結果を記録。</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>xcodebuild -scheme URLSaveriOS build/test; Release generic build</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>署名なしRelease compile</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL: iOS compile成功、XCTest実行は環境ブロック</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS_WITH_LIVE_SUPABASE_ENV_GAP</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>PASS: 2026-06-29 iOS generic Simulator build成功、URLRepositoryTests単独成功、PendingInviteStoreTests単独成功。PARTIAL: 全体XCTestはSharedTagCloudLiveSyncTests 3件がInvalid API keyで失敗。</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>iOS全体XCTest: live Supabase shared-tag tests が Invalid API key で失敗。ローカル対象テストは成功。物理iPhone UI操作は未検証。</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>PASS local targeted retest。live Supabaseキー/環境が整ったら全体再実行。</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:36:46 +0900</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>ES-004</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>品質管理</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Web管理画面検証</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>web/admin/package.json; web/admin/app; web/admin/lib</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>従業員として、管理画面の型/ビルドを確認できる。</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>npm run typecheck と npm run build を実行し結果記録。</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>cd web/admin &amp;&amp; npm run typecheck &amp;&amp; npm run build</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>本番env未設定時の挙動を分離</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>PASS: Web管理画面 typecheck/build 成功</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>PASS: web/admin npm run typecheck と npm run build 成功。</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PASS: 2026-06-29 web/admin npm run typecheck と npm run build 成功。Next.js buildで管理API route生成まで確認。</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>修正なし: typecheck/buildエラー未検出。</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>PASS local retest。本番env/API実動作は未検証。</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:39:51 +0900</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ES-005</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>品質管理</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>SQL/RPC検証</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>supabase/migrations; supabase/tests</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>従業員として、共有タグ/優待コードのDB契約を検証できる。</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>migrationとvalidation SQLの構文/対象を確認し、linked/localは資格情報の有無を明記。</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>supabase tests inspection; psql/supabase CLI可能なら実行</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>本番DBは承認と秘密値が必要</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED_LOCAL: ローカルDB未起動、linked DB未接続</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>Supabase local lint: ローカルPostgres 127.0.0.1:55422 が接続拒否。</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS_WITH_LOCAL_DB_GAP</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>PASS: 2026-06-29 deno check supabase/functions/verify-store-purchase/index.ts 成功。BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 connection refused。</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Supabase local DB/RLS live validationは未実施。ローカルPostgres 127.0.0.1:55422 が接続拒否。linked/prod DBは秘密値と明示承認なしで未接続。</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr"/>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>PASS Edge Function type check。DB lint/RLS/migration live testはローカルDB起動またはlinked DB承認後に再実行。</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:39:51 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>US-031</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>タグ共有</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ローカルタグ共有リンク/JSON export/import</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TagDetailScreen.kt; TagDetailViewModel.kt; ShareReceiverActivity.kt; ShareReceiverEntrypointRouter.kt; URLRepository.swift; RootView.swift; ShareViewController.swift; Models.swift</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ユーザーとして、ローカルタグを他端末や共有先へ渡し、受け取った側でタグ名・URL・タイトル・メモを可能な範囲で復元できる。</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Androidはタグ詳細から同端末リンクとJSONタグデータを共有できる。iOSはタグJSONをexport/importでき、Share Extensionで受け取ったタグJSONを取り込める。既存URLは上書きせず、作成/統合/重複/失敗件数を返す。</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Android: assembleDebug/testDebugUnitTest/lintDebug; iOS: URLRepositoryTests testLocalTagPayloadExportImportTracksCreatedMergedAndSkipped; iOS generic build; source inspection</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>正準アプリIDで共有入口が残り、Share Extension/Intent経由でも同じimport契約を使うこと</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug 成功。PASS: iOS URLRepositoryTests単独成功、generic iOS Simulator build成功。</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>物理Android共有シート操作と物理iPhone Share Extension操作は未検証。iOS全体XCTestはlive Supabase 3件がInvalid API keyで失敗したが、このストーリー対象外。</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>実装済み: Androidタグ詳細のリンク/JSON共有、iOSタグJSON export/import、Share Extension importを追加。</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PASS local retest。実機共有操作は未実施。</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>未実機操作: 共有シートからのタグJSON受け渡しは未検証。</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: Share Extension操作は未検証。</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>実装コミット 7a2aba31。旧タグ共有復元の独立ストーリーとして追加。</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:36:46 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>US-032</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>共有タグ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>未ログイン招待の保留/サインイン後再開</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PendingInviteStore.kt; SharedTagInviteViewModel.kt; SharedTagAuthViewModel.kt; SharedTagCloudScreens.kt; UrlSaverRoot.kt; PendingInviteStore.swift; URLSaverAppModel.swift; SharedTagCloudSheet.swift</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ユーザーとして、共有タグ招待を未ログインで開いても招待を失わず、サインイン後に参加を再開できる。</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>招待tokenを端末内に保存し、無効招待または参加成功で消す。プロフィール/クラウド画面で保留招待を表示し、サインイン後に参加または削除できる。</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Android: SharedTagAuthViewModelTest/TagRepositoryTest + assembleDebug/testDebugUnitTest/lintDebug; iOS: PendingInviteStoreTests; source inspection</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>OAuth/メールサインイン後も同じpending invite storeを参照し、招待tokenをログやUIへ露出しないこと</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>PASS: Android SharedTagAuthViewModelTest/TagRepositoryTest対象実行成功。PASS: iOS PendingInviteStoreTests単独成功。Android全体build/test/lint成功。</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>OAuth実ブラウザ往復、Supabase live invite accept、物理iPhone Appium操作は未検証。</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>実装済み: AndroidにもPendingInviteStoreと再開カードを追加。iOSの既存pending invite再開と合わせた。</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>PASS local retest。live invite再開は外部Auth/Supabase環境待ち。</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>未実機操作: 実OAuth/招待リンク受け取りは未検証。</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI操作未検証。</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>実装コミット 7a2aba31。US-017の招待参加から保留再開を分離して追跡。</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:36:46 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>US-033</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Android/iOS/Supabase</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>課金/プラン</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Standard/Proストア購入検証</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GooglePlayBillingService.kt; StoreKitPurchaseService.swift; StorePurchaseRemoteDataSource.kt; verify-store-purchase/index.ts; 20260628150316_restore_store_purchase_verification.sql; EntitlementResolver.kt; Models.swift</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ユーザーとして、Google Play BillingまたはStoreKitでStandard/Proを購入し、検証後に該当プランの権限を受け取れる。</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>クライアントは購入token/JWSをEdge Functionへ送り、Functionがストア検証後にuser_entitlement_grantsへstore_subscription grantを作る。raw tokenはDBに保存せずhashのみ保存する。</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Android: assembleDebug/testDebugUnitTest/lintDebug; iOS: generic build; Supabase: deno check verify-store-purchase; SQL/source inspection</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Google Play package name、App Store bundle ID、service account、Supabase service role envが本番/ストアsandboxで正しく設定されること</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_EXTERNAL_STORE_GAP</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>PASS: Android build/test/lint/release build成功。PASS: iOS generic build成功。PASS: deno check supabase/functions/verify-store-purchase/index.ts 成功。</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Google Play sandbox purchase、StoreKit sandbox purchase、Edge Function deploy、migration適用、RTDN/App Store Server Notificationsは未検証。Supabase local db lintはローカルDB未起動で失敗。</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>実装済み: Store purchase verification table/migrationとEdge Functionを追加し、client purchase serviceから呼ぶ契約を整備。</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>PASS local/type/build retest。外部ストアsandboxとSupabase deployは未実施。</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>未実機操作: Google Play Billing実購入フロー未検証。</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: StoreKit sandbox購入フロー未検証。</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>実装コミット 7a2aba31。ストア側product/価格/審査設定は外部ゲート。</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:39:51 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AS-007</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Supabase</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>課金監査</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ストア購入検証履歴/entitlement grant監査</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>store_purchase_verifications table; user_entitlement_grants; verify-store-purchase/index.ts; entitlement-foundation.md</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>管理者として、ストア購入検証が成功/失敗した履歴とgrantの紐づきを監査できる。</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>store_purchase_verificationsにplatform/product/transaction/hash/status/failure_reason/grant_id/expires_atを保存し、user_entitlement_grantsにはstore_subscription grantを重複transactionなしで作る。</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Supabase migration/source inspection; deno check Edge Function; future: deployed DB RLS/RPC verification</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>本番DB migration適用、service_roleのみのwrite、authenticated本人select、ストア通知による失効更新方針の追加が必要</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_DEPLOY_GAP</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>PASS: deno check Edge Function成功。SQL migrationはsource確認済み。BLOCKED_LOCAL: supabase db lint --local はローカルDB接続拒否。</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>本番/linked DB migration適用、RLS live verification、失効webhookは未検証。ローカルDB未起動でSupabase lint不可。</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>実装済み: 検証履歴table、RLS、transaction unique index、grant作成処理を追加。</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>PASS local type/source retest。DB live validationは未実施。</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>実装コミット 7a2aba31。AS系に課金監査ストーリーを追加。</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:39:51 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>US-034</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>共有保存</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>共有保存時のタグ選択/作成</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ShareReceiverActivity.kt; ShareViewController.swift; URLRepository.swift; DefaultUrlRepository.kt; ShareReceiverActivityEntrypointTest.kt</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ユーザーとして、他アプリからURLを保存するとき、保存前に既存タグを選ぶか新しいタグを作成して、そのタグ付きで保存できる。</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Android共有受信画面とiOS Share Extensionが保存先タグ一覧、複数選択、新規タグ作成、保存/キャンセルを提供する。保存後は選択タグにURLが紐づき、タグJSON importは通常URL保存とは別に処理される。</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Android: ShareReceiverActivityEntrypointTest; RepositoryBehaviorTest; full assemble/test/lint. iOS: ShareViewController source inspection; URLRepositoryTests; Share Extension build included in generic build.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>正準IDのShare target/Share Extensionで同等UIが表示されること。物理共有シートで保存前タグ選択が見えること。</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>PASS: ShareReceiverActivityEntrypointTest/RepositoryBehaviorTest対象実行成功。PASS: iOS generic buildとURLRepositoryTests成功。Source inspectionでiOS Share Extension tag picker/create/save確認。</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>物理Android共有シート操作、物理iPhone Share Extension操作は未検証。</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>修正なし: コード上はAndroid/iOSとも保存前タグ選択/作成UIあり。</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>PASS local/source retest。実機共有シートは未実施。</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>未実機操作: Android share sheetからタグ選択/作成は未検証。</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: Share Extensionタグ選択/作成は未検証。</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Androidで消えていたと報告された旧実装UIの追跡行。iOSにも対応UIあり。</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>US-035</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>コレクション</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>受信箱/自作コレクション作成・移動・並び替え</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CollectionDao.kt; CollectionModels.kt; DefaultUrlRepositoryCollectionsSupport.kt; CollectionFilterRow.kt; MainListViewModel.kt; RepositoryBehaviorTest.kt; TopFilterOrderResolutionTest.kt</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ユーザーとして、保存URLを受信箱以外の自作コレクションへ整理し、一覧上部のコレクションを並べ替えて絞り込める。</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>デフォルト受信箱を保持し、自作コレクション作成/重複検出/削除時の受信箱戻し/同名ローカルタグ連携/並び替え/フィルタが動く。</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>RepositoryBehaviorTest; MainListViewModelTest; ListFilterStateTest; TopFilterOrderResolutionTest; assembleDebug/testDebugUnitTest/lintDebug</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Room migration後もcollectionsとurl_entries.collectionIdが保持され、削除時にURL本体は削除されないこと。</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ANDROID_LOCAL_PASS_WITH_IOS_MODEL_DIFFERENCE</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PASS: RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。Android全体build/test/lint成功。</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>iOSは同名のcollectionモデルではなくlocal tag中心の整理UI。Android固有機能として記録。物理Androidで並び替え/削除は未検証。</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>修正なし: ローカルテスト上のエラー未検出。</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>PASS local retest。実機UI操作は未実施。</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>未実機操作: コレクション作成/並び替え/削除は未検証。</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>iOS parityはlocal tag管理で別途US-014/US-031/US-034に追跡。</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>US-036</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Android/iOS/Supabase</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AI連携</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ChatGPT personal link sync</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ChatGptPersonalLinkSync.kt; SharedTagAuthViewModel.kt; SharedTagCloudScreens.kt; SharedTagCloud.swift; SharedTagCloudSheet.swift; URLSaverAppModel.swift</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ユーザーとして、サインイン後に保存中/アーカイブ済みリンクをChatGPT提案対象として同期し、本文取得の送信有無も選べる。</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>サインイン必須。enabled/contentFetchEnabledをSupabase RPCへ保存し、有効化時にactive+archivedの個人リンクをupsert_link opsとして同期する。本文送信はcontentFetchEnabled=trueのときだけ行う。</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Android: SharedTagAuthViewModelTest/build source inspection. iOS: source inspection/generic build. Supabase: RPC/migration source inspection; local DB live validation pending.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>本番Supabase RPC set_personal_link_chatgpt_sync/apply_personal_link_opsが適用済みで、ユーザー権限と本文送信設定が一致すること。</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_LIVE_GAP</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>PASS: Android/iOS build系成功。Source inspectionでAndroid/iOSのUI toggle、AuthRequired、ops生成、content_fetch_allowed確認。</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Supabase live RPC実行、ChatGPT側実消費、物理端末toggle操作は未検証。</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>修正なし: ローカルビルド/ソース上の明確なエラー未検出。</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>再テスト未実施: live Supabase環境が必要。</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>未実機操作: ChatGPT連携toggle未検証。</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: ChatGPT連携toggle未検証。</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>本文送信のprivacy影響あり。store/privacy文言と継続照合が必要。</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AS-008</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Supabase</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>問い合わせ監査</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>問い合わせ送信/Resend配信追跡</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>supabase/functions/contact-support/index.ts; supabase/functions/contact-support-resend-webhook/index.ts; ContactSupportClient.kt; SharedTagCloudScreens.kt; SharedTagCloudSheet.swift</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>管理者として、アプリ内問い合わせの送信、rate limit、Resend message id、配信イベントを追跡できる。</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>contact-support Functionが問い合わせを保存してResend送信し、webhookが署名検証後にdelivered/bounced等を反映する。クライアントは成功/失敗をUIへ返す。</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Android: ContactSupportClientTest. Supabase: deno check contact-support/contact-support-resend-webhook. Future: live Resend webhook event verification.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>CONTACT_TO_EMAIL/CONTACT_FROM_EMAIL/RESEND_API_KEY/RESEND_WEBHOOK_SECRETが本番設定され、rate limitと配信イベントが実DBに残ること。</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>PASS: ContactSupportClientTest成功。PASS: deno check contact-support と contact-support-resend-webhook 成功。Web admin buildも成功。</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Resend live送信/配信/バウンスwebhook、Supabase DB live row確認は未検証。</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>修正なし: ローカル型/単体テスト上のエラー未検出。</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>PASS local/type retest。live deliveryは未実施。</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>US-022のユーザー問い合わせ導線に対応する管理/配信監査行。</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ES-006</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Web/Store</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>公開Web/リンク</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Privacy・Account deletion・App Links/Universal Links公開運用</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>web/invite-link/privacy/index.html; web/invite-link/account-deletion/index.html; web/invite-link/.well-known/assetlinks.json; web/invite-link/.well-known/apple-app-site-association; docs/release/final-submission-checklist.md</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>従業員として、ストア提出に必要なprivacy policy、account deletion URL、Android App Links、iOS Universal Linksの公開状態を追跡できる。</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>公開HTTPSでprivacy/account-deletionが200、assetlinks/AASAがJSONとして取得でき、package/bundle/team/fingerprintが提出対象と一致する。</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>docs/release/final-submission-checklist.md evidence; future: curl live URLs and JSON parse; store console values確認</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Play App Signing SHA-256、Apple Team ID、bundle/package ID、公開ドメインmiyamibu.xyzが最終提出値と一致すること。</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>DOCUMENTED_PASS_WITH_FINAL_SHA_GAP</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>PASS(documented): final-submission-checklistに2026-06-27 live URL 200/JSON parse証跡あり。Current turnではlive curl未再実行。</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Play App Signing final SHA-256はNEEDS_USER_ACTION。今回ターンでは外部live URL再検証未実施。</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>修正なし: 台帳追跡行として追加。</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>再テスト未実施: final SHA確定後にcurl/JSON parse/端末リンク確認が必要。</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>公開/ストア運用はコード機能ではないが、アプリ機能の到達性とストア審査に直結するためESとして追跡。</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S42"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
+  <sheetPr/>
+  <dimension ref="A1:B8"/>
+  <sheetViews/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>更新日時</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:43:50 +0900</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Android local</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>PASS: assembleDebug/testDebugUnitTest/lintDebug/assembleRelease</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>総ストーリー数</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Android physical</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>PASS: Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum, home/use guide/back evidence captured</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>今回追加</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>US-034 共有保存時タグ選択/作成, US-035 コレクション, US-036 ChatGPT sync, AS-008 問い合わせ監査, ES-006 公開Web/リンク</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>iOS local</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL: Release generic build/build-for-testing PASS; XCTest実行はCoreSimulator不整合で未実施</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Android targeted</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PASS: ShareReceiverActivityEntrypointTest/RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest; ContactSupportClientTest</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>iPhone physical</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL: 00008101-00066D96340A001E, com.mibu.codebridge.ios installed/launched; Appium UI proof blocked by RemoteXPC/WDA</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Supabase functions</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PASS: deno check verify-store-purchase/contact-support/contact-support-resend-webhook</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Web admin</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>PASS: npm run typecheck/build</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Known gaps</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Physical share/invite/purchase operations, Supabase DB live/RLS, store sandbox purchases, final Play SHA remain unverified</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Supabase</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED_LOCAL: local DB not running; linked/prod not touched</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>修正</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>コード/UX修正なし。サイズ/デザイン変更なし。</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>未コミット注意</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>build.gradle.kts remains uncommitted unrelated AGP version change</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -449,10 +449,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
-  <dimension ref="A1:S51"/>
-  <sheetViews/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,7 +1063,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EntryCardDisplayMode.kt; EntryCard.kt; MainListViewModel.kt; ArchiveViewModel.kt</t>
+          <t>EntryCardDisplayMode.kt; EntryCard.kt; MainListViewModel.kt; ArchiveViewModel.kt; EntryCardDisplayModeStore.kt; RootView.swift; AppChrome.swift</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1075,7 +1073,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>表示モードが保存され、Main/Archiveで反映される。</t>
+          <t>表示モードが保存され、Main/Archive/Tag detailで反映される。AndroidはDataStore、iOSは@AppStorageで再起動後も保持する。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1090,27 +1088,27 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests MainListViewModelTest.toggleEntryCardDisplayMode_updatesStore --tests ArchiveViewModelTest 成功。PASS: iOS generic simulator build成功。iOS RootView/AppChromeを@AppStorage保存へ修正。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>物理Android/iPhoneでの表示モード切替と再起動後保持は未検証。以前のiOSは@Stateのみで再起動後保持しないギャップがあり、今回修正済み。</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>FIXED_LOCAL: iOS displayModeをEntryListDisplayMode.rawValue + @AppStorage("entryListDisplayMode")で永続化。</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: Android targeted unit、iOS generic build成功。物理端末再起動保持は未実施。</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1125,12 +1123,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t/>
+          <t>iOS display mode persistence fixed 2026-06-29.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 00:57:14 +0900</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1645,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FetchMetadataWorker.kt; MetadataFetcher.kt; MetadataCoordinator.swift; MetadataStatusTextTests.swift; MetadataUiText.kt</t>
+          <t>FetchMetadataWorker.kt; MetadataFetcher.kt; MetadataCoordinator.swift; MetadataStatusTextTests.swift; MetadataUiText.kt; MetadataWorkScheduler.kt; ResolveWorker.kt; AppBackgroundScheduler.swift; BackgroundTaskRunner.swift</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1657,7 +1655,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>READY/PENDING/FAILED/UNAVAILABLEをUI文言へ分離し、部分成功をREADY扱いする。</t>
+          <t>READY/PENDING/FAILED/UNAVAILABLEをUI文言へ分離し、部分成功をREADY扱いする。 iOSはBGTaskSchedulerでbest-effortにmetadata backlogを再実行し、expiration時は一度だけ失敗完了する。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1672,17 +1670,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: iOS MetadataStatusTextTests 5件成功し、BackgroundTaskRunnerの成功/失敗/expiration完了契約を確認。Android metadata系は既存unit/buildで通過済み。</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。 iOS実機BGTaskSchedulerの実スケジュール発火、Android WorkManager実機発火は未検証。</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1692,7 +1690,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: iOS MetadataStatusTextTests成功。実機バックグラウンド発火は未実施。</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1707,12 +1705,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t/>
+          <t>iOS BGTaskScheduler/BackgroundTaskRunner coverage added 2026-06-29.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 00:57:14 +0900</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2227,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SharedTagSyncWorker.kt; SharedTagSyncCoordinator.kt; SharedTagSyncExecutor.swift; SharedTagCloud.swift</t>
+          <t>SharedTagSyncWorker.kt; SharedTagSyncCoordinator.kt; SharedTagSyncExecutor.swift; SharedTagCloud.swift; SQLiteDatabase.swift</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2254,27 +2252,27 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: iOS MetadataStatusTextTests 5件成功。SharedTagCloud migrationのdisplay_name追加をaddColumnIfMissingへ変更し、重複カラムログが消えたことを/tmp/rinbam-metadata-test.logで確認。</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>物理端末での共有タグ同期/グループ同期、Supabase live syncは未検証。iOS simulatorではApp Group entitlement警告とCoreSimulator WebCore/WebKit重複クラス警告が残るが、display_name重複カラムログは解消。</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>FIXED_LOCAL: SharedTagCloud migrationのtry? ALTER TABLEをSQLiteDatabase.addColumnIfMissingへ置換し、既存DBでの冪等性を改善。</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: xcodebuild test -only-testing:URLSaveriOSTests/MetadataStatusTextTests 成功、重複display_name migrationログなし。</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2284,17 +2282,17 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>NOT VERIFIED on physical iPhone: 共有タグ/グループ同期は未検証。</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t/>
+          <t>iOS shared tag display_name migration idempotency fixed 2026-06-29.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 01:02:48 +0900</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2324,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DefaultTagRepository.kt; SharedTagCloudScreens.kt; SharedTagManagementSheets.swift; SharedTagCloud.swift</t>
+          <t>DefaultTagRepository.kt; SharedTagCloudScreens.kt; SharedTagManagementSheets.swift; SharedTagCloud.swift; SQLiteDatabase.swift</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2351,27 +2349,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: iOS MetadataStatusTextTests 5件成功。SharedTagCloud migrationのdisplay_name追加をaddColumnIfMissingへ変更し、重複カラムログが消えたことを/tmp/rinbam-metadata-test.logで確認。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>物理端末での共有タグ同期/グループ同期、Supabase live syncは未検証。iOS simulatorではApp Group entitlement警告とCoreSimulator WebCore/WebKit重複クラス警告が残るが、display_name重複カラムログは解消。</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>FIXED_LOCAL: SharedTagCloud migrationのtry? ALTER TABLEをSQLiteDatabase.addColumnIfMissingへ置換し、既存DBでの冪等性を改善。</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: xcodebuild test -only-testing:URLSaveriOSTests/MetadataStatusTextTests 成功、重複display_name migrationログなし。</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2381,17 +2379,17 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>NOT VERIFIED on physical iPhone: 共有タグ/グループ同期は未検証。</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t/>
+          <t>iOS shared tag display_name migration idempotency fixed 2026-06-29.</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 01:02:48 +0900</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2712,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EntitlementGrantRepository.kt; SharedTagCloudScreens.kt; URLSaverAppModel.swift; SharedTagCloud.swift</t>
+          <t>EntitlementGrantRepository.kt; SharedTagCloudScreens.kt; URLSaverAppModel.swift; SharedTagCloud.swift; EntitlementGrantStore.kt; EntitlementGrantRemoteDataSource.kt; UsageSummaryDataSource.kt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2739,27 +2737,27 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests EntitlementResolverTest 成功。PASS: iOS URLRulesTests LimitChecker対象2件成功。SharedTagAuthViewModelTestは直近実行済み。</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>本番Supabase RPC/get_my_entitlement_grants/redeem_promo_code live実行、実メール/リンクからの優待適用、物理端末操作は未検証。</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>修正なし: ローカルテスト上のエラー未検出。Entitlement cache/remote/usage summaryのcode_basisを補強。</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: Android entitlement targeted test、iOS limit checker targeted tests成功。</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2774,12 +2772,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t/>
+          <t>entitlement cache/remote coverage refreshed 2026-06-29.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 01:00:20 +0900</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2809,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PlanModels.kt; Models.swift; EntitlementResolver.kt</t>
+          <t>PlanModels.kt; Models.swift; EntitlementResolver.kt; UsageSummaryDataSource.kt; EntitlementResolverTest.kt; URLRulesTests.swift</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2836,27 +2834,27 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests EntitlementResolverTest 成功。PASS: iOS URLRulesTests LimitChecker対象2件成功。</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>物理端末で実使用量が上限に達した時のUI文言/ブロック、Supabase live grant反映は未検証。</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>修正なし: ローカル制限判定テスト上のエラー未検出。</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: Android/iOS limit checker targeted tests成功。</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2871,12 +2869,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t/>
+          <t>usage/limit checker coverage refreshed 2026-06-29.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 01:00:20 +0900</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2906,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ExportRepository.kt; ExportScreen.kt; ExportArchiveBuilder.swift; ExportSheet.swift</t>
+          <t>ExportRepository.kt; ExportScreen.kt; ExportArchiveBuilder.swift; ExportSheet.swift; ExportViewModel.kt; ActivityShareSheet.swift; URLSaverAppModel.swift</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2918,7 +2916,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>manifest、entries.jsonl、entries/*.md またはJSONを生成し、範囲/タグ/状態/サービス/メモ/日付フィルタ対応。</t>
+          <t>manifest、entries.jsonl、entries/*.md またはJSONを生成し、範囲/タグ/状態/サービス/メモ/日付フィルタ対応。Androidは共有シート/ファイル保存、iOSはUIActivityViewController/fileExporterで出力できる。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2933,47 +2931,47 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests ExportRepositoryTest --tests ExportScreenTest 成功。PASS: iOS ExportArchiveBuilderTests/ServiceFilterTests 対象実行19件中Export関連17件成功。</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>物理Android/iPhoneでの共有シート、ファイル保存、ファイル受け渡し先アプリでの実確認は未検証。iOS simulator test中にApp Group entitlement警告と重複display_name migrationログあり、テスト失敗はなし。</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>修正なし: ローカルテスト上のエラー未検出。台帳code_basisに共有シート/保存先実装を補強。</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>PASS local retest: Android export targeted tests、iOS export/filter targeted tests成功。物理共有先は未実施。</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>未実機操作: export共有シート/ファイル保存は未検証。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>NOT VERIFIED on physical iPhone: export共有シート/fileExporterは未検証。</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t/>
+          <t>export share/file destination coverage refreshed 2026-06-29.</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 01:00:20 +0900</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4130,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>US-034/US-035/US-036/AS-008/ES-006を追加。</t>
+          <t>US-034/US-035/US-036/AS-008/ES-006を追加。 US-037/US-038/US-039/US-040/TS-001を追加。 AS-009を追加し、US-039に公開reset-passwordページを追記。 US-006のiOS表示モード永続化ギャップを修正し、US-012にiOS BGTaskScheduler証跡を追記。 US-025/US-023/US-024のexport/entitlement近接テスト結果を更新。US-040にiOS PrivacyInfo証跡を補強。 iOS SharedTagCloud display_name migrationの冪等性を修正し、US-018/US-019/ES-003へ反映。</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>2026-06-29 01:02:48 +0900</t>
         </is>
       </c>
     </row>
@@ -4291,27 +4289,27 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_LIVE_SUPABASE_ENV_GAP</t>
+          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PASS: 2026-06-29 iOS generic Simulator build成功、URLRepositoryTests単独成功、PendingInviteStoreTests単独成功。PARTIAL: 全体XCTestはSharedTagCloudLiveSyncTests 3件がInvalid API keyで失敗。</t>
+          <t>PASS: iOS MetadataStatusTextTests 5件成功。display_name duplicate column migrationログとApp Group container_create_or_lookup警告は修正後に消失。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>iOS全体XCTest: live Supabase shared-tag tests が Invalid API key で失敗。ローカル対象テストは成功。物理iPhone UI操作は未検証。</t>
+          <t>iOS simulator testでCoreSimulator WebCore/WebKit重複クラス警告は残存。物理iPhone UI操作は未検証。</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>PARTIAL_FIXED_LOCAL: SharedTagCloud migrationの重複カラムログとSharedContainerのXCTest時App Group lookup警告を修正。残る警告はCoreSimulator runtime由来として継続記録。</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>PASS local targeted retest。live Supabaseキー/環境が整ったら全体再実行。</t>
+          <t>PASS local retest: MetadataStatusTextTests成功、duplicate display_nameログなし、container_create_or_lookupログなし。</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4326,12 +4324,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t/>
+          <t>App Group XCTest warning fixed 2026-06-29; CoreSimulator UIAccessibilityLoaderWebShared warning remains.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-06-29 00:36:46 +0900</t>
+          <t>2026-06-29 01:07:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5399,6 +5397,588 @@
       <c r="S51" t="inlineStr">
         <is>
           <t>2026-06-29 00:43:50 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>US-037</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>保存リンク検索</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>UrlSaverRoot.kt; RootView.swift; MainListViewModel.kt; URLSaverAppModel.swift</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ユーザーとして、保存済みリンクをタイトル、URL、ホスト、コレクション、タグ名で検索し、目的のリンクだけを一覧に絞り込める。</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。クリアまたは戻る操作で検索状態を解除し、使い方画面表示中の検索操作はホーム検索へ戻る。</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Android/iOS source inspection; future UI test: search input, clear, no-result, guide-to-search transition. Android existing local build/test/lint; iOS generic build.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>正準Android/iOSアプリで実データを消さずに検索欄表示、入力、クリア、戻るが動くこと。</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SOURCE_CONFIRMED_WITH_UI_TEST_GAP</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>PASS(source): Android filterEntriesBySearch and searchBarVisible, iOS isShowingSearchBar/searchQuery UIを確認。近接build/testは既存実行で成功済み。</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>専用unit/UIテストと物理端末検索操作は未実施。Androidの検索はprivate UI関数中心で現在はソース確認寄り。</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>修正なし: 台帳未記載の既存機能として追加。</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>未実施: 専用UI確認が必要。</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>未実機操作: 検索欄表示/入力/クリアは未検証。</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: 検索欄表示/入力/クリアは未検証。</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>AS-005の管理者検索とは別のユーザー向けホーム検索。</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:49:24 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>US-038</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>一覧</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>複数選択で一括アーカイブ/削除</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>UrlSaverRoot.kt; MainActivityViewModel.kt; RootView.swift; URLSaverAppModel.swift</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ユーザーとして、複数の保存リンクを選択してまとめてアーカイブまたは削除し、Undoで戻せる。</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>選択モード、個別選択、すべて選択、キャンセル、一括アーカイブ、一括pending delete、Undo通知が動く。選択中は通常ボトムバーを隠す。</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Android/iOS source inspection; Android targeted unit for MainActivityViewModel batch archive/delete; iOS source inspection for archive(entryIDs)/markPendingDelete(entryIDs). Future physical UI selection.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>実データ保護のため物理端末ではテスト用データで選択/Undoまで確認すること。</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>SOURCE_CONFIRMED_WITH_DEVICE_GAP</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>PASS(source): Android selectedEntryIds/EntrySelectionBar/archiveEntries/markPendingDeleteEntries確認。iOS EntrySelectionBar/archive(entryIDs)/markPendingDelete(entryIDs)確認。</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>物理端末UI操作と専用UIテスト未実施。</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>修正なし: 台帳未記載の既存機能として追加。</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>未実施: UI実操作確認が必要。</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>未実機操作: 一括選択/Undoは未検証。</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: 一括選択/Undoは未検証。</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>US-007/US-008の単体操作とは別の一括操作。</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:49:24 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>US-039</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Android/iOS/Supabase</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>確認メール再送/パスワード再設定</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SharedTagCloudScreens.kt; SharedTagAuthViewModel.kt; DefaultTagRepository.kt; SharedTagAuthRemoteDataSource.kt; SharedTagCloudSheet.swift; URLSaverAppModel.swift; SharedTagCloud.swift; web/invite-link/auth/reset-password/index.html; web/invite-link/index.html; web/invite-link/vercel.json</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ユーザーとして、共有タグクラウドのサインイン/招待参加で確認メールを再送したり、パスワード再設定メールを送信できる。</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>メール入力後、確認メール再送とパスワード再設定ボタンがSupabase auth endpointを呼び、成功/失敗メッセージを表示する。招待参加画面でも同じ補助導線を使える。 公開reset-passwordページはSupabase recovery code/sessionを受け取り、8文字以上かつ確認一致後にupdateUserで新パスワードを設定する。</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Android SharedTagAuthViewModelTest/TagRepositoryTest source; iOS source inspection/generic build; future Supabase auth live mail delivery verification.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>本番Supabase auth SMTP/redirect URL設定で実メールが届き、アプリの文言が成功扱いだけで誤解を生まないこと。</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>PASS: ./gradlew testDebugUnitTest --tests SharedTagAuthViewModelTest 成功。Source inspectionでAndroid/iOS resendEmailConfirmation/sendPasswordRecovery経路確認。 PASS(source): reset-password static pageのexchangeCodeForSession/updateUser/signOut経路を確認。</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Supabase本番メール送信/到達、redirect挙動、物理端末操作は未検証。 公開reset-passwordページのlive到達と実メールリンクからの更新は未検証。</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>修正なし: US-020から独立した補助機能として台帳追加。</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>未実施: live auth mailが必要。</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>未実機操作: 確認メール再送/パスワード再設定は未検証。</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on physical iPhone: 確認メール再送/パスワード再設定は未検証。</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>US-020は基本サインイン系。メール補助は外部メール到達が別ゲート。 targeted unit pass 2026-06-29. reset-password public page source-confirmed 2026-06-29.</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:52:34 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>US-040</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Android/Store</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>プライバシー/広告</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>データ取り扱い表示と広告無効化ガード</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UrlSaverRoot.kt; strings.xml; AdsConfig.kt; AdsManager.kt; BannerAdSlot.kt; AdsConfigTest.kt; docs/release/final-submission-checklist.md; ios/URLSaveriOS/PrivacyInfo.xcprivacy; ios/URLSaverShareExtension/PrivacyInfo.xcprivacy</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ユーザーとして、保存データの扱いをアプリ内で確認でき、リリース設定では広告SDKが初期化/表示されない状態で使える。</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>プライバシーダイアログ文言が表示可能で、ADS_ENABLED/ADS_TRIAL_LAUNCH_ADS_ENABLEDが無効ならSDK初期化、バナー、インタースティシャルが走らない。</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Android AdsConfigTest; source inspection for privacy dialog; release checklist review; future physical UI privacy dialog確認。</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Google Playのデータセーフティ/広告申告、リリースmanifest、アプリ内説明が最終build設定と一致すること。</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>PASS: ./gradlew testDebugUnitTest --tests AdsConfigTest 成功。Source inspectionでprivacy_dialog stringsとUrlSaverRoot AlertDialogを確認。</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>物理端末でのプライバシーダイアログ表示とPlay Console最終申告一致は未検証。</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>修正なし: 台帳未記載の既存ユーザー/ストア影響機能として追加。</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>未実施: store申告最終確認が必要。</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>未実機操作: プライバシーダイアログ表示は未検証。</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>ES-006は公開Web/リンク。これはAndroidアプリ内表示と広告ガード。 targeted unit pass 2026-06-29. iOS privacy manifests included in release source review.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026-06-29 01:00:20 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TS-001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>開発/従業員</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>未実装基盤</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>UserLabel DB/Repository基盤のみでUI未接続</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>UserLabelDao.kt; RoomModels.kt; AppDatabase.kt; DefaultUrlRepositoryCollectionsSupport.kt; UrlRepository.kt; MigrationDedupTest.kt</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>開発者として、将来のユーザーラベル機能のDB/Repository基盤がある一方、現行アップロード対象アプリではユーザーがラベルを作成/割当/削除するUIが未提供であることを追跡できる。</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>user_labels table、url_entries.userLabelId、create/delete/assign API、migration testが存在する。Compose/SwiftUIのユーザー操作面には同等ラベルUIがないことを明示する。</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Android source inspection; MigrationDedupTest migration_8_9_preservesExistingData_andCreatesUserLabels; rgでUI参照確認。</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>リリース判断時に「基礎はあるがユーザー機能ではない」と扱い、ストア説明やUI期待に載せないこと。</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>PASS: ./gradlew testDebugUnitTest --tests MigrationDedupTest.migration_8_9_preservesExistingData_andCreatesUserLabels 成功。DAO/Entity/Repository/APIはsource確認、UI入口は未確認。</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>機能基礎はあるが現行ユーザーUI未実装。iOS側に同等UserLabelモデルは未確認。</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>未修正: 仕様化するならAndroid UI追加とiOS parity設計が必要。現状は未実装基盤として記録。</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>未実施: UI実装後に再テスト。</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>該当UIなし。</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>該当UIなし。</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>ユーザー依頼の「基礎は作ったが実装していないもの」候補として追跡。 targeted unit pass 2026-06-29.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:50:01 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AS-009</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Web/Admin/Resend</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>配信監査</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Resend message id手動配送照会</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>web/admin/app/api/admin/promo-codes/[id]/delivery/route.ts; web/admin/app/page.tsx; web/admin/lib/auth.ts; web/admin/lib/env.ts</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>管理者として、優待コードに保存されたResend message idからResend APIを照会し、最後の配送イベントや宛先情報を確認できる。</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>管理者認証が必要。delivery_message_idがない場合は404を返し、Resend API応答からid/message_id/from/to/subject/created_at/last_eventを返す。RESEND_API_KEY未設定やResendエラーは明示する。</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Web admin npm typecheck/build; source inspection; future live Resend API call with real delivery_message_id.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>本番管理者トークン、service role、RESEND_API_KEY、実delivery_message_idでResendのtruthとDB状態が一致すること。</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>PASS: npm run typecheck &amp;&amp; npm run build 成功。Next build route一覧に /api/admin/promo-codes/[id]/delivery が含まれることを確認。Source inspectionでResend API照会経路確認。</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Resend live API照会、実message id、管理画面ボタン/表示の操作は未検証。</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>修正なし: AS-006 webhook追跡とは別の手動配送照会機能として台帳追加。</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>未実施: live Resend APIと管理者セッションが必要。</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>AS-006はwebhook反映、AS-009はResend APIへの手動照会。</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:53:06 +0900</t>
         </is>
       </c>
     </row>
@@ -5408,105 +5988,271 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetViews/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>値</t>
+          <t>count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>ANDROID_LOCAL_PASS_WITH_IOS_MODEL_DIFFERENCE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>総ストーリー数</t>
+          <t>DOCUMENTED_PASS_WITH_FINAL_SHA_GAP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>今回追加</t>
+          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>US-034 共有保存時タグ選択/作成, US-035 コレクション, US-036 ChatGPT sync, AS-008 問い合わせ監査, ES-006 公開Web/リンク</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Android targeted</t>
+          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PASS: ShareReceiverActivityEntrypointTest/RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest; ContactSupportClientTest</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Supabase functions</t>
+          <t>LOCAL_PASS_WITH_DEPLOY_GAP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PASS: deno check verify-store-purchase/contact-support/contact-support-resend-webhook</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Known gaps</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Physical share/invite/purchase operations, Supabase DB live/RLS, store sandbox purchases, final Play SHA remain unverified</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>未コミット注意</t>
+          <t>LOCAL_PASS_WITH_EXTERNAL_STORE_GAP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>build.gradle.kts remains uncommitted unrelated AGP version change</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_LIVE_GAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS_WITH_LOCAL_DB_GAP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS_WITH_SIMULATOR_WARNINGS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PASS: Androidローカル検証成功、release buildも成功、実機共有系は未検証</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PASS: Web管理画面 typecheck/build 成功</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SOURCE_CONFIRMED_WITH_DEVICE_GAP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SOURCE_CONFIRMED_WITH_UI_TEST_GAP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Android/iOS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CollectionDao.kt; CollectionModels.kt; DefaultUrlRepositoryCollectionsSupport.kt; CollectionFilterRow.kt; MainListViewModel.kt; RepositoryBehaviorTest.kt; TopFilterOrderResolutionTest.kt</t>
+          <t>CollectionDao.kt; CollectionModels.kt; DefaultUrlRepositoryCollectionsSupport.kt; CollectionFilterRow.kt; MainListViewModel.kt; URLRepository.swift; Models.swift; URLRepositoryTests.swift</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>RepositoryBehaviorTest; MainListViewModelTest; ListFilterStateTest; TopFilterOrderResolutionTest; assembleDebug/testDebugUnitTest/lintDebug</t>
+          <t>Android: RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest. iOS: URLRepositoryTests collection lifecycle. Future iOS collection UI tests.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5065,27 +5065,27 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>ANDROID_LOCAL_PASS_WITH_IOS_MODEL_DIFFERENCE</t>
+          <t>LOCAL_PASS_WITH_IOS_UI_GAP</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PASS: RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。Android全体build/test/lint成功。</t>
+          <t>PASS: Android RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。PASS: iOS URLRepositoryTests 12件成功、受信箱/作成/重複/移動/並び替え/削除時受信箱戻しを確認。</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>iOSは同名のcollectionモデルではなくlocal tag中心の整理UI。Android固有機能として記録。物理Androidで並び替え/削除は未検証。</t>
+          <t>iOSはcollectionsテーブル/API/URLRecord.collectionIDの土台を追加済み。自作コレクションの作成、移動、並び替え、フィルタUIは未実装。物理Androidで並び替え/削除は未検証。</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>修正なし: ローカルテスト上のエラー未検出。</t>
+          <t>PARTIAL_FIXED_LOCAL: iOS collectionsテーブル、CollectionSummary、create/assign/reorder/delete/load API、collection_id DEFAULT 1を追加。US-035完全復元にはiOS UI接続が必要。</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>PASS local retest。実機UI操作は未実施。</t>
+          <t>PASS local retest: iOS URLRepositoryTests 12件成功。Android既存ローカルテストは前回成功済み。iOS UI実装/実機操作は未実施。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5095,17 +5095,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t/>
+          <t>NOT VERIFIED on physical iPhone: コレクション作成/移動/並び替え/フィルタUIは未実装・未検証。</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>iOS parityはlocal tag管理で別途US-014/US-031/US-034に追跡。</t>
+          <t>iOS collection repository/API foundation added 2026-06-29; full UI parity still required.</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>2026-06-29 01:24:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UrlSaverRoot.kt; RootView.swift; MainListViewModel.kt; URLSaverAppModel.swift</t>
+          <t>UrlSaverRoot.kt; MainListViewModel.kt; TagDao.kt; RootView.swift; ServiceFilterTests.swift; MainListViewModelTest.kt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。クリアまたは戻る操作で検索状態を解除し、使い方画面表示中の検索操作はホーム検索へ戻る。</t>
+          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。Androidはタイトル/URL/ホスト/コレクション名/割当ローカルタグ名、iOSはタイトル/URL/ホスト/割当ローカルタグ名を検索対象にする。未割当タグ名ではヒットしない。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Android/iOS source inspection; future UI test: search input, clear, no-result, guide-to-search transition. Android existing local build/test/lint; iOS generic build.</t>
+          <t>Android: MainListViewModelTest search tests. iOS: ServiceFilterTests search tests. Future UI test: search input, clear, no-result, guide-to-search transition.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5453,27 +5453,27 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SOURCE_CONFIRMED_WITH_UI_TEST_GAP</t>
+          <t>LOCAL_PASS_WITH_UI_DEVICE_GAP</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PASS(source): Android filterEntriesBySearch and searchBarVisible, iOS isShowingSearchBar/searchQuery UIを確認。近接build/testは既存実行で成功済み。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/ServiceFilterTests 成功、15 tests。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>専用unit/UIテストと物理端末検索操作は未実施。Androidの検索はprivate UI関数中心で現在はソース確認寄り。</t>
+          <t>物理Android/iPhoneでの検索欄表示、入力、クリア、戻る操作は未検証。iOSはcollections Repository/APIの土台は追加済みだが、RootView検索へのコレクション名連携はまだ未接続。</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>修正なし: 台帳未記載の既存機能として追加。</t>
+          <t>FIXED_LOCAL: Androidのタグ名検索が任意タグ名一致で全件ヒットし得る誤爆を修正。Android/iOSとも割当ローカルタグ名だけを検索対象にするテストを追加。</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>未実施: 専用UI確認が必要。</t>
+          <t>PASS local retest: Android MainListViewModelTest、iOS ServiceFilterTests 成功。UI実操作は未実施。</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>AS-005の管理者検索とは別のユーザー向けホーム検索。</t>
+          <t>User search local-tag false-positive fixed 2026-06-29. iOS collection repository/API foundation exists; collection-name search still needs RootView/UI wiring.</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-06-29 00:49:24 +0900</t>
+          <t>2026-06-29 01:24:30 +0900</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UrlSaverRoot.kt; MainActivityViewModel.kt; RootView.swift; URLSaverAppModel.swift</t>
+          <t>UrlSaverRoot.kt; MainListViewModel.kt; RootView.swift; URLSaverAppModel.swift; URLRepository.swift; MainListViewModelTest.kt; URLRepositoryTests.swift</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Android/iOS source inspection; Android targeted unit for MainActivityViewModel batch archive/delete; iOS source inspection for archive(entryIDs)/markPendingDelete(entryIDs). Future physical UI selection.</t>
+          <t>Android: MainListViewModelTest batch archive/delete. iOS: URLRepositoryTests multiple archive/pending-delete state transitions. Future physical UI selection.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5550,27 +5550,27 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SOURCE_CONFIRMED_WITH_DEVICE_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PASS(source): Android selectedEntryIds/EntrySelectionBar/archiveEntries/markPendingDeleteEntries確認。iOS EntrySelectionBar/archive(entryIDs)/markPendingDelete(entryIDs)確認。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/URLRepositoryTests 成功、10 tests。</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>物理端末UI操作と専用UIテスト未実施。</t>
+          <t>物理端末UI操作は未検証。iOSは保存層の複数件状態遷移を検証済みだが、RootViewの選択バー操作そのものは未検証。</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>修正なし: 台帳未記載の既存機能として追加。</t>
+          <t>TESTED_LOCAL: Android ViewModel一括archive/pending deleteの成功/失敗混在をテスト追加。iOS URLRepositoryで複数件archive/pending delete状態遷移をテスト追加。</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>未実施: UI実操作確認が必要。</t>
+          <t>PASS local retest: Android MainListViewModelTest、iOS URLRepositoryTests 成功。物理UI選択/Undo操作は未実施。</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>US-007/US-008の単体操作とは別の一括操作。</t>
+          <t>Batch selection local contract tests added 2026-06-29. UI operation still needs physical-device proof.</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-06-29 00:49:24 +0900</t>
+          <t>2026-06-29 01:16:00 +0900</t>
         </is>
       </c>
     </row>

--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -5065,27 +5065,27 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IOS_UI_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PASS: Android RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。PASS: iOS URLRepositoryTests 12件成功、受信箱/作成/重複/移動/並び替え/削除時受信箱戻しを確認。</t>
+          <t>PASS: Android RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。PASS: iOS URLRepositoryTests 12件成功、受信箱/作成/重複/移動/並び替え/削除時受信箱戻し/削除時同名ローカルタグ削除を確認。PASS: iOS ServiceFilterTests 18件成功、RootView/AppChrome/DetailViewのコレクション作成/選択/移動/削除/並び替え/検索/同名ローカルタグ込みフィルタ契約を確認。</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>iOSはcollectionsテーブル/API/URLRecord.collectionIDの土台を追加済み。自作コレクションの作成、移動、並び替え、フィルタUIは未実装。物理Androidで並び替え/削除は未検証。</t>
+          <t>物理Androidでコレクション並び替え/削除、物理iPhoneでコレクション作成/保存先選択/既存URL移動/削除/並び替え/フィルタUIは未検証。iOSの同名ローカルタグ連携は、詳細移動時の作成/割当、削除時の同名タグ削除、コレクション選択時の同名タグ付きURL表示までローカル実装済みだが、実機操作は未確認。</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PARTIAL_FIXED_LOCAL: iOS collectionsテーブル、CollectionSummary、create/assign/reorder/delete/load API、collection_id DEFAULT 1を追加。US-035完全復元にはiOS UI接続が必要。</t>
+          <t>FIXED_LOCAL: iOS collectionsテーブル/API、AppModel.collections、上部コレクションチップ、+保存先作成、保存先管理シート、手動保存先選択、詳細画面の保存先表示/移動シート、削除/並び替え、同名ローカルタグ連携、検索/フィルタ連携を追加。Android同様に同名ローカルタグ付きURLも選択コレクションに含める。</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>PASS local retest: iOS URLRepositoryTests 12件成功。Android既存ローカルテストは前回成功済み。iOS UI実装/実機操作は未実施。</t>
+          <t>PASS local retest: iOS URLRepositoryTests + ServiceFilterTests 30件成功。Android既存ローカルテストは前回成功済み。iOS/Android物理UI操作は未実施。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5095,17 +5095,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: コレクション作成/移動/並び替え/フィルタUIは未実装・未検証。</t>
+          <t>NOT VERIFIED on physical iPhone: コレクション作成/保存先選択/既存URL移動/削除/並び替え/フィルタUIは実機操作未検証。</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>iOS collection repository/API foundation added 2026-06-29; full UI parity still required.</t>
+          <t>iOS collection parity local implementation completed for create/filter/manual-save/detail-move/manage/delete/reorder/search/same-name local-tag linkage on 2026-06-29. Same-name local-tag filter parity added after gap audit. Physical-device proof still required.</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-06-29 01:24:00 +0900</t>
+          <t>2026-06-29 01:43:21 +0900</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。Androidはタイトル/URL/ホスト/コレクション名/割当ローカルタグ名、iOSはタイトル/URL/ホスト/割当ローカルタグ名を検索対象にする。未割当タグ名ではヒットしない。</t>
+          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。Android/iOSともタイトル/URL/ホスト/コレクション名/割当ローカルタグ名を検索対象にする。未割当タグ名ではヒットしない。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5458,22 +5458,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/ServiceFilterTests 成功、15 tests。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/ServiceFilterTests 成功、17 tests。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>物理Android/iPhoneでの検索欄表示、入力、クリア、戻る操作は未検証。iOSはcollections Repository/APIの土台は追加済みだが、RootView検索へのコレクション名連携はまだ未接続。</t>
+          <t>物理Android/iPhoneでの検索欄表示、入力、クリア、戻る操作は未検証。iOSのコレクション名検索はRootView/AppChrome経由で接続済みだが実機UI操作は未検証。</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>FIXED_LOCAL: Androidのタグ名検索が任意タグ名一致で全件ヒットし得る誤爆を修正。Android/iOSとも割当ローカルタグ名だけを検索対象にするテストを追加。</t>
+          <t>FIXED_LOCAL: Androidのタグ名検索が任意タグ名一致で全件ヒットし得る誤爆を修正。Android/iOSとも割当ローカルタグ名だけを検索対象にし、iOSもコレクション名検索を追加。</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>PASS local retest: Android MainListViewModelTest、iOS ServiceFilterTests 成功。UI実操作は未実施。</t>
+          <t>PASS local retest: Android MainListViewModelTest、iOS ServiceFilterTests 17件成功。UI実操作は未実施。</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: 検索欄表示/入力/クリアは未検証。</t>
+          <t>NOT VERIFIED on physical iPhone: 検索欄表示/入力/クリアとコレクション名検索の実機操作は未検証。</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>User search local-tag false-positive fixed 2026-06-29. iOS collection repository/API foundation exists; collection-name search still needs RootView/UI wiring.</t>
+          <t>User search local-tag false-positive fixed 2026-06-29. iOS collection-name search wired and tested 2026-06-29.</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-06-29 01:24:30 +0900</t>
+          <t>2026-06-29 01:32:41 +0900</t>
         </is>
       </c>
     </row>
@@ -5983,13 +5983,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6007,7 +6006,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANDROID_LOCAL_PASS_WITH_IOS_MODEL_DIFFERENCE</t>
+          <t>DOCUMENTED_PASS_WITH_FINAL_SHA_GAP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6019,7 +6018,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DOCUMENTED_PASS_WITH_FINAL_SHA_GAP</t>
+          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6031,48 +6030,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
+          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
+          <t>LOCAL_PASS_WITH_DEPLOY_GAP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEPLOY_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6126,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_LIVE_GAP</t>
+          <t>LOCAL_PASS_WITH_UI_DEVICE_GAP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6139,7 +6138,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_LIVE_GAP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6151,19 +6150,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
+          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6175,19 +6174,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_LOCAL_DB_GAP</t>
+          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_SIMULATOR_WARNINGS</t>
+          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6199,7 +6198,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PASS: Androidローカル検証成功、release buildも成功、実機共有系は未検証</t>
+          <t>PARTIAL_PASS_WITH_LOCAL_DB_GAP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6211,7 +6210,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PASS: Web管理画面 typecheck/build 成功</t>
+          <t>PASS: Androidローカル検証成功、release buildも成功、実機共有系は未検証</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6223,7 +6222,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
+          <t>PASS: Web管理画面 typecheck/build 成功</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6235,7 +6234,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOURCE_CONFIRMED_WITH_DEVICE_GAP</t>
+          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6244,19 +6243,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SOURCE_CONFIRMED_WITH_UI_TEST_GAP</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'canonical_story_status'!$A$1:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'canonical_story_status'!$A$1:$S$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:S57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -4110,12 +4110,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>FIXED_LOCAL: XLSXの_FilterDatabase定義をA1:S57へ更新し、summaryシートもCSV最新ステータス集計と残ゲート集計から再生成。</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>PASS: CSV/XLSX更新後に行数/ID/XLSX dimension確認予定。</t>
+          <t>PASS: CSV 56行、XLSX dimension A1:S57、_FilterDatabase A1:S57、CSV/XLSXセル差分0、summaryステータス集計一致、summary残ゲート集計生成、XLSX zip integrity確認済み。</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>US-034/US-035/US-036/AS-008/ES-006を追加。 US-037/US-038/US-039/US-040/TS-001を追加。 AS-009を追加し、US-039に公開reset-passwordページを追記。 US-006のiOS表示モード永続化ギャップを修正し、US-012にiOS BGTaskScheduler証跡を追記。 US-025/US-023/US-024のexport/entitlement近接テスト結果を更新。US-040にiOS PrivacyInfo証跡を補強。 iOS SharedTagCloud display_name migrationの冪等性を修正し、US-018/US-019/ES-003へ反映。</t>
+          <t>US-034/US-035/US-036/AS-008/ES-006を追加。 US-037/US-038/US-039/US-040/TS-001を追加。 AS-009を追加し、US-039に公開reset-passwordページを追記。 US-006のiOS表示モード永続化ギャップを修正し、US-012にiOS BGTaskScheduler証跡を追記。 US-025/US-023/US-024のexport/entitlement近接テスト結果を更新。US-040にiOS PrivacyInfo証跡を補強。 iOS SharedTagCloud display_name migrationの冪等性を修正し、US-018/US-019/ES-003へ反映。2026-06-29にXLSXフィルタ範囲、summaryステータス集計、残ゲート集計を実データへ修正。Public privacy stale検出後にsummary再生成。 Release privacy/store docsのpublic privacy stale反映後にsummary再生成。 Public web verifier追加後にsummary再生成。 Android privacy dialog文言更新後にsummary再生成。</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-06-29 01:02:48 +0900</t>
+          <t>2026-06-29 02:11:30 +0900</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>PASS: Androidローカル検証成功、release buildも成功、実機共有系は未検証</t>
+          <t>LOCAL_PASS_WITH_CONNECTED_TEST_GAP</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Release manifestで広告/AD_ID削除指定の対象なしwarning、MenuBook deprecated warningあり。どちらもbuild失敗ではない。物理共有/購入操作は未検証。</t>
+          <t>Release manifestで広告/AD_ID削除指定の対象なしwarning、MenuBook deprecated warningあり。どちらもbuild失敗ではない。connectedDebugAndroidTest、物理共有、購入操作は未検証。</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PASS local retest。connectedDebugAndroidTestは実機データ保護のため未実施。</t>
+          <t>PASS local retest。connectedDebugAndroidTestは実機データ保護のため未実施。物理共有/購入操作は各ユーザーストーリー側で別ゲートとして追跡。</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>connectedDebugAndroidTestは承認なし実行しない</t>
+          <t>connectedDebugAndroidTestは承認なし実行しない。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-06-29 00:39:51 +0900</t>
+          <t>2026-06-29 01:52:52 +0900</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>web/invite-link/privacy/index.html; web/invite-link/account-deletion/index.html; web/invite-link/.well-known/assetlinks.json; web/invite-link/.well-known/apple-app-site-association; docs/release/final-submission-checklist.md</t>
+          <t>web/invite-link/privacy/index.html; web/invite-link/account-deletion/index.html; web/invite-link/.well-known/assetlinks.json; web/invite-link/.well-known/apple-app-site-association; scripts/verify_public_web_release.sh; docs/release/final-submission-checklist.md; docs/release/privacy-data-safety-draft.md; docs/release/store-listing-draft.md</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>docs/release/final-submission-checklist.md evidence; future: curl live URLs and JSON parse; store console values確認</t>
+          <t>scripts/verify_public_web_release.sh; docs/release/final-submission-checklist.md evidence; future: store console values確認</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5356,27 +5356,27 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>DOCUMENTED_PASS_WITH_FINAL_SHA_GAP</t>
+          <t>PARTIAL_PUBLIC_PRIVACY_STALE_WITH_FINAL_SHA_GAP</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PASS(documented): final-submission-checklistに2026-06-27 live URL 200/JSON parse証跡あり。Current turnではlive curl未再実行。</t>
+          <t>PARTIAL: 2026-06-29 live curlで privacy/account-deletion はHTTP 200、assetlinks.json/AASA はJSON parse成功。assetlinksは jp.miyamibu.urlalbum、AASAは 8R3B5675ZJ.com.mibu.codebridge.ios を含む。</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Play App Signing final SHA-256はNEEDS_USER_ACTION。今回ターンでは外部live URL再検証未実施。</t>
+          <t>BLOCKED_PUBLIC_DEPLOY_STALE: live privacy pageが「本物の課金も行いません」と表示し、repo sourceのStandard / Proサブスクリプション記述と不一致。Play App Signing final SHA-256もNEEDS_USER_ACTION。</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>修正なし: 台帳追跡行として追加。</t>
+          <t>FIXED_DOCS_LOCAL: final-submission-checklist、privacy-data-safety-draft、store-listing-draftを公開privacy staleとして更新。未修正: public privacy pageの再デプロイとfinal Play SHA-256差し替えが必要。</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>再テスト未実施: final SHA確定後にcurl/JSON parse/端末リンク確認が必要。</t>
+          <t>FAIL expected-current: scripts/verify_public_web_release.sh はHTTP/JSON/ID確認をPASSしつつ、privacyのStandard / Pro、Google Play Billing、StoreKit不足と stale no-real-billing文言2件を検出して5 issueで終了。再デプロイ後に同スクリプトを再実行する。</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>公開/ストア運用はコード機能ではないが、アプリ機能の到達性とストア審査に直結するためESとして追跡。</t>
+          <t>2026-06-29 live privacy staleを検出。repo source web/invite-link/privacy/index.html は課金あり文言に更新済みだが、miyamibu.xyz は古いno-real-billing文言を返す。privacy-data-safety-draft/store-listing-draftにも反映済み。scripts/verify_public_web_release.shで再検証可能。</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>2026-06-29 02:08:03 +0900</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UrlSaverRoot.kt; strings.xml; AdsConfig.kt; AdsManager.kt; BannerAdSlot.kt; AdsConfigTest.kt; docs/release/final-submission-checklist.md; ios/URLSaveriOS/PrivacyInfo.xcprivacy; ios/URLSaverShareExtension/PrivacyInfo.xcprivacy</t>
+          <t>UrlSaverRoot.kt; strings.xml; AdsConfig.kt; AdsManager.kt; BannerAdSlot.kt; AdsConfigTest.kt; scripts/verify_public_web_release.sh; docs/release/final-submission-checklist.md; docs/release/privacy-data-safety-draft.md; docs/release/store-listing-draft.md; ios/URLSaveriOS/PrivacyInfo.xcprivacy; ios/URLSaverShareExtension/PrivacyInfo.xcprivacy</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Android AdsConfigTest; source inspection for privacy dialog; release checklist review; future physical UI privacy dialog確認。</t>
+          <t>Android AdsConfigTest; source inspection for privacy dialog; scripts/verify_public_web_release.sh; release checklist review; future physical UI privacy dialog確認。</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5744,27 +5744,27 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_AND_PUBLIC_PRIVACY_GAP</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew testDebugUnitTest --tests AdsConfigTest 成功。Source inspectionでprivacy_dialog stringsとUrlSaverRoot AlertDialogを確認。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS: ./gradlew assembleDebug 成功。Source inspectionでprivacy_dialog stringsとUrlSaverRoot AlertDialogを確認。</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>物理端末でのプライバシーダイアログ表示とPlay Console最終申告一致は未検証。</t>
+          <t>物理端末でのプライバシーダイアログ表示とPlay Console最終申告一致は未検証。2026-06-29時点のlive privacy pageは課金なし文言のままで、repo source/Standard-Pro課金復元と不一致。修正前のAndroidアプリ内privacy dialogも共有タグクラウド、問い合わせ、Standard/Pro購入を説明していなかった。</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>修正なし: 台帳未記載の既存ユーザー/ストア影響機能として追加。</t>
+          <t>PARTIAL_FIXED_LOCAL: Androidアプリ内privacy dialogを、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ送信、Standard/Pro Google Play Billing、広告/分析/クラッシュ収集なしの文言へ更新。final-submission-checklist/privacy-data-safety-draft/store-listing-draftにpublic privacy staleを反映。未修正: public privacy page再デプロイ、store console最終申告一致、物理UI表示確認。</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>未実施: store申告最終確認が必要。</t>
+          <t>PASS local: ./gradlew assembleDebug 成功。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。NOTE: 最初の jp.mimac.urlsaver.AdsConfigTest 指定はテストフィルタ不一致で失敗し、正しい完全修飾名で再実行済み。FAIL expected-current: scripts/verify_public_web_release.sh がlive privacy課金文言staleを5 issueで検出。</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ES-006は公開Web/リンク。これはAndroidアプリ内表示と広告ガード。 targeted unit pass 2026-06-29. iOS privacy manifests included in release source review.</t>
+          <t>ES-006は公開Web/リンク。これはAndroidアプリ内表示と広告ガード。 Android app privacy dialog source updated 2026-06-29. iOS privacy manifests included in release source review; iOS同等のアプリ内privacy dialogは未確認。public privacy staleをUS-040にも連動記録し、release privacy/store docsとverify_public_web_release.shへ反映。</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-06-29 01:00:20 +0900</t>
+          <t>2026-06-29 02:11:30 +0900</t>
         </is>
       </c>
     </row>
@@ -5846,22 +5846,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew testDebugUnitTest --tests MigrationDedupTest.migration_8_9_preservesExistingData_andCreatesUserLabels 成功。DAO/Entity/Repository/APIはsource確認、UI入口は未確認。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests MigrationDedupTest.migration_8_9_preservesExistingData_andCreatesUserLabels 成功。DAO/Entity/Repository/APIはsource確認。追加監査でAndroid UI/testsにUserLabel操作参照なし、iOSに同等UserLabelモデル/APIなし、git履歴上もdata foundation由来で旧UI削除ではないことを確認。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>機能基礎はあるが現行ユーザーUI未実装。iOS側に同等UserLabelモデルは未確認。</t>
+          <t>機能基礎はあるが現行ユーザーUI未実装。iOS側にも同等UserLabelモデル/API/UIなし。旧UI復元対象ではなく、公開ユーザー機能にするなら新規仕様判断が必要。</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>未修正: 仕様化するならAndroid UI追加とiOS parity設計が必要。現状は未実装基盤として記録。</t>
+          <t>未修正: DESIGN.mdでadvanced taggingは明示承認なしに広げない方針。既存のローカルタグ/コレクションと重複するため、現状は未公開基盤として維持。</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>未実施: UI実装後に再テスト。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MigrationDedupTest.migration_8_9_preservesExistingData_andCreatesUserLabels 成功。PASS audit: Android/iOS UI入口なしをrgで再確認。UI実装は未実施。</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ユーザー依頼の「基礎は作ったが実装していないもの」候補として追跡。 targeted unit pass 2026-06-29.</t>
+          <t>ユーザー依頼の「基礎は作ったが実装していないもの」候補として追跡。2026-06-29追加監査で旧実装UIの削除ではなくfoundation-onlyと判断。</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-06-29 00:50:01 +0900</t>
+          <t>2026-06-29 01:49:20 +0900</t>
         </is>
       </c>
     </row>
@@ -5987,8 +5987,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6006,7 +6006,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DOCUMENTED_PASS_WITH_FINAL_SHA_GAP</t>
+          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6018,24 +6018,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
+          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
+          <t>LOCAL_PASS_WITH_CONNECTED_TEST_GAP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_AND_PUBLIC_PRIVACY_GAP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PASS: Androidローカル検証成功、release buildも成功、実機共有系は未検証</t>
+          <t>PARTIAL_PUBLIC_PRIVACY_STALE_WITH_FINAL_SHA_GAP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6240,6 +6240,142 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>remaining_gate</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>story_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>physical_Android</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-026,US-027,US-028,US-029,US-030,ES-002,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039,US-040</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>physical_iPhone</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-026,US-027,US-028,US-029,US-030,ES-003,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>supabase_or_auth_live</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US-016,US-018,US-019,US-023,US-024,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-031,US-032,US-033,AS-007,US-036,AS-008,US-039</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>store_or_public_console</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US-033,US-036,ES-006,US-040</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>public_privacy_deploy_stale</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ES-006,US-040</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>resend_live</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AS-008,AS-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>connected_android_instrumentation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ES-002</t>
         </is>
       </c>
     </row>

--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -449,7 +449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -608,7 +608,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestは実機データ保護のため未実行。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>US-034/US-035/US-036/AS-008/ES-006を追加。 US-037/US-038/US-039/US-040/TS-001を追加。 AS-009を追加し、US-039に公開reset-passwordページを追記。 US-006のiOS表示モード永続化ギャップを修正し、US-012にiOS BGTaskScheduler証跡を追記。 US-025/US-023/US-024のexport/entitlement近接テスト結果を更新。US-040にiOS PrivacyInfo証跡を補強。 iOS SharedTagCloud display_name migrationの冪等性を修正し、US-018/US-019/ES-003へ反映。2026-06-29にXLSXフィルタ範囲、summaryステータス集計、残ゲート集計を実データへ修正。Public privacy stale検出後にsummary再生成。 Release privacy/store docsのpublic privacy stale反映後にsummary再生成。 Public web verifier追加後にsummary再生成。 Android privacy dialog文言更新後にsummary再生成。</t>
+          <t>US-034/US-035/US-036/AS-008/ES-006を追加。 US-037/US-038/US-039/US-040/TS-001を追加。 AS-009を追加し、US-039に公開reset-passwordページを追記。 US-006のiOS表示モード永続化ギャップを修正し、US-012にiOS BGTaskScheduler証跡を追記。 US-025/US-023/US-024のexport/entitlement近接テスト結果を更新。US-040にiOS PrivacyInfo証跡を補強。 iOS SharedTagCloud display_name migrationの冪等性を修正し、US-018/US-019/ES-003へ反映。2026-06-29にXLSXフィルタ範囲、summaryステータス集計、残ゲート集計を実データへ修正。Public privacy stale検出後にsummary再生成。 Release privacy/store docsのpublic privacy stale反映後にsummary再生成。 Public web verifier追加後にsummary再生成。 Android privacy dialog文言更新後にsummary再生成。 iOS PrivacyInfoSheet反映後にsummary再生成。 connectedDebugAndroidTest AVD PASS反映後にsummary再生成。</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-06-29 02:11:30 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -4192,17 +4192,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_CONNECTED_TEST_GAP</t>
+          <t>PASS_WITH_PHYSICAL_OPERATION_GAP</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PASS: 2026-06-29 ./gradlew assembleDebug testDebugUnitTest lintDebug 成功。PASS: ./gradlew assembleRelease 成功。対象追加確認として SharedTagAuthViewModelTest/TagRepositoryTest 単独実行も成功。</t>
+          <t>PASS: 2026-06-29 ./gradlew assembleDebug testDebugUnitTest lintDebug 成功。PASS: ./gradlew assembleRelease 成功。PASS: urlsaverParityApi35 AVDで connectedDebugAndroidTest 成功（17 tests、SharedTagCloudLiveDeviceTest 1件はlive Supabase設定なしでSKIP）。対象追加確認として SharedTagAuthViewModelTest/TagRepositoryTest 単独実行も成功。</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Release manifestで広告/AD_ID削除指定の対象なしwarning、MenuBook deprecated warningあり。どちらもbuild失敗ではない。connectedDebugAndroidTest、物理共有、購入操作は未検証。</t>
+          <t>Release manifestで広告/AD_ID削除指定の対象なしwarning、MenuBook deprecated warningあり。どちらもbuild失敗ではない。物理共有、購入操作は未検証。SharedTagCloudLiveDeviceTestはlive Supabase設定なしでSKIPし、Supabase/Auth live側に残す。</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PASS local retest。connectedDebugAndroidTestは実機データ保護のため未実施。物理共有/購入操作は各ユーザーストーリー側で別ゲートとして追跡。</t>
+          <t>PASS local + connected retest。connectedDebugAndroidTestはテスト専用AVD urlsaverParityApi35で成功。物理共有/購入操作は各ユーザーストーリー側で別ゲートとして追跡。</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>connectedDebugAndroidTestは承認なし実行しない。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。</t>
+          <t>connectedDebugAndroidTestは通常端末では承認なし実行しない。テスト専用AVDでは2026-06-29に実行済み。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。 2026-06-29 connectedDebugAndroidTestをテスト専用AVDで実行し成功。</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-06-29 01:52:52 +0900</t>
+          <t>2026-06-29 06:32:51 +0900</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_LOCAL_DB_GAP</t>
+          <t>PASS_LINKED_DB_WITH_ADVISORY_WARNINGS</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Supabase local DB/RLS live validationは未実施。ローカルPostgres 127.0.0.1:55422 が接続拒否。linked/prod DBは秘密値と明示承認なしで未接続。</t>
+          <t>linked DB schema/RPC validationは実施済み。残りはDB advisorsの既存WARN確認と、ローカルDB起動なしによりlocal lintが未実施である点。</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>APPLIED_LINKED_DB: 未適用だったshared group/profile、promo delivery inbox、contact support request、store purchase verification系schemaをlinked DBへ適用。PUBLIC実行権限が残っていたSECURITY DEFINER RPCをhardenし、anon実行は招待preview系だけに限定。</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>PASS Edge Function type check。DB lint/RLS/migration live testはローカルDB起動またはlinked DB承認後に再実行。</t>
+          <t>PASS linked DB: db query --linkedで主要table/RPC存在確認成功。PASS functions: contact-support/contact-support-resend-webhook/verify-store-purchase deploy成功。PASS advisors improvement: anon executable SECURITY DEFINERはpreview系3件のみ。Remaining advisors WARN: function search_path、signed-in SECURITY DEFINER、RLS initplan、multiple policies、leaked password protection。</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t/>
+          <t>linked project xocumgxbylmpoobfqows。db pushはremote migration history driftにより不可だったため、必要migrationをdb query --linkedで個別適用。</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-06-29 00:39:51 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4784,17 +4784,17 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Google Play sandbox purchase、StoreKit sandbox purchase、Edge Function deploy、migration適用、RTDN/App Store Server Notificationsは未検証。Supabase local db lintはローカルDB未起動で失敗。</t>
+          <t>Google Play sandbox purchase、StoreKit sandbox purchase、RTDN/App Store Server Notificationsは未検証。linked DB schemaとverify-store-purchase Function deployは確認済み。</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>実装済み: Store purchase verification table/migrationとEdge Functionを追加し、client purchase serviceから呼ぶ契約を整備。</t>
+          <t>実装済み: Store purchase verification table/migrationとEdge Functionを追加し、client purchase serviceから呼ぶ契約を整備。本番Function version 13へdeploy済み。</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>PASS local/type/build retest。外部ストアsandboxとSupabase deployは未実施。</t>
+          <t>PASS local/type/build retest。PASS linked DB: public.store_purchase_verifications と user_entitlement_grants 制約確認。PASS Function deploy/list: verify-store-purchase ACTIVE version 13。未実施: 外部ストアsandbox購入と通知。</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-06-29 00:39:51 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEPLOY_GAP</t>
+          <t>PASS_LINKED_DB_WITH_STORE_WEBHOOK_GAP</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4881,17 +4881,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>本番/linked DB migration適用、RLS live verification、失効webhookは未検証。ローカルDB未起動でSupabase lint不可。</t>
+          <t>ストア実通知、sandbox購入、管理画面からの実監査操作は未検証。linked DB migration/RLS/schema validationは実施済み。</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>実装済み: 検証履歴table、RLS、transaction unique index、grant作成処理を追加。</t>
+          <t>APPLIED_LINKED_DB: store purchase verification table/RLS/index、transaction unique index、grant作成処理をlinked DBへ適用。本番verify-store-purchase Functionもdeploy済み。</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>PASS local type/source retest。DB live validationは未実施。</t>
+          <t>PASS linked DB: store_purchase_verifications columns/RLS policy確認。PASS Function: verify-store-purchase no-session request is rejected with 401. Remaining: Google Play/App Store sandbox実取引と通知イベント。</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-06-29 00:39:51 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_LIVE_GAP</t>
+          <t>LINKED_RPC_PASS_WITH_CHATGPT_CONSUMPTION_GAP</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Supabase live RPC実行、ChatGPT側実消費、物理端末toggle操作は未検証。</t>
+          <t>ChatGPT側実消費と物理端末toggle操作は未検証。linked DB上のpersonal link table/RPC存在は確認済み。</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>再テスト未実施: live Supabase環境が必要。</t>
+          <t>PASS linked DB: personal_link_sync_settings/personal_saved_links と set_personal_link_chatgpt_sync/apply_personal_link_ops RPC存在確認。Remaining: ChatGPT側実消費、サインイン済みユーザーによるtoggle実行。</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
+          <t>PASS_RESEND_SENT_WITH_DELIVERY_EVENT_GAP</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5269,17 +5269,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Resend live送信/配信/バウンスwebhook、Supabase DB live row確認は未検証。</t>
+          <t>Resend delivered/bounced/complained等の実webhookイベント反映は未確認。問い合わせ送信、Resend accepted相当のemail.sent、DB監査row、message id保存は確認済み。</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>修正なし: ローカル型/単体テスト上のエラー未検出。</t>
+          <t>FIXED_LIVE: contact-support-resend-webhookを本番deploy。contact-support Functionをpublic.contact_support_requests契約へ修正し、問い合わせ本文/メール/名前の原文を監査DBへ保存しない形へ変更。Resend message idを保存し、webhookが後続更新できる状態にした。</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>PASS local/type retest。live deliveryは未実施。</t>
+          <t>PASS live send: contact-support POST returned 202 accepted requestId=56d99d04-bbea-4b48-be13-eef62cb1f8d4。PASS DB: delivery_status=sent, delivery_provider=resend, has_message_id=true, delivery_event_type=email.sent。PASS webhook smoke: unsigned webhook returns 401 Invalid webhook secret。15秒後の確認ではdelivered webhook未反映。</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>US-022のユーザー問い合わせ導線に対応する管理/配信監査行。</t>
+          <t>Resend配送完了truthはResend側webhook実イベントまたはResend API照会が必要。</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>PARTIAL_PUBLIC_PRIVACY_STALE_WITH_FINAL_SHA_GAP</t>
+          <t>PASS_PUBLIC_WEB_WITH_FINAL_SHA_GAP</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>BLOCKED_PUBLIC_DEPLOY_STALE: live privacy pageが「本物の課金も行いません」と表示し、repo sourceのStandard / Proサブスクリプション記述と不一致。Play App Signing final SHA-256もNEEDS_USER_ACTION。</t>
+          <t>Play App Signing final SHA-256はNEEDS_USER_ACTION。公開privacy staleは2026-06-29本番deploy後に解消済み。</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>FIXED_DOCS_LOCAL: final-submission-checklist、privacy-data-safety-draft、store-listing-draftを公開privacy staleとして更新。未修正: public privacy pageの再デプロイとfinal Play SHA-256差し替えが必要。</t>
+          <t>FIXED_PUBLIC_DEPLOY: web/invite-link をVercel project invite-linkへproduction deployし、miyamibu.xyzへalias済み。未修正: final Play SHA-256差し替えはGoogle Play Consoleの外部操作が必要。</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>FAIL expected-current: scripts/verify_public_web_release.sh はHTTP/JSON/ID確認をPASSしつつ、privacyのStandard / Pro、Google Play Billing、StoreKit不足と stale no-real-billing文言2件を検出して5 issueで終了。再デプロイ後に同スクリプトを再実行する。</t>
+          <t>PASS: npx --yes vercel@latest --prod --yes 成功。deployment dpl_8WZa3BBdqQs4f8s8mKcvxzaspVdv / alias https://miyamibu.xyz。PASS: scripts/verify_public_web_release.sh は privacy/account-deletion HTTP 200、assetlinks/AASA ID、Standard / Pro、Google Play Billing、StoreKit、stale no-real-billing文言なしを全て確認。</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-06-29 live privacy staleを検出。repo source web/invite-link/privacy/index.html は課金あり文言に更新済みだが、miyamibu.xyz は古いno-real-billing文言を返す。privacy-data-safety-draft/store-listing-draftにも反映済み。scripts/verify_public_web_release.shで再検証可能。</t>
+          <t>2026-06-29 live privacy staleはproduction deployで解消。残りはPlay Console final SHA-256など外部Console確認のみ。</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2026-06-29 02:08:03 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Android/Store</t>
+          <t>Android/iOS/Store</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UrlSaverRoot.kt; strings.xml; AdsConfig.kt; AdsManager.kt; BannerAdSlot.kt; AdsConfigTest.kt; scripts/verify_public_web_release.sh; docs/release/final-submission-checklist.md; docs/release/privacy-data-safety-draft.md; docs/release/store-listing-draft.md; ios/URLSaveriOS/PrivacyInfo.xcprivacy; ios/URLSaverShareExtension/PrivacyInfo.xcprivacy</t>
+          <t>UrlSaverRoot.kt; strings.xml; AdsConfig.kt; AdsManager.kt; BannerAdSlot.kt; AdsConfigTest.kt; scripts/verify_public_web_release.sh; docs/release/final-submission-checklist.md; docs/release/privacy-data-safety-draft.md; docs/release/store-listing-draft.md; ios/URLSaveriOS/UI/RootView.swift; ios/URLSaveriOS/PrivacyInfo.xcprivacy; ios/URLSaverShareExtension/PrivacyInfo.xcprivacy</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>プライバシーダイアログ文言が表示可能で、ADS_ENABLED/ADS_TRIAL_LAUNCH_ADS_ENABLEDが無効ならSDK初期化、バナー、インタースティシャルが走らない。</t>
+          <t>AndroidのプライバシーダイアログとiOSのデータ取り扱いシートが表示可能で、ADS_ENABLED/ADS_TRIAL_LAUNCH_ADS_ENABLEDが無効ならSDK初期化、バナー、インタースティシャルが走らない。</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Android AdsConfigTest; source inspection for privacy dialog; scripts/verify_public_web_release.sh; release checklist review; future physical UI privacy dialog確認。</t>
+          <t>Android AdsConfigTest; Android source inspection for privacy dialog; iOS source inspection/generic build for PrivacyInfoSheet; scripts/verify_public_web_release.sh; release checklist review; future physical UI privacy dialog/sheet確認。</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5744,27 +5744,27 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_AND_PUBLIC_PRIVACY_GAP</t>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS: ./gradlew assembleDebug 成功。Source inspectionでprivacy_dialog stringsとUrlSaverRoot AlertDialogを確認。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS: ./gradlew assembleDebug 成功。PASS: xcodebuild -quiet -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination generic/platform=iOS Simulator CODE_SIGNING_ALLOWED=NO build 成功。Source inspectionでAndroid privacy_dialog strings/UrlSaverRoot AlertDialogとiOS RootView PrivacyInfoSheet/info.circle入口を確認。</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>物理端末でのプライバシーダイアログ表示とPlay Console最終申告一致は未検証。2026-06-29時点のlive privacy pageは課金なし文言のままで、repo source/Standard-Pro課金復元と不一致。修正前のAndroidアプリ内privacy dialogも共有タグクラウド、問い合わせ、Standard/Pro購入を説明していなかった。</t>
+          <t>物理端末でのAndroidプライバシーダイアログ/iOSデータ取り扱いシート表示とPlay Console/App Store最終申告一致は未検証。修正前のAndroidアプリ内privacy dialogは共有タグクラウド、問い合わせ、Standard/Pro購入を説明していなかった。修正前のiOSはPrivacyInfo.xcprivacyはあったが、アプリ内でユーザーが確認できる同等シートがなかった。live privacy pageの課金なし文言staleは2026-06-29本番deploy後に解消済み。</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PARTIAL_FIXED_LOCAL: Androidアプリ内privacy dialogを、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ送信、Standard/Pro Google Play Billing、広告/分析/クラッシュ収集なしの文言へ更新。final-submission-checklist/privacy-data-safety-draft/store-listing-draftにpublic privacy staleを反映。未修正: public privacy page再デプロイ、store console最終申告一致、物理UI表示確認。</t>
+          <t>PARTIAL_FIXED_LOCAL_AND_PUBLIC: Androidアプリ内privacy dialogを、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ送信、Standard/Pro Google Play Billing、広告/分析/クラッシュ収集なしの文言へ更新。iOSはRootViewにinfo.circle入口とPrivacyInfoSheetを追加し、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ、Standard/Pro StoreKit、広告/分析なしを表示。web/invite-link production deployでpublic privacy staleを解消。未修正: store console最終申告一致、物理UI表示確認。</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>PASS local: ./gradlew assembleDebug 成功。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。NOTE: 最初の jp.mimac.urlsaver.AdsConfigTest 指定はテストフィルタ不一致で失敗し、正しい完全修飾名で再実行済み。FAIL expected-current: scripts/verify_public_web_release.sh がlive privacy課金文言staleを5 issueで検出。</t>
+          <t>PASS local: ./gradlew assembleDebug 成功。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS local: iOS generic simulator build成功。PASS public: scripts/verify_public_web_release.sh 成功。NOTE: 最初の jp.mimac.urlsaver.AdsConfigTest 指定はテストフィルタ不一致で失敗し、正しい完全修飾名で再実行済み。</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5774,17 +5774,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t/>
+          <t>NOT VERIFIED on physical iPhone: データ取り扱いシート表示は実機操作未検証。</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ES-006は公開Web/リンク。これはAndroidアプリ内表示と広告ガード。 Android app privacy dialog source updated 2026-06-29. iOS privacy manifests included in release source review; iOS同等のアプリ内privacy dialogは未確認。public privacy staleをUS-040にも連動記録し、release privacy/store docsとverify_public_web_release.shへ反映。</t>
+          <t>ES-006は公開Web/リンク。これはAndroid/iOSアプリ内表示と広告ガード。 Android app privacy dialog source updated 2026-06-29. iOS PrivacyInfoSheet/info.circle app UI added 2026-06-29 and generic build passed. public privacy staleはproduction deployで解消。</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-06-29 02:11:30 +0900</t>
+          <t>2026-06-29 07:25:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S57"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6018,103 +6020,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
+          <t>LINKED_RPC_PASS_WITH_CHATGPT_CONSUMPTION_GAP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_CONNECTED_TEST_GAP</t>
+          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEPLOY_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
+          <t>LOCAL_PASS_WITH_EXTERNAL_STORE_GAP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_EXTERNAL_STORE_GAP</t>
+          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_AND_PUBLIC_PRIVACY_GAP</t>
+          <t>LOCAL_PASS_WITH_UI_DEVICE_GAP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6126,7 +6128,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_UI_DEVICE_GAP</t>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6138,55 +6140,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_LIVE_GAP</t>
+          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
+          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
+          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
+          <t>PASS: Web管理画面 typecheck/build 成功</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
+          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6198,7 +6200,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_LOCAL_DB_GAP</t>
+          <t>PASS_LINKED_DB_WITH_ADVISORY_WARNINGS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6210,7 +6212,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PARTIAL_PUBLIC_PRIVACY_STALE_WITH_FINAL_SHA_GAP</t>
+          <t>PASS_LINKED_DB_WITH_STORE_WEBHOOK_GAP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6222,7 +6224,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PASS: Web管理画面 typecheck/build 成功</t>
+          <t>PASS_PUBLIC_WEB_WITH_FINAL_SHA_GAP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6234,7 +6236,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
+          <t>PASS_RESEND_SENT_WITH_DELIVERY_EVENT_GAP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6243,105 +6245,101 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>remaining_gate</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>story_ids</t>
-        </is>
-      </c>
-    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PASS_WITH_PHYSICAL_OPERATION_GAP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>physical_Android</t>
+          <t>remaining_gate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>count</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-026,US-027,US-028,US-029,US-030,ES-002,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039,US-040</t>
+          <t>story_ids</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>physical_iPhone</t>
+          <t>physical_Android</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-026,US-027,US-028,US-029,US-030,ES-003,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039</t>
+          <t>US-001,US-002,US-003,US-004,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-028,US-029,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039,US-040</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>supabase_or_auth_live</t>
+          <t>physical_iPhone</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US-016,US-018,US-019,US-023,US-024,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-031,US-032,US-033,AS-007,US-036,AS-008,US-039</t>
+          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-026,US-027,US-028,US-029,US-030,ES-003,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039,US-040</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>store_or_public_console</t>
+          <t>supabase_or_auth_live</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US-033,US-036,ES-006,US-040</t>
+          <t>US-016,US-018,US-019,US-023,US-024,US-031,US-032,US-039</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>public_privacy_deploy_stale</t>
+          <t>store_or_public_console</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ES-006,US-040</t>
+          <t>US-033,AS-007,ES-006,US-039,US-040,TS-001</t>
         </is>
       </c>
     </row>
@@ -6370,15 +6368,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ES-002</t>
+          <t/>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B30"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -1,63 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="canonical_story_status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="stories" sheetId="1" r:id="rId1"/>
+    <sheet name="summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'canonical_story_status'!$A$1:$S$57</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="1">
     <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9F2D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="1">
@@ -72,96 +33,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -208,250 +82,24 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
+      <a:fillStyleLst/>
+      <a:lnStyleLst/>
+      <a:effectStyleLst/>
+      <a:bgFillStyleLst/>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -603,7 +251,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で手動貼り付け保存PASS、重複時挙動は未検証</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -628,22 +276,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 一時URL https://example.com/rinbam-device-test-20260629-1214 を入力欄から保存し、一覧に example.com / 保存 12:15 / 自動取得できません が表示。証跡: artifacts/device-verification/2026-06-29/android-us001-add-form-ready-save.png, android-us001-after-save-final.png。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 一時URL https://example.com/rinbam-iphone-device-test-20260629-1226 を入力欄から保存し、一覧に example.com / 保存 12:27 / 自動取得できません が表示。証跡: iphone-us001-add-form-filled.png, iphone-us001-after-save-final.png。</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>重複保存の実機挙動は次ループで別URL表記差分を使って確認する。既存ユーザーデータは削除/リセットしていない。</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:34:00 +0900</t>
         </is>
       </c>
     </row>
@@ -700,7 +348,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS_WITH_IPHONE_SHARE_EXTENSION_ERROR: Android実機の単一URL共有保存はPASS。iPhone実機は共有シートにりんばむ表示まで確認したが、選択後の保存引き継ぎが失敗。</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -710,37 +358,37 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>iPhone physical share extension: Safari共有シートで「りんばむ」を選択後、「アプリへ引き継げなかったため保存できませんでした」と表示。ShareViewControllerのhost app fallback/openHostApp経路または実機URL引き継ぎに問題の可能性。CoreSimulator/XCTest不整合は別件として継続。</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>未修正: US-002 iPhone共有拡張の保存引き継ぎ失敗を新規実機エラーとして記録。原因候補はShare Extensionからurlsaver://saveをopenするfallback経路、App Group repository初期化、または実機URL scheme引き継ぎ。</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>Android physical retest PASS: ACTION_SEND text/plainで新規URLをShareReceiverActivityへ送り、「保存先タグ」シート -&gt; 「保存」 -&gt; 「保存しました」を確認。iPhone physical retest FAIL: Safari共有シートで「りんばむ」セルは表示されるが、選択後に保存できず失敗文言。connected Android instrumentationは2026-06-29 urlsaverParityApi35 AVDでPASS済み。</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum 1.0.13/13): ACTION_SEND text/plainで https://example.com/rinbam-us002-20260629125754 を共有。保存先タグシート、保存ボタン、保存後「保存しました」を確認。完了後ホームにexample.comカードが追加。証跡: android-us002-share-sheet.png/xml, android-us002-after-save.png/xml, android-us002-home-after-back.png/xml。</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>FAIL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): Safariで https://example.com/rinbam-us002-ios-20260629130000 を開き、共有メニュー -&gt; 共有シートで「りんばむ」セルを確認。XCUIElementTypeCell label=りんばむ をクリック後、「アプリへ引き継げなかったため保存できませんでした」と表示。証跡: iphone-us002-safari.png/xml, iphone-us002-safari-more-menu.png/xml, iphone-us002-share-sheet.png/xml, iphone-us002-share-sheet-scroll-3.png/xml, iphone-us002-after-rinbam-element-click.png/xml。</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>iPhone共有シート上の表示名は「りんばむ」で旧名ではない。US-002完全PASSにはiPhone Share Extension保存成功または直接保存経路の修正と再テストが必要。</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 13:06:00 +0900</t>
         </is>
       </c>
     </row>
@@ -797,7 +445,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS_WITH_IPHONE_INPUT_GAP: Android実機の複数URL共有保存はPASS。iPhone実機は複数URL共有入力を生成できず、実保存未検証。</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,37 +455,37 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>iPhone physical US-003 input gap: Safari通常共有は単一URLのみ。Web Share APIで複数URLテキスト共有を作る一時ページを試したが、物理iPhone Safari上で navigator.share is not a function となり共有シートを生成できなかった。US-002では共有シートの「りんばむ」選択後に保存引き継ぎ失敗も確認済み。</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>未修正: US-003 iPhone複数URL共有の実機入力手段と、US-002で見つかったShare Extension保存引き継ぎ失敗の修正が必要。Android側の今回検証ではロジスティカル/UXエラーなし。</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>Android physical retest PASS: ACTION_SEND_MULTIPLE + 改行区切りEXTRA_TEXTで新規2件をShareReceiverActivityへ送り、「保存先タグ」シート -&gt; 「保存」 -&gt; 「2件を処理しました（新規2 / 既存0 / 復元0 / 失敗0）」を確認。iPhone physical retest NOT VERIFIED for multi URL save: Web Share代替はnavigator.share未対応で共有シート生成不可。</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum 1.0.13/13): ACTION_SEND_MULTIPLE text/plainで https://example.com/rinbam-us003-a2-202606291309 と https://example.com/rinbam-us003-b2-202606291309 を改行区切りEXTRA_TEXTとして共有。保存先タグシート、保存ボタン、保存後「2件を処理しました（新規2 / 既存0 / 復元0 / 失敗0）」を確認。証跡: android-us003-share-sheet-retry.png/xml, android-us003-after-save.png/xml。</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>NOT VERIFIED on physical iPhone for US-003 multi URL save (00008101-00066D96340A001E via Appium/WDA): Safari通常共有は単一URLのみのためUS-003条件を満たさず。ローカル一時ページからWeb Share APIで複数URLテキスト共有を試したが、物理iPhone Safariで「navigator.share is not a function」と表示され共有シートを生成できなかった。証跡: iphone-us003-webshare-start.png/xml, iphone-us003-webshare-after-button.png/xml, us003-webshare/index.html。</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>Android投入時、adb --esa配列形式では実機am経由でURL抽出できず「URLが見つかりませんでした」になったため、テストで許容されるACTION_SEND_MULTIPLE + 改行区切りEXTRA_TEXTで再検証しPASS。iPhone US-003完全確認にはNotes/Files等から複数URLテキストを共有する実機手段、またはUS-002 Share Extension引き継ぎ修正後の再テストが必要。</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 13:11:27 +0900</t>
         </is>
       </c>
     </row>
@@ -894,47 +542,47 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS_WITH_NORMALIZATION_AND_IPHONE_UX_GAP: 両実機で同一URL重複は確認済み。表記違い正規化とiPhone通知導線は未完了。</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。 / PASS device partial: 2026-06-29 両実機で同一URLの重複保存を追加確認。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>PARTIAL_DEVICE_GAP: Android/iPhone実機で同一URL重複判定は確認。表記違いURLの正規化重複は未検証。iPhone手動追加の重複保存後、コード上は「このURLはすでに保存済みです」+「見る」通知を5秒表示する設計だが、Appium証跡では保存後ホームに戻り通知が見えなかった。</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>未修正: 今回は検証結果の記録のみ。iPhone重複通知/見る導線はUX差分候補として次ループで原因特定と修正対象判定が必要。</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。 / RETEST NEEDED: 表記違い正規化、iPhone重複通知「見る」、修正後の両実機再確認。</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639): 既存URL https://example.com/rinbam-device-test-20260629-1214 をACTION_SENDでShareReceiverActivityへ渡し、保存押下後に「このURLはすでに保存されています」表示を確認。証跡: artifacts/device-verification/2026-06-29/android-us004-share-duplicate-before.png/xml, android-us004-share-duplicate-after.png/xml, android-us004-share-duplicate-result.png/xml。表記違い正規化重複は未検証。</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL_PASS_WITH_UX_GAP(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8ea12d85-7105-48c3-ac0c-4b2b77650cf2): 既存URL https://example.com/rinbam-iphone-device-test-20260629-1226 を手動追加し、保存後にホームへ戻り既存1件表示のまま追加重複は見えなかった。証跡: iphone-us004-duplicate-before.png/xml, iphone-us004-duplicate-add-form.png/xml, iphone-us004-duplicate-filled.png/xml, iphone-us004-duplicate-result-after-save.png/xml。期待される「このURLはすでに保存済みです」+「見る」通知は証跡上未確認。表記違い正規化重複は未検証。</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t/>
+          <t>US-004は完全PASSではない。同一URL重複は両実機で進捗あり。残: 表記違いURLのnormalizedUrl重複、Android手動追加側の「見る」導線、iPhone通知/見る導線の表示確認または修正。</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:46:10 +0900</t>
         </is>
       </c>
     </row>
@@ -991,7 +639,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android実機PASS、iPhoneホーム/フィルター表示PASS、保存URL絞り込み操作未実施</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1021,17 +669,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): アプリ名「りんばむ」、ホーム表示、サービス/タグ系フィルタチップ、下部5アクションをXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml。保存済みURLを用いた絞り込み操作は未実施。</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t/>
+          <t>iPhone Appium/WDAが復旧しホーム表示証跡を取得。データ作成を伴うURL一覧/絞り込み操作は次ループで非破壊手順を設計して確認する。</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 11:48:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1088,7 +736,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で表示モード切替PASS、再起動後保持は未検証</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1113,22 +761,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 表示モードボタンをタップし content-desc が「画像つき表示へ切り替える」へ変化。証跡: artifacts/device-verification/2026-06-29/android-pixel9a-display-toggle-after.png, android-pixel9a-display-toggle-after.xml。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): 表示モードボタンをタップし、XMLで「画像なし表示へ切り替える」を確認。証跡: artifacts/device-verification/2026-06-29/iphone-ui-loop-display-toggle-after.png, iphone-ui-loop-display-toggle-after.xml。</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>iOS display mode persistence fixed 2026-06-29.</t>
+          <t>物理端末で切替自体は確認済み。再起動後保持、Archive/Tag detail反映は次ループで確認が必要。</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-06-29 00:57:14 +0900</t>
+          <t>2026-06-29 12:03:48 +0900</t>
         </is>
       </c>
     </row>
@@ -1185,7 +833,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で詳細からアーカイブ/復元PASS、スワイプ操作とUndo実行は未検証</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1210,22 +858,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): 詳細のアーカイブでactive一覧から消え、アーカイブ詳細でアーカイブ解除、active一覧へ復元。Undo表示は確認したが実行成功は未証明。証跡: android-us007-archive-after-tap.png, android-us007-archive-detail-open.png, android-us007-unarchive-after-tap.png。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 詳細のアーカイブでactive一覧から消え、アーカイブ一覧に移動、アーカイブ済み詳細で削除無効/アーカイブ解除、active一覧へ復元。スワイプ/Undo実行は未証明。証跡: iphone-us007-archive-after-tap.png, iphone-us007-archive-list.png, iphone-us007-archive-detail.png, iphone-us007-unarchive-home.png。</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t/>
+          <t>この行の受入条件に含まれるスワイプ操作とUndo復帰は未完了。次ループで一時データを使い、猶予中Undoをタイミング込みで確認する。</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:34:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1282,47 +930,47 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PHYSICAL_PASS_WITH_TEMP_DATA: 両実機で一時URLを使い、削除確認、5秒Undo通知、Undo後の一覧復帰を確認。</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: 既存のローカル/ビルド検証に加え、2026-06-29に両実機で一時URLを使った削除猶予/Undo導線を確認。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>過去試行ではAndroidの座標タップが5秒Undoに間に合わず復元未証明だったが、今回bounds由来のUndo中心タップで復元を確認。iPhoneもAppium/WDA連続操作で復元確認。製品ロジック上の不具合は今回未検出。</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>修正対象なし: 実機再検証で削除猶予/Undoの期待動作を確認。</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>PASS physical retest: Android Pixel 9a と iPhone 12 で削除確認文言、削除後通知「削除しました」「元に戻す」、Undo後のカード復帰を確認。</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 一時カード(保存 14:55/14:56系)で詳細削除確認「このURLは削除待ちに移動します。5秒以内なら元に戻せます。」、削除後Snackbar「削除しました」「元に戻す」、Undo後に一覧へ「保存 14:56」「保存 14:55」が復帰/残存することを確認。証跡: artifacts/device-verification/2026-06-29/us008/android-us008-delete-dialog-retry.*, android-us008-after-delete-retry.*, android-us008-after-undo-retry.*</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E, Appium/WDA, com.mibu.codebridge.ios): 一時URL https://example.com/rinbam-us008-iphone-202606291501 を追加し、詳細削除確認、削除後通知「削除しました」「元に戻す」、Undo後に「保存 15:03」のカードが一覧復帰することを確認。証跡: artifacts/device-verification/2026-06-29/us008/iphone-us008-temp-*.xml/png</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>通常端末の既存データは消さない</t>
+          <t>通常端末の既存データは消さず、一時テストURLのみ使用。iPhoneはAppium/WDA、AndroidはADB/uiautomator/screencapで証跡取得。</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 15:07:47 +0900</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1027,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で詳細遷移と外部で開く導線表示PASS、外部ブラウザ起動は未実行</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1404,22 +1052,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): 一覧カードタップで詳細へ遷移し、開く/コピー/アーカイブ/削除/メモ編集/metadata失敗表示を確認。外部ブラウザ起動は未実行。証跡: android-us009-detail-open.png。</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 一覧カードタップで詳細へ遷移し、開く/コピー/アーカイブ/削除/メモ編集/metadata失敗表示を確認。外部ブラウザ起動は未実行。証跡: iphone-us009-detail-open.png。</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t/>
+          <t>外部ブラウザ起動は別アプリ遷移を伴うため未実行。次ループで戻り動作も含めて確認する。</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:34:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1124,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でタイトル編集保存PASS、Undo実行は未検証</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1501,22 +1149,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): タイトル編集UIを開き Rinbam Device Title を保存、詳細に反映。Undo表示は確認したが実行は未証明。証跡: android-us010-title-edit-open.png, android-us010-title-saved.png。</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): タイトル編集UIを開き Rinbam iPhone Title を保存、詳細に反映。Undo通知は取得時点で確認できず、Undo実行は未証明。証跡: iphone-us010-title-edit-open.png, iphone-us010-title-saved.png。</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t/>
+          <t>タイトルUndoは次ループで保存直後に通知捕捉と実行確認を行う。</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:34:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1221,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PASS: Android/iPhone実機でメモ編集保存PASS</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1598,22 +1246,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): メモ編集UIを開き Android device memo 1216 を保存、詳細に反映。証跡: android-us011-memo-edit-open.png, android-us011-memo-saved.png。</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): メモ編集ダイアログを開き iPhone device memo 1228 を保存、詳細に反映。証跡: iphone-us011-memo-edit-open.png, iphone-us011-memo-saved.png。</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t/>
+          <t>一時URLのメモ保存のみ確認。既存ユーザーデータは削除/リセットしていない。</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:34:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1318,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でmetadata失敗状態表示PASS、成功取得は未検証</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1695,22 +1343,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): example.com 一時URLで一覧/詳細に 自動取得できません と HTTP_404 系説明、再取得導線表示を確認。成功取得は未検証。証跡: android-us001-after-save-final.png, android-us009-detail-open.png。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): example.com 一時URLで一覧/詳細に 自動取得できません、ページが見つかりませんでした (HTTP_404)、再取得導線表示を確認。成功取得は未検証。証跡: iphone-us001-after-save-final.png, iphone-us009-detail-open.png。</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>iOS BGTaskScheduler/BackgroundTaskRunner coverage added 2026-06-29.</t>
+          <t>iOS BGTaskScheduler/BackgroundTaskRunner coverage added 2026-06-29. 実機では失敗状態表示のみ確認。成功取得と再取得実行はUS-013側で継続確認する。</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-06-29 00:57:14 +0900</t>
+          <t>2026-06-29 12:34:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1767,47 +1415,47 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS_WITH_INTERNAL_CONTRACT_GAP: 両実機で失敗metadataの再取得UI導線と押下を確認。再enqueue/updatedAt不変は未検証。</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。 / PASS device partial: 2026-06-29 Android/iPhone実機で失敗metadata詳細と再取得ボタン表示、押下操作を確認。</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>PARTIAL_DEVICE_GAP: 両実機で「再取得」ボタン表示と押下は確認。example.comのHTTP_404/ページ未検出状態のため、成功metadata取得は未確認。UI証跡だけでは再enqueue実行、WorkManager/MetadataCoordinator処理、metadata更新だけでupdatedAtを変えない契約は証明できない。</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>未修正: 今回は実機導線の確認と未検証内部契約の記録のみ。UI上の明確なクラッシュ/操作不能は未検出。必要ならログ/DB観測付きの非破壊検証を追加する。</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。 / RETEST NEEDED: 成功取得可能URLでのmetadata更新、再enqueueログ/DB観測、updatedAt不変確認。</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639): 既存URL詳細で「このURLは自動取得できません」「ページが見つからないため、自動取得できませんでした。」と「再取得」ボタンを確認し、再取得をタップ。短時間後も同じ404失敗表示。証跡: artifacts/device-verification/2026-06-29/android-us013-detail-before-retry.png/xml, android-us013-after-retry-tap.png/xml, android-us013-after-retry-settled.xml。再enqueue/updatedAt不変は未検証。</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL_PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session c5da0df9-c429-41d4-acc2-c82b0575b95c): 既存URL詳細で「このURLは自動取得できません」「ページが見つかりませんでした (HTTP_404)」と「再取得」ボタンを確認し、再取得をタップ。短時間後も同じ404失敗表示。証跡: iphone-us013-detail-before-retry.png/xml, iphone-us013-after-retry-tap.png/xml, iphone-us013-after-retry-settled.xml。再enqueue/updatedAt不変は未検証。</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t/>
+          <t>US-013は実機UI導線の確認は前進。完全PASSには、成功取得可能URLまたはDB/ログ観測で再enqueueとupdatedAt不変を確認する必要がある。</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:52:04 +0900</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1512,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS_WITH_TAG_DELETE_AND_DUPLICATE_GAP: 両実機でローカルタグ作成とURLへの割当は確認。削除時関連付け解除、重複処理、タグ別件数は未確認。</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1874,37 +1522,37 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>未完了範囲: タグ削除時の関連付け解除、重複タグ名/既割当時の文言、タグ別URL件数表示は今回未確認。iPhoneではタグ追加後にキーボード表示中のシートを閉じる操作がAppiumで安定せず、詳細画面へ戻した後の表示確認は未完了。</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>修正対象未確定: Android/iPhoneともローカルタグ作成・割当の実機導線は動作。iPhoneのタグ編集シート閉じ操作は追加調査対象。削除/重複/件数表示は次回以降の検証対象。</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>Android physical retest PARTIAL_PASS: 詳細タグ欄 -&gt; 編集 -&gt; 新しいタグ -&gt; タグを作成して追加で、現在のタグと詳細タグ欄に作成タグが表示。iPhone physical retest PARTIAL_PASS: 詳細タグ欄 -&gt; 編集 -&gt; 新しいタグ -&gt; タグを作成して追加で、現在のタグに us014-ios-1314 が表示。削除/重複/件数表示は未実施。</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum 1.0.13/13): 既存URL詳細でタグ欄「まだタグは付いていません」と編集ボタンを確認。タグ編集シートで新規タグを作成して追加し、「現在のタグ」に作成タグが表示、閉じた後の詳細タグ欄にも表示を確認。証跡: android-us014-detail-start.png/xml, android-us014-tag-editor-open.png/xml, android-us014-tag-name-entered.png/xml, android-us014-after-create-assign.png/xml, android-us014-detail-after-tag.png/xml。削除/重複/件数表示は未確認。</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PARTIAL_PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 31809d80-ed0b-4331-8c1f-fc32cc1ad527): 既存URL詳細でタグ欄「まだタグは付いていません」とローカルタグ編集ボタンを確認。タグ編集シートで us014-ios-1314 を入力し「タグを作成して追加」を実行、「現在のタグ」に us014-ios-1314 と「外す」が表示。証跡: iphone-us014-detail-tags-visible.png/xml, iphone-us014-tag-editor-open.png/xml, iphone-us014-tag-name-entered.png/xml, iphone-us014-after-create-assign.png/xml。キーボード表示中のシート閉じ/詳細戻り表示、削除/重複/件数表示は未確認。</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t/>
+          <t>Androidは端末キーボード変換により入力タグ名が全角混じりになったが、作成・割当・詳細表示は確認済み。US-014完全PASSには、両実機で重複タグ名/既割当時の文言、タグ削除時の関連付け解除、タグ管理/タグ詳細でURL件数表示を確認する必要がある。</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 13:18:39 +0900</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1609,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PHYSICAL_PASS_WITH_ANDROID_LOCAL_TAG_COPY_UX_GAP: 両実機でタグ選択/タグ詳細から対象URLだけの一覧と詳細遷移を確認。Androidローカルタグ詳細の共有タグ文言はUX不整合。</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1971,37 +1619,37 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>Android UX: ローカルタグ詳細でも「クラウド共有を使うにはサインインが必要です」「この共有タグを削除」など共有タグ文言が表示される。iPhoneはタグチップ選択で対象URL1件に絞り込みできるが、独立したタグ詳細画面ではなくホーム一覧フィルタとして実装されている。</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>未修正: Androidのローカルタグ詳細文言をローカルタグ向けに分岐する改善候補。iPhoneは現行設計上フィルタ導線で機能達成。</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>Android physical PASS: DB読取で tagId=1/entryId=4 の割当を確認後、urlsaver://tag/1 でタグ詳細を開き、タグ名、1件表示、対象URLカード、カードから詳細遷移を確認。iPhone physical PASS: Appium/WDAで us014-ios-1314 チップを横スクロール後にタップし、表示URLが2件から対象1件へ絞り込まれ、カードから詳細へ遷移することを確認。</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS on physical Android Pixel 9a 55211JEBF16639: artifacts/device-verification/2026-06-29/us015/android-us015-tag-detail.xml/png と android-us015-tag-detail-open-entry.xml/png。</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS on physical iPhone 12 UDID 00008101-00066D96340A001E via Appium/WDA: artifacts/device-verification/2026-06-29/us015/iphone-us015-after-tag-tap-source.json と iphone-us015-tag-open-entry-source.json。</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t/>
+          <t>非破壊確認のみ。Android DBは run-as で url_saver.db/-wal/-shm を読み取りコピーし、タグ割当を現在状態として照合。iPhoneはAppium session 2a3a89b1-ee18-4c91-8099-a11a7b00dbbf。</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 13:27:31 +0900</t>
         </is>
       </c>
     </row>
@@ -2145,7 +1793,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Android: MainActivityViewModelSecondaryIntentTest/ShareReceiverActivityEntrypointTest; iOS: PendingInviteStoreTests/URLSaverAppModel source + live tests</t>
+          <t>Android実機: adb am start deep link + uiautomator/screencap; iPhone実機: devicectl --payload-url + Appium/WDA source/screenshot; 既存unit/build結果参照</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2155,7 +1803,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PHYSICAL_PARTIAL_PASS_WITH_INVITE_UX_GAPS: 両実機で urlsaver://invite と https://miyamibu.xyz/invite が招待確認導線へ入ることを確認。Android HTTPSはローディング継続、iPhoneはraw error露出。実招待作成/参加は未検証。</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2165,37 +1813,37 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>Android HTTPS invite: 30秒以上「招待リンクを確認しています」から進まず、無効/失敗状態へ遷移しない。iPhone invalid invite: 「invalid_or_expired_invite」のraw errorが画面に露出し日本語UXになっていない。実招待作成/acceptは未検証。</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>未修正: 今回は検証・記録のみ。修正候補はAndroid invite previewのタイムアウト/失敗表示、iOS remote errorの日本語マッピング。</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>今回の再検証: Android physical Pixel 9aで urlsaver://invite は無効表示PASS、https inviteはローディング継続FAIL。iPhone physical + Appium/WDAで両形式とも招待確認画面遷移PASS、invalid raw error表示UX_FAIL。</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PHYSICAL_PARTIAL: Pixel 9a 55211JEBF16639 / jp.miyamibu.urlalbum v1.0.13。urlsaver://invite/codex-invalid-us017-20260629 は「招待リンクが無効か期限切れです」表示。https://miyamibu.xyz/invite/codex-invalid-us017-https-20260629 は招待確認画面へ入るが30秒以上ローディング継続。証跡: artifacts/device-verification/2026-06-29/us017/android-us017-*.png/xml</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PHYSICAL_PARTIAL: iPhone 12 UDID 00008101-00066D96340A001E / com.mibu.codebridge.ios v1.0.11 / Appium WDA session 1bf0b8f3-5c1a-49c8-8bf3-8f672e3ea7b0。urlsaver://invite と https://miyamibu.xyz/invite は招待確認画面へ遷移。無効時に「招待リンクを確認できませんでした」+ raw `invalid_or_expired_invite` 表示。証跡: artifacts/device-verification/2026-06-29/us017/iphone-us017-*.png/json</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t/>
+          <t>US-017はDeep Link受信/画面遷移は両実機で確認済み。実際の有効招待作成・参加・権限同期はSupabase liveユーザー状態が必要なため未完了。</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 14:49:26 +0900</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2094,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で認証関連画面表示PASS、OAuth/サインアウト実行は未検証</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2471,22 +2119,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): プロフィール画面で「Googleで続ける」「サインイン後に利用できます」を確認。実OAuthは未実施。証跡: android-pixel9a-profile-open-portrait.png/xml。</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): プロフィールシートでアカウント表示、ChatGPT連携トグル、サインアウトボタンを確認。サインアウト/OAuth callbackは未実施。証跡: iphone-ui-loop-profile-open.png/xml, iphone-ui-loop-after-inquiry-close-correct.png/xml。</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>秘密値入力はユーザー操作のみ</t>
+          <t>秘密情報入力や外部OAuthは実行せず、画面表示のみ確認。</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:03:48 +0900</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2191,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でプロフィール編集画面表示PASS、編集保存は未検証</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2568,22 +2216,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): プロフィール写真、プロフィール名、写真追加、画面モード、保存ボタンを確認。編集保存は未実施。証跡: android-pixel9a-profile-open-portrait.png/xml。</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): プロフィール名、メール、写真追加、画面モード、保存ボタンを確認。編集保存は未実施。証跡: iphone-ui-loop-profile-open.png/xml。</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t/>
+          <t>ユーザーデータ変更を避けるため、編集・保存は未実施。</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:03:48 +0900</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2288,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で問い合わせ/アカウント導線表示PASS、送信/削除は未検証</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2665,22 +2313,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): プロフィール画面で問い合わせ導線を確認。削除/送信は未実施。証跡: android-pixel9a-profile-open-portrait.png/xml。</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): プロフィールシートで問い合わせ、アカウント削除、サインアウトを確認し、問い合わせシートのメール/氏名/内容/送信UIを表示。送信/削除は未実施。証跡: iphone-ui-loop-profile-open.png/xml, iphone-ui-loop-after-closing-profile.png/xml, iphone-ui-loop-after-inquiry-close-correct.png/xml。</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>破壊的な実削除は承認なしに実行しない</t>
+          <t>破壊的なアカウント削除と問い合わせ送信は実行していない。</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 12:03:48 +0900</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2579,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でエクスポート設定画面PASS、共有シート/ファイル保存実行は未検証</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2956,22 +2604,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>未実機操作: export共有シート/ファイル保存は未検証。</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): エクスポート画面で「共有タグだけ」「ZIP」「JSON」「共有シート」「ファイルに保存」「書き出す」を確認。出力実行は未実施。証跡: android-pixel9a-export-open-portrait.png/xml。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: export共有シート/fileExporterは未検証。</t>
+          <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): エクスポート画面で「ZIP」「JSON」「共有シート」「ファイルに保存」「書き出す」を確認。UIActivityViewController/fileExporter実行は未実施。証跡: iphone-ui-loop-export-open-final.png/xml。</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>export share/file destination coverage refreshed 2026-06-29.</t>
+          <t>実ファイル生成、共有先アプリ、ファイル保存先確認は次ループで実施。</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-06-29 01:00:20 +0900</t>
+          <t>2026-06-29 12:03:48 +0900</t>
         </is>
       </c>
     </row>
@@ -3028,7 +2676,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
+          <t>PASS: Android/iPhone実機で使い方リストと戻る復帰を確認</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3058,17 +2706,17 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): ブック/使い方ボタンをタップし、初回spotlightではなく使い方リストへ遷移。「まず覚える」「便利な操作」「共有とAI」をXMLで確認し、戻るでホーム復帰。証跡: artifacts/device-verification/2026-06-29/iphone-appium-usage.png, iphone-appium-usage-source.xml, iphone-appium-home-after-usage-back.png, iphone-appium-home-after-usage-back-source.xml。</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>大きさデザイン変更は禁止</t>
+          <t>iPhone実機で下部バー非表示の使い方リストと戻る復帰を確認。</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 11:48:00 +0900</t>
         </is>
       </c>
     </row>
@@ -3125,7 +2773,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
+          <t>PASS: Android/iPhone実機でホーム下部5アクションと使い方画面非表示を確認</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3155,17 +2803,17 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): ホーム下部に グループ/エクスポート/中央＋/タグ/アーカイブ が表示され、中央＋が突出。使い方画面では下部バーが表示されないことをPNG/XMLで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml; artifacts/device-verification/2026-06-29/iphone-appium-usage.png, iphone-appium-usage-source.xml, iphone-appium-home-after-usage-back.png, iphone-appium-home-after-usage-back-source.xml。</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>サイズ変更は禁止。必要時は不具合記録のみ</t>
+          <t>iPhone実機でホーム下部5アクションと使い方画面の下部バー非表示を確認。</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 11:48:00 +0900</t>
         </is>
       </c>
     </row>
@@ -3319,7 +2967,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
+          <t>PASS_WITH_STORE_GAP: Android/iPhone実機の正準IDとiPhone表示名PASS、ストア表示未検証</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3344,22 +2992,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): canonical package jp.miyamibu.urlalbum をADBで起動しホーム証跡を取得。</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E): com.mibu.codebridge.ios インストールとdevicectl launch成功。Appium/WDA UI取得はRemoteXPC tunnel未起動/port 8100 refusedで失敗。NOT VERIFIED on physical iPhone for UI operations.</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): bundleId com.mibu.codebridge.ios のAppium sourceを取得し、Application name/label が「りんばむ」であることを確認。devicectl apps JSONでも表示名「りんばむ」を確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml; artifacts/device-verification/2026-06-29/iphone-rinbam-apps-after-rename.json。</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t/>
+          <t>実機上の正準Android package/iOS bundle IDは確認済み。App Store/Google Play Console上の表示は未操作。</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 11:48:00 +0900</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3064,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
+          <t>PASS: Android/iPhone実機で非破壊の起動・画面証跡を取得</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3446,17 +3094,17 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E): com.mibu.codebridge.ios インストールとdevicectl launch成功。Appium/WDA UI取得はRemoteXPC tunnel未起動/port 8100 refusedで失敗。NOT VERIFIED on physical iPhone for UI operations.</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): noResetのAppiumセッションでホーム、使い方遷移、戻る復帰を確認。アンインストール、pm clear、DB削除、データリセットなし。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml; artifacts/device-verification/2026-06-29/iphone-appium-usage.png, iphone-appium-usage-source.xml, iphone-appium-home-after-usage-back.png, iphone-appium-home-after-usage-back-source.xml。</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t/>
+          <t>iPhone Appium/WDA復旧後も非破壊確認のみ実施。Android connectedDebugAndroidTestや物理端末データ削除系コマンドは未実行。</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>2026-06-29 11:48:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5065,7 +4713,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
+          <t>BLOCKED_DEVICE_UI_DISABLED: コレクション保存先UIがAndroid/iOS現行ビルドで無効化されており、作成/移動/削除/並び替えを実機操作できない。</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5075,37 +4723,37 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>物理Androidでコレクション並び替え/削除、物理iPhoneでコレクション作成/保存先選択/既存URL移動/削除/並び替え/フィルタUIは未検証。iOSの同名ローカルタグ連携は、詳細移動時の作成/割当、削除時の同名タグ削除、コレクション選択時の同名タグ付きURL表示までローカル実装済みだが、実機操作は未確認。</t>
+          <t>Device/source gap: Androidは UrlSaverRoot.kt の SHOW_COLLECTION_UI=false によりコレクション作成/選択/並び替え/手動保存先指定が非表示。iOSは RootView.swift/DetailView.swift の showsCollectionUI=false により collectionCreateAction/collectionManageAction/collections、手動保存先、詳細の保存先変更が無効。iPhone実機に見える「+保存先」「保存先管理」「受信箱」はServiceFilterRow上のローカルタグ系チップで、コレクション作成「＋ コレクションを作成」やコレクション文言は表示されない。</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>FIXED_LOCAL: iOS collectionsテーブル/API、AppModel.collections、上部コレクションチップ、+保存先作成、保存先管理シート、手動保存先選択、詳細画面の保存先表示/移動シート、削除/並び替え、同名ローカルタグ連携、検索/フィルタ連携を追加。Android同様に同名ローカルタグ付きURLも選択コレクションに含める。</t>
+          <t>未修正: US-035を実機操作可能にするには、現行デザイン/仕様に沿ってAndroid SHOW_COLLECTION_UI と iOS showsCollectionUI の有効化方針を決め、コレクション作成/管理/詳細移動/削除/並び替えUIを有効化またはストーリー範囲をローカルタグへ再定義する必要がある。</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>PASS local retest: iOS URLRepositoryTests + ServiceFilterTests 30件成功。Android既存ローカルテストは前回成功済み。iOS/Android物理UI操作は未実施。</t>
+          <t>BLOCKED physical retest 2026-06-29: Android/iPhone実機でホーム画面を確認したが、コレクション作成/管理/移動UIが無効化されており、US-035 acceptance criteriaの作成/保存先選択/既存URL移動/削除/並び替えを操作できなかった。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>未実機操作: コレクション作成/並び替え/削除は未検証。</t>
+          <t>NOT VERIFIED / BLOCKED(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): ホーム画面にりんばむ、共有タグ、タグ、保存カードは表示。SHOW_COLLECTION_UI=false のためコレクション作成/管理/選択/並び替えUIは表示されず、コレクション作成/移動/削除/並び替えは実機操作不能。証跡: artifacts/device-verification/2026-06-29/us035/android-start.xml, android-start.png。</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: コレクション作成/保存先選択/既存URL移動/削除/並び替え/フィルタUIは実機操作未検証。</t>
+          <t>NOT VERIFIED / BLOCKED(iPhone physical 00008101-00066D96340A001E, Appium/WDA, com.mibu.codebridge.ios): ホーム画面に「+保存先」「保存先管理」「受信箱」等は見えるが、source上「コレクション」「＋ コレクションを作成」は表示なし。showsCollectionUI=false のためコレクション作成/管理/保存先指定/詳細移動UIは無効で、US-035の実機操作は不能。証跡: artifacts/device-verification/2026-06-29/us035/iphone-start-source.xml, iphone-start.png。</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>iOS collection parity local implementation completed for create/filter/manual-save/detail-move/manage/delete/reorder/search/same-name local-tag linkage on 2026-06-29. Same-name local-tag filter parity added after gap audit. Physical-device proof still required.</t>
+          <t>2026-06-29 physical/source audit: US-035はローカル実装済み扱いだったが、現行UIフラグで実機から到達不能。iOSの「保存先」表示はローカルタグ系導線と混同しやすいため、コレクション機能としては未提供扱い。</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-06-29 01:43:21 +0900</t>
+          <t>2026-06-29 15:32:41 +0900</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5101,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_UI_DEVICE_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で検索欄表示・入力・クリアPASS、実データ絞り込みは未検証</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5478,22 +5126,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>未実機操作: 検索欄表示/入力/クリアは未検証。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 検索アイコンから検索欄表示、入力、クリアを確認。IME影響で入力値は「りんばｍてｓｔ」になったが、EditText入力状態とクリア後空欄復帰をXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/android-us037-search-open-retry.png/xml, android-us037-search-input-rinbamtest.png/xml, android-us037-search-cleared.png/xml。</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: 検索欄表示/入力/クリアとコレクション名検索の実機操作は未検証。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session cca5fad7-b2ae-491d-a4ac-95499e1ed33b): 検索ボタンからTextField表示、rinbamtest入力、クリアボタン表示、クリア後ホーム復帰を確認。証跡: artifacts/device-verification/2026-06-29/iphone-us037-search-open.png/source.xml, iphone-us037-search-input.png/source.xml, iphone-us037-search-cleared.png/source.xml。</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>User search local-tag false-positive fixed 2026-06-29. iOS collection-name search wired and tested 2026-06-29.</t>
+          <t>物理Android/iPhoneで検索欄の表示・入力・クリアは確認済み。保存済み実データに対するタイトル/URL/ホスト/コレクション/タグ絞り込み結果は、テスト用データ作成許可後に確認が必要。</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-06-29 01:32:41 +0900</t>
+          <t>2026-06-29 12:12:03 +0900</t>
         </is>
       </c>
     </row>
@@ -5550,47 +5198,47 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
+          <t>PHYSICAL_PASS_WITH_ANDROID_SELECTION_BUTTON_UX_GAP</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/URLRepositoryTests 成功、10 tests。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/URLRepositoryTests 成功、10 tests。PHYSICAL PASS: 2026-06-29にAndroid/iPhone実機で複数選択、一括アーカイブUndo、一括削除Undoを確認。</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>物理端末UI操作は未検証。iOSは保存層の複数件状態遷移を検証済みだが、RootViewの選択バー操作そのものは未検証。</t>
+          <t>Android physical UX/logical gap: ヘッダーの「選択」を押しても selectedEntryIds が空のため MainEntryList の selectionMode が false のままで、カードタップが詳細遷移した。コード上 selectionMode = selectedEntryIds.isNotEmpty() が selectionModeActive を見ていない。長押し選択、2件選択、一括アーカイブUndo、一括削除Undoは両実機で確認済み。</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>TESTED_LOCAL: Android ViewModel一括archive/pending deleteの成功/失敗混在をテスト追加。iOS URLRepositoryで複数件archive/pending delete状態遷移をテスト追加。</t>
+          <t>未修正: Androidヘッダー選択ボタンの空選択モードをカード選択に反映する修正候補あり。US-038の一括削除Undo未証明は2026-06-29実機再検証で解消。</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>PASS local retest: Android MainListViewModelTest、iOS URLRepositoryTests 成功。物理UI選択/Undo操作は未実施。</t>
+          <t>PASS physical retest: Android長押し選択 -&gt; 2件選択 -&gt; 2件一括アーカイブ -&gt; Undo復帰、2件一括削除 -&gt; Undo復帰を確認。iPhone選択ボタン -&gt; 2件選択 -&gt; 2件一括アーカイブ -&gt; Undo復帰、2件一括削除 -&gt; Undo復帰を確認。Androidヘッダー「選択」単体の空選択UXのみ未修正。</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>未実機操作: 一括選択/Undoは未検証。</t>
+          <t>PASS_WITH_UX_GAP(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 長押しで1件選択、2件選択、選択バー「すべて選択/アーカイブ/削除/キャンセル」、一括アーカイブ通知「2件をアーカイブしました」「元に戻す」、Undo後に保存 14:56/14:55 復帰、一括削除通知「2件を削除しました」「元に戻す」、Undo後に保存 14:56/14:55 復帰を確認。ヘッダー「選択」単体は空選択状態からカード選択に繋がらず詳細遷移。証跡: artifacts/device-verification/2026-06-29/us038/android-us038-longpress2.*, android-us038-two-selected.*, android-us038-after-batch-archive.*, android-us038-after-batch-archive-undo.*; artifacts/device-verification/2026-06-29/us038-delete-undo/android-two-selected-before-delete.*, android-after-batch-delete.*, android-after-batch-delete-undo.*</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: 一括選択/Undoは未検証。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E, Appium/WDA, com.mibu.codebridge.ios): ヘッダー「選択」で2件選択、選択バー「すべて選択/アーカイブ/削除/キャンセル」、一括アーカイブ通知「2件をアーカイブしました」「元に戻す」、Undo後に保存 15:03/保存 12:27/Rinbam iPhone Title 復帰、一括削除通知「2件を削除しました」「元に戻す」、Undo後に保存 15:03/保存 12:27/Rinbam iPhone Title 復帰を確認。証跡: artifacts/device-verification/2026-06-29/us038/iphone-us038-after-select-button.*, iphone-us038-after-batch-archive.*, iphone-us038-after-batch-archive-undo.*; artifacts/device-verification/2026-06-29/us038-delete-undo/iphone-two-selected-before-delete.*, iphone-after-batch-delete.*, iphone-after-batch-delete-undo.*</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Batch selection local contract tests added 2026-06-29. UI operation still needs physical-device proof.</t>
+          <t>既存データ保護のため物理端末では一時/検証カードのみ対象。Androidのヘッダー選択不具合はコード上も再現理由を確認済み。</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-06-29 01:16:00 +0900</t>
+          <t>2026-06-29 15:27:27 +0900</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5392,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP: Android/iPhone実機データ取り扱い表示PASS、コード/公開WebローカルPASS、ストア申告未検証</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5769,22 +5417,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>未実機操作: プライバシーダイアログ表示は未検証。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): プライバシー情報ボタンから「データの取り扱い」ダイアログを表示。端末内保存、メタデータ取得、共有タグクラウド、問い合わせ、Standard / Pro Google Play Billing、広告/分析/第三者クラッシュ収集なしの文言をXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/android-us040-home-before.png/xml, android-us040-privacy-dialog.png/xml。</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: データ取り扱いシート表示は実機操作未検証。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): info.circle からデータ取り扱いシートを表示。「端末内に保存する情報」「メタデータ取得」「共有タグクラウド」と閉じるボタンをPNG/XMLで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-privacy.png, iphone-appium-privacy-source.xml。</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ES-006は公開Web/リンク。これはAndroid/iOSアプリ内表示と広告ガード。 Android app privacy dialog source updated 2026-06-29. iOS PrivacyInfoSheet/info.circle app UI added 2026-06-29 and generic build passed. public privacy staleはproduction deployで解消。</t>
+          <t>Android/iPhoneアプリ内データ取り扱い表示は実機確認済み。Google Play/App Storeのデータセーフティ/広告申告画面は未操作。</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-06-29 07:25:00 +0900</t>
+          <t>2026-06-29 12:12:03 +0900</t>
         </is>
       </c>
     </row>
@@ -5983,15 +5631,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S57"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6008,7 +5652,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
+          <t>BLOCKED_DEVICE_UI_DISABLED: コレクション保存先UIがAndroid/iOS現行ビルドで無効化されており、作成/移動/削除/並び替えを実機操作できない。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +5664,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LINKED_RPC_PASS_WITH_CHATGPT_CONSUMPTION_GAP</t>
+          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6032,36 +5676,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
+          <t>LINKED_RPC_PASS_WITH_CHATGPT_CONSUMPTION_GAP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_UI_GAP</t>
+          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -6085,7 +5729,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6104,7 +5748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP</t>
+          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP: Android/iPhone実機データ取り扱い表示PASS、コード/公開WebローカルPASS、ストア申告未検証</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6116,7 +5760,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_UI_DEVICE_GAP</t>
+          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6128,7 +5772,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でmetadata失敗状態表示PASS、成功取得は未検証</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6140,31 +5784,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone UI操作は未検証</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でエクスポート設定画面PASS、共有シート/ファイル保存実行は未検証</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhone launchのみPASS</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でタイトル編集保存PASS、Undo実行は未検証</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
+          <t>PARTIAL_PASS: Android/iPhone実機でプロフィール編集画面表示PASS、編集保存は未検証</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6176,7 +5820,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PASS: Web管理画面 typecheck/build 成功</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で問い合わせ/アカウント導線表示PASS、送信/削除は未検証</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6188,7 +5832,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で手動貼り付け保存PASS、重複時挙動は未検証</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6200,7 +5844,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PASS_LINKED_DB_WITH_ADVISORY_WARNINGS</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で検索欄表示・入力・クリアPASS、実データ絞り込みは未検証</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6212,7 +5856,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PASS_LINKED_DB_WITH_STORE_WEBHOOK_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で表示モード切替PASS、再起動後保持は未検証</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6224,7 +5868,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PASS_PUBLIC_WEB_WITH_FINAL_SHA_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で詳細からアーカイブ/復元PASS、スワイプ操作とUndo実行は未検証</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6236,7 +5880,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PASS_RESEND_SENT_WITH_DELIVERY_EVENT_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で詳細遷移と外部で開く導線表示PASS、外部ブラウザ起動は未実行</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6248,7 +5892,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PASS_WITH_PHYSICAL_OPERATION_GAP</t>
+          <t>PARTIAL_PASS: Android/iPhone実機で認証関連画面表示PASS、OAuth/サインアウト実行は未検証</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6257,128 +5901,402 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PARTIAL_PASS: Android実機PASS、iPhoneホーム/フィルター表示PASS、保存URL絞り込み操作未実施</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>remaining_gate</t>
+          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>story_ids</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>physical_Android</t>
+          <t>PARTIAL_PASS_WITH_INTERNAL_CONTRACT_GAP: 両実機で失敗metadataの再取得UI導線と押下を確認。再enqueue/updatedAt不変は未検証。</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US-001,US-002,US-003,US-004,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-028,US-029,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039,US-040</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>physical_iPhone</t>
+          <t>PARTIAL_PASS_WITH_IPHONE_INPUT_GAP: Android実機の複数URL共有保存はPASS。iPhone実機は複数URL共有入力を生成できず、実保存未検証。</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-009,US-010,US-011,US-012,US-013,US-014,US-015,US-016,US-017,US-018,US-019,US-020,US-021,US-022,US-023,US-024,US-025,US-026,US-027,US-028,US-029,US-030,ES-003,US-031,US-032,US-033,US-034,US-035,US-036,US-037,US-038,US-039,US-040</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>supabase_or_auth_live</t>
+          <t>PARTIAL_PASS_WITH_IPHONE_SHARE_EXTENSION_ERROR: Android実機の単一URL共有保存はPASS。iPhone実機は共有シートにりんばむ表示まで確認したが、選択後の保存引き継ぎが失敗。</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US-016,US-018,US-019,US-023,US-024,US-031,US-032,US-039</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>store_or_public_console</t>
+          <t>PARTIAL_PASS_WITH_NORMALIZATION_AND_IPHONE_UX_GAP: 両実機で同一URL重複は確認済み。表記違い正規化とiPhone通知導線は未完了。</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>US-033,AS-007,ES-006,US-039,US-040,TS-001</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>resend_live</t>
+          <t>PARTIAL_PASS_WITH_TAG_DELETE_AND_DUPLICATE_GAP: 両実機でローカルタグ作成とURLへの割当は確認。削除時関連付け解除、重複処理、タグ別件数は未確認。</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AS-008,AS-009</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>PASS: Android/iPhone実機でホーム下部5アクションと使い方画面非表示を確認</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PASS: Android/iPhone実機でメモ編集保存PASS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PASS: Android/iPhone実機で使い方リストと戻る復帰を確認</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PASS: Android/iPhone実機で非破壊の起動・画面証跡を取得</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PASS: Web管理画面 typecheck/build 成功</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PASS_LINKED_DB_WITH_ADVISORY_WARNINGS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PASS_LINKED_DB_WITH_STORE_WEBHOOK_GAP</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PASS_PUBLIC_WEB_WITH_FINAL_SHA_GAP</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PASS_RESEND_SENT_WITH_DELIVERY_EVENT_GAP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PASS_WITH_PHYSICAL_OPERATION_GAP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PASS_WITH_STORE_GAP: Android/iPhone実機の正準IDとiPhone表示名PASS、ストア表示未検証</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PHYSICAL_PARTIAL_PASS_WITH_INVITE_UX_GAPS: 両実機で urlsaver://invite と https://miyamibu.xyz/invite が招待確認導線へ入ることを確認。Android HTTPSはローディング継続、iPhoneはraw error露出。実招待作成/参加は未検証。</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PHYSICAL_PASS_WITH_ANDROID_LOCAL_TAG_COPY_UX_GAP: 両実機でタグ選択/タグ詳細から対象URLだけの一覧と詳細遷移を確認。Androidローカルタグ詳細の共有タグ文言はUX不整合。</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PHYSICAL_PASS_WITH_ANDROID_SELECTION_BUTTON_UX_GAP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PHYSICAL_PASS_WITH_TEMP_DATA: 両実機で一時URLを使い、削除確認、5秒Undo通知、Undo後の一覧復帰を確認。</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>remaining_gate</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>story_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>physical_Android</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>US-016,US-018,US-019,US-023,US-024,US-028,US-031,US-032,US-033,US-034,US-035,US-036,US-039</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>physical_iPhone</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>US-003,US-016,US-018,US-019,US-023,US-024,US-028,ES-003,US-031,US-032,US-033,US-034,US-035,US-036,US-039</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>supabase_or_auth_live</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>US-016,US-017,US-018,US-019,US-020,US-023,US-024,US-031,US-032,US-039</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>store_or_public_console</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>US-029,US-033,AS-007,ES-006,US-039,US-040,TS-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>resend_live</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AS-008,AS-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>connected_android_instrumentation</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B30"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -1,24 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="stories" sheetId="1" r:id="rId1"/>
-    <sheet name="summary" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="canonical_story_status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'canonical_story_status'!$A$1:$U$59</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -34,8 +50,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -82,24 +170,277 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
-      <a:fillStyleLst/>
-      <a:lnStyleLst/>
-      <a:effectStyleLst/>
-      <a:bgFillStyleLst/>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -159,40 +500,50 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>status_code</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>remaining_gate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>first_test_result</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>documented_errors</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>fix_status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>retest_result</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>android_device_result</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>iphone_device_result</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -251,47 +602,57 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で手動貼り付け保存PASS、重複時挙動は未検証</t>
+          <t>PASS: Android/iPhone実機で通常手動貼り付け保存と重複通知/見る導線PASS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 一時URL https://example.com/rinbam-device-test-20260629-1214 を入力欄から保存し、一覧に example.com / 保存 12:15 / 自動取得できません が表示。証跡: artifacts/device-verification/2026-06-29/android-us001-add-form-ready-save.png, android-us001-after-save-final.png。</t>
+          <t>PARTIAL_FIXED_WITH_CONTRACT_TESTS: Android/iOSのURL抽出をcase-insensitive化し、手動入力の大文字HTTPS+443+fragmentが小文字正規化URLとDUPLICATE_ACTIVEになるRepository回帰テストを追加。 2026-07-03追加: iOS手動保存フローをprepareManualSave/finishPreparedManualSaveへ分離し、保存成功・重複時はManualInputSheetを閉じてから通知を出すよう修正。これにより重複通知「このURLはすでに保存済みです」/「見る」がシート裏で消えるリスクを下げた。iOS generic simulator build成功、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。物理iPhoneには04:19署名済みDebug appを上書きインストールし04:20 devicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-notification-fix.json。 2026-07-03追加: iOS ManualSaveOutcomeにcompleted分岐を追加し、タグJSON読み込み時は既存のタグ読み込み通知だけにして、保存通知を重ねないよう副作用を修正。xcodebuild generic simulator build PASS、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 一時URL https://example.com/rinbam-iphone-device-test-20260629-1226 を入力欄から保存し、一覧に example.com / 保存 12:27 / 自動取得できません が表示。証跡: iphone-us001-add-form-filled.png, iphone-us001-after-save-final.png。</t>
+          <t>PASS local contract: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.RepositoryBehaviorTest --tests jp.mimac.urlsaver.UrlRulesTest 成功。xcodebuild selected URLRepositoryTests/URLRulesTests 成功。Android実機DBでも共有保存の表記違い重複は1件にまとまることを確認。Android手動追加UIでも重複通知「このURLはすでに保存済みです」+「見る」押下で既存詳細へ遷移することを確認。iPhone物理UI操作の同条件はAppium usbmuxd 0件のため未検証。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。手動入力、正規化、重複、URLなしテキストカードのiOS契約をURLRulesTests/URLRepositoryTestsで確認。 2026-07-03追加: iOS手動保存フローをprepareManualSave/finishPreparedManualSaveへ分離し、保存成功・重複時はManualInputSheetを閉じてから通知を出すよう修正。これにより重複通知「このURLはすでに保存済みです」/「見る」がシート裏で消えるリスクを下げた。iOS generic simulator build成功、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。物理iPhoneには04:19署名済みDebug appを上書きインストールし04:20 devicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-notification-fix.json。 2026-07-03追加: iOS ManualSaveOutcomeにcompleted分岐を追加し、タグJSON読み込み時は既存のタグ読み込み通知だけにして、保存通知を重ねないよう副作用を修正。xcodebuild generic simulator build PASS、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>重複保存の実機挙動は次ループで別URL表記差分を使って確認する。既存ユーザーデータは削除/リセットしていない。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 一時URL https://example.com/rinbam-device-test-20260629-1214 の通常手動保存PASS。2026-07-03追加で既存URL https://example.com/rinbam-normalize-fixed-direct-20260703003607 を手動追加し、重複通知「このURLはすでに保存済みです」+「見る」を確認、即時タップで既存詳細画面へ遷移。証跡: artifacts/device-verification/2026-06-29/android-us001-add-form-ready-save.png, android-us001-after-save-final.png; artifacts/device-verification/2026-07-03-us001-016-continuation/android-manual-duplicate-filled.png/xml, android-manual-duplicate-snackbar-fast.png/xml, android-manual-duplicate-after-fast-open-existing.png/xml。</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-06-29 12:34:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 一時URL https://example.com/rinbam-iphone-device-test-20260629-1226 を入力欄から保存し、一覧に example.com / 保存 12:27 / 自動取得できません が表示。証跡: iphone-us001-add-form-filled.png, iphone-us001-after-save-final.png。 INSTALL/LAUNCH_ONLY: 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。 2026-07-03再確認: 手動追加で同一URL重複通知「このURLはすでに保存済みです」と「見る」を確認し、押下で詳細へ遷移PASS。証跡: artifacts/device-verification/2026-07-03-iphone-appium-resumed/iphone-manual-duplicate-second-save.png, iphone-manual-duplicate-after-view.png。</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>手動貼り付けの通常保存は両実機の既存証跡あり。表記違い正規化重複はAndroid/iOSのRepositoryテストで固定し、Android実機DBでも確認。Android手動追加UIの重複通知/見る導線は2026-07-03に実機確認済み。残: iPhoneの手動追加UIで重複通知「見る」押下までの実機操作証跡。iPhone実機へ修正版Debug appは上書きインストール済みだが、Appium側usbmuxd 0件で操作証跡未取得。 2026-07-03 04:20再確認: devicectlではiPhone 12にインストール/起動できるが、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723未起動、RemoteXPC 42314 timeout。このためiPhoneの重複通知「見る」実操作は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:22追加: Appium 3.5.0 serverを通常権限で起動しXCUITest session作成を再試行。RemoteXPC devices listing unavailable: tunnel registry timeout。fallback後も Unknown device or simulator UDID 00008101-00066D96340A001E でHTTP 500。ログ: artifacts/device-verification/2026-07-03-iphone-nonvideo/appium-server-retry.log。devicectl install/launchは可能だが、Appium/WDA UI操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:29追加: devicectl install/launchは成功。Appium/WDAはRemoteXPC tunnel timeout / Unknown device or simulator UDIDで継続失敗のため、iPhone物理UI操作は引き続き NOT VERIFIED on physical iPhone。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。 2026-07-03 06:11追加: iPhone physical 00008101-00066D96340A001E via Appium session 11de0304-6218-47b3-8ef4-d90eb4eae34b で手動追加から https://example.com を保存し、2回目保存時に「このURLはすでに保存済みです」通知と「見る」ボタンを確認。「見る」押下で詳細画面へ遷移PASS。証跡: artifacts/device-verification/2026-07-03-iphone-appium-resumed/iphone-manual-duplicate-second-save.png, iphone-manual-duplicate-after-view.png。</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:11:00 +0900</t>
         </is>
       </c>
     </row>
@@ -348,47 +709,57 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_IPHONE_SHARE_EXTENSION_ERROR: Android実機の単一URL共有保存はPASS。iPhone実機は共有シートにりんばむ表示まで確認したが、選択後の保存引き継ぎが失敗。</t>
+          <t>PASS: Android/iPhone実機で単一URL共有保存PASS</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>iPhone physical share extension: Safari共有シートで「りんばむ」を選択後、「アプリへ引き継げなかったため保存できませんでした」と表示。ShareViewControllerのhost app fallback/openHostApp経路または実機URL引き継ぎに問題の可能性。CoreSimulator/XCTest不整合は別件として継続。</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>未修正: US-002 iPhone共有拡張の保存引き継ぎ失敗を新規実機エラーとして記録。原因候補はShare Extensionからurlsaver://saveをopenするfallback経路、App Group repository初期化、または実機URL scheme引き継ぎ。</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Android physical retest PASS: ACTION_SEND text/plainで新規URLをShareReceiverActivityへ送り、「保存先タグ」シート -&gt; 「保存」 -&gt; 「保存しました」を確認。iPhone physical retest FAIL: Safari共有シートで「りんばむ」セルは表示されるが、選択後に保存できず失敗文言。connected Android instrumentationは2026-06-29 urlsaverParityApi35 AVDでPASS済み。</t>
+          <t>解消済み: 2026-06-29時点のiPhone共有拡張保存引き継ぎ失敗は、2026-07-02/03の物理iPhone Safari共有再検証で再現せず、保存完了まで確認。CoreSimulator/XCTest不整合は別ゲートとして継続。</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>FIXED_LOCAL_AND_DEVICE_VERIFIED: iPhone Share ExtensionはApp Group内保存経路でSafari単一URLを保存できることを実機確認済み。</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>PASS physical retest: Android ACTION_SEND単一URL共有保存PASS。iPhone physical Safari https://example.com 共有 -&gt; りんばむ -&gt; 保存先タグ -&gt; 保存 -&gt; 保存しました -&gt; 完了 -&gt; Safari復帰をAppium/WDAで確認。</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum 1.0.13/13): ACTION_SEND text/plainで https://example.com/rinbam-us002-20260629125754 を共有。保存先タグシート、保存ボタン、保存後「保存しました」を確認。完了後ホームにexample.comカードが追加。証跡: android-us002-share-sheet.png/xml, android-us002-after-save.png/xml, android-us002-home-after-back.png/xml。</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>FAIL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): Safariで https://example.com/rinbam-us002-ios-20260629130000 を開き、共有メニュー -&gt; 共有シートで「りんばむ」セルを確認。XCUIElementTypeCell label=りんばむ をクリック後、「アプリへ引き継げなかったため保存できませんでした」と表示。証跡: iphone-us002-safari.png/xml, iphone-us002-safari-more-menu.png/xml, iphone-us002-share-sheet.png/xml, iphone-us002-share-sheet-scroll-3.png/xml, iphone-us002-after-rinbam-element-click.png/xml。</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>iPhone共有シート上の表示名は「りんばむ」で旧名ではない。US-002完全PASSにはiPhone Share Extension保存成功または直接保存経路の修正と再テストが必要。</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-06-29 13:06:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA, bundle com.mibu.codebridge.ios.share): Safari https://example.com 共有シートで「りんばむ」を選択し、Share Extensionの「保存先タグ」「保存」「キャンセル」「新しいタグ名」とタグ表示を確認。保存押下後「保存しました」、完了押下後Safari復帰を確認。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/iphone-share-sheet.png/source, iphone-share-extension-after-click.png/source, iphone-share-extension-after-save.png/source, iphone-share-extension-after-done.png/source。</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>iPhone共有シート上の表示名は「りんばむ」。単一URL共有は復旧確認済み。複数URL共有はUS-003で別途追跡。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-07-03 04:45:00 +0900</t>
         </is>
       </c>
     </row>
@@ -445,47 +816,57 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_IPHONE_INPUT_GAP: Android実機の複数URL共有保存はPASS。iPhone実機は複数URL共有入力を生成できず、実保存未検証。</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>iPhone physical US-003 input gap: Safari通常共有は単一URLのみ。Web Share APIで複数URLテキスト共有を作る一時ページを試したが、物理iPhone Safari上で navigator.share is not a function となり共有シートを生成できなかった。US-002では共有シートの「りんばむ」選択後に保存引き継ぎ失敗も確認済み。</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>未修正: US-003 iPhone複数URL共有の実機入力手段と、US-002で見つかったShare Extension保存引き継ぎ失敗の修正が必要。Android側の今回検証ではロジスティカル/UXエラーなし。</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Android physical retest PASS: ACTION_SEND_MULTIPLE + 改行区切りEXTRA_TEXTで新規2件をShareReceiverActivityへ送り、「保存先タグ」シート -&gt; 「保存」 -&gt; 「2件を処理しました（新規2 / 既存0 / 復元0 / 失敗0）」を確認。iPhone physical retest NOT VERIFIED for multi URL save: Web Share代替はnavigator.share未対応で共有シート生成不可。</t>
+          <t>iPhone physical US-003 input source gap: Safari通常共有は単一URLのみ。Web Share API一時ページでは共有シート生成不可。Notesに2件URL本文を作り、その他アプリ一覧にりんばむは表示されたが、Notes側が共同作業リンク作成フローへ遷移し、Share Extension保存画面まで到達しなかった。 2026-07-03 07:05追加: iPhone実機で追加確認。Notes共有は共有先一覧にりんばむが表示されても、選択後にNotesの「リンクを作成」共同作業UIへ遷移しShare Extensionに渡らない。Safari Web Share検証はCloudflare Quick Tunnelが404、localhost.runがTLS不可。LAN HTTPページは表示できたがSafariで navigator.share is not a function となり、HTTPS入力元なしでは共有シート生成不可。 2026-07-03 07:18追加: HTTPS example.com 上でSafariアドレスバーから javascript:navigator.share(...) を実行する方式も試したが、iPhone Safariが「スクリプトを実行できません。JavaScriptは、この方法で使用することが許されていません。」を表示し共有シートは出なかった。</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>未修正: Androidは動作確認済み。iPhoneは実装以前に複数URLテキストを通常共有できる入力元アプリ/手順の確立が必要。Share Extensionの複数URL抽出契約自体はURLRulesTests extractAllで継続確認。 2026-07-03追加: iOS URLRulesTestsに共有拡張候補グループ相当の複数URL抽出テストを追加。単一テキスト内+provider/stream候補をまたいだ複数URL、fragment除去、重複排除、順序維持を確認。xcodebuild test -only-testing:URLSaveriOSTests/URLRulesTests は22 tests PASS。ただし物理iPhoneでの複数URL共有完了操作は入力元アプリ問題とAppium/usbmuxd未復旧により未検証。 2026-07-03 04:33追加: iOS Share Extensionの複数URL分岐を修正し、明示的な複数アイテム共有でなくても共有本文/候補グループから2件以上URLを抽出できた場合はバッチ保存に入るようにした。これにより、1つのプレーンテキスト本文に複数URLが入る入力元でもAndroid同様に複数保存できる契約へ寄せた。iOS generic simulator build PASS、URLRulesTests 22件 PASS。 2026-07-03 22:48追加: 入力元ギャップは一時署名済み共有元アプリで解消し、実機保存完了まで確認済み。</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Android physical retest PASS継続。iPhone physical retest PARTIAL: Notes新規ノートへ2件URLを入力し共有シート/その他内のりんばむ表示までは確認したが、Notesの共同作業リンク作成UIに遷移し保存未完了。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。複数URL抽出、重複排除、最大件数切り詰めのiOS契約をURLRulesTestsで確認。物理iPhoneの複数URL共有入力元ギャップは継続。 2026-07-03追加: iOS URLRulesTestsに共有拡張候補グループ相当の複数URL抽出テストを追加。単一テキスト内+provider/stream候補をまたいだ複数URL、fragment除去、重複排除、順序維持を確認。xcodebuild test -only-testing:URLSaveriOSTests/URLRulesTests は22 tests PASS。ただし物理iPhoneでの複数URL共有完了操作は入力元アプリ問題とAppium/usbmuxd未復旧により未検証。 2026-07-03 04:33追加: iOS Share Extensionの複数URL分岐を修正し、明示的な複数アイテム共有でなくても共有本文/候補グループから2件以上URLを抽出できた場合はバッチ保存に入るようにした。これにより、1つのプレーンテキスト本文に複数URLが入る入力元でもAndroid同様に複数保存できる契約へ寄せた。iOS generic simulator build PASS、URLRulesTests 22件 PASS。 2026-07-03 07:05追加 iPhone physical via Appium/WDA: 一時Web Shareページを用意し、LAN HTTPで実機表示まではPASS。ただしSafariがHTTP上では navigator.share undefined を返した。Notesは共同作業リンク作成フローに固定され、りんばむ保存画面まで到達せず。 2026-07-03 07:18追加 iPhone physical via Appium/WDA: HTTPS example.com で javascript: navigator.share を試行し、Safariのスクリプト実行不可アラートを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us003-after-js-share2.png/xml。 2026-07-03 22:48追加 iPhone physical via Appium/WDA: 一時共有元アプリからURLオブジェクト2件を共有し、りんばむShare Extensionの保存先タグ画面、保存押下、完了文言「2件を処理しました（新規2 / 既存0 / 復元0 / 失敗0）」を確認。US-003 iPhone物理確認 PASS。</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum 1.0.13/13): ACTION_SEND_MULTIPLE text/plainで https://example.com/rinbam-us003-a2-202606291309 と https://example.com/rinbam-us003-b2-202606291309 を改行区切りEXTRA_TEXTとして共有。保存先タグシート、保存ボタン、保存後「2件を処理しました（新規2 / 既存0 / 復元0 / 失敗0）」を確認。証跡: android-us003-share-sheet-retry.png/xml, android-us003-after-save.png/xml。</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED on physical iPhone for US-003 multi URL save (00008101-00066D96340A001E via Appium/WDA): Safari通常共有は単一URLのみのためUS-003条件を満たさず。ローカル一時ページからWeb Share APIで複数URLテキスト共有を試したが、物理iPhone Safariで「navigator.share is not a function」と表示され共有シートを生成できなかった。証跡: iphone-us003-webshare-start.png/xml, iphone-us003-webshare-after-button.png/xml, us003-webshare/index.html。</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Android投入時、adb --esa配列形式では実機am経由でURL抽出できず「URLが見つかりませんでした」になったため、テストで許容されるACTION_SEND_MULTIPLE + 改行区切りEXTRA_TEXTで再検証しPASS。iPhone US-003完全確認にはNotes/Files等から複数URLテキストを共有する実機手段、またはUS-002 Share Extension引き継ぎ修正後の再テストが必要。</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-06-29 13:11:27 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 一時署名済み共有元アプリ com.mibu.rinbam.sharesource を作成/実機インストールし、UIActivityViewController から URL オブジェクト2件 https://example.com/rinbam-ios-activity-a-20260703 と https://example.com/rinbam-ios-activity-b-20260703 を共有。共有シートで「りんばむ」を選択し、Share Extensionの「保存先タグ」画面へ到達、保存ボタン押下後に「2件を処理しました（新規2 / 既存0 / 復元0 / 失敗0）」を確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us003-share-source-start.png/xml, iphone-us003-share-sheet-urlitems.png/xml, iphone-us003-share-extension-correct-tap.png/xml, iphone-us003-after-save.png/xml。</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>iPhone US-003完全確認には、Notes共同作業ではなくプレーンテキストとして複数URLを共有できる入力元、またはテスト用共有元アプリ/ショートカットの整備が必要。 2026-07-03 04:33追加: 上記Share Extension修正版を物理iPhone 12へ上書きインストールしdevicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-share-extension-multiurl-fix.json。Appium/WDA UI操作証跡ではないため、物理iPhoneの複数URL共有保存完了は引き続き NOT VERIFIED on physical iPhone。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。 2026-07-03 07:05追加: iPhoneのみ追加検証。現時点の未完了理由はアプリ実装ではなく、実機で複数URLテキストをHTTPS/Web Shareまたはプレーンテキスト共有として渡せる入力元確保。次に進めるなら、署名済みの小さな検証用共有元アプリ、または信頼済みHTTPSホスト上のWeb Shareページが必要。 2026-07-03 07:18追加: Safari/Notes/Webだけでは複数URLプレーンテキスト共有の入力元を確保できず。完全な物理iPhone保存完了確認には、一時的な署名済み共有元アプリ、または信頼済みHTTPSホスト上のWeb Shareページが必要。 2026-07-03 22:48追加: iPhone物理US-003は完了。検証用共有元アプリは artifacts 配下の一時証跡で、本番アプリには含めない。CoreDeviceのappGroup DB直接コピーは転送エラーで未使用だが、Share Extension UIの新規2件完了表示をAppium/WDAで確認済み。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:48:00 +0900</t>
         </is>
       </c>
     </row>
@@ -542,47 +923,57 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_NORMALIZATION_AND_IPHONE_UX_GAP: 両実機で同一URL重複は確認済み。表記違い正規化とiPhone通知導線は未完了。</t>
+          <t>PASS: Android/iPhone実機で同一URL/表記違い正規化重複と見る導線PASS</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。 / PASS device partial: 2026-06-29 両実機で同一URLの重複保存を追加確認。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>PARTIAL_DEVICE_GAP: Android/iPhone実機で同一URL重複判定は確認。表記違いURLの正規化重複は未検証。iPhone手動追加の重複保存後、コード上は「このURLはすでに保存済みです」+「見る」通知を5秒表示する設計だが、Appium証跡では保存後ホームに戻り通知が見えなかった。</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>未修正: 今回は検証結果の記録のみ。iPhone重複通知/見る導線はUX差分候補として次ループで原因特定と修正対象判定が必要。</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。 / RETEST NEEDED: 表記違い正規化、iPhone重複通知「見る」、修正後の両実機再確認。</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639): 既存URL https://example.com/rinbam-device-test-20260629-1214 をACTION_SENDでShareReceiverActivityへ渡し、保存押下後に「このURLはすでに保存されています」表示を確認。証跡: artifacts/device-verification/2026-06-29/android-us004-share-duplicate-before.png/xml, android-us004-share-duplicate-after.png/xml, android-us004-share-duplicate-result.png/xml。表記違い正規化重複は未検証。</t>
+          <t>PARTIAL_FIXED_AND_ANDROID_DEVICE_VERIFIED: Android/iOS共通でURL候補抽出の大文字scheme対応を実装し、Android実機で保存+重複DB検証PASS。iPhone実機の同条件操作確認は未実施。 2026-07-03追加: iOS手動保存フローをprepareManualSave/finishPreparedManualSaveへ分離し、保存成功・重複時はManualInputSheetを閉じてから通知を出すよう修正。これにより重複通知「このURLはすでに保存済みです」/「見る」がシート裏で消えるリスクを下げた。iOS generic simulator build成功、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。物理iPhoneには04:19署名済みDebug appを上書きインストールし04:20 devicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-notification-fix.json。 2026-07-03追加: iOS ManualSaveOutcomeにcompleted分岐を追加し、タグJSON読み込み時は既存のタグ読み込み通知だけにして、保存通知を重ねないよう副作用を修正。xcodebuild generic simulator build PASS、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_UX_GAP(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8ea12d85-7105-48c3-ac0c-4b2b77650cf2): 既存URL https://example.com/rinbam-iphone-device-test-20260629-1226 を手動追加し、保存後にホームへ戻り既存1件表示のまま追加重複は見えなかった。証跡: iphone-us004-duplicate-before.png/xml, iphone-us004-duplicate-add-form.png/xml, iphone-us004-duplicate-filled.png/xml, iphone-us004-duplicate-result-after-save.png/xml。期待される「このURLはすでに保存済みです」+「見る」通知は証跡上未確認。表記違い正規化重複は未検証。</t>
+          <t>PASS(Android physical): 2026-07-03 UrlRulesのURL候補抽出をcase-insensitive化後、実機上書きインストール済みアプリで大文字HTTPS入力がtext.rinbam.localテキストカードに落ちず、normalizedUrlで1件にまとまることをDB+WALコピーで確認。さらにAndroid手動追加UIで同一normalizedUrl重複時の通知「このURLはすでに保存済みです」+「見る」押下が既存詳細へ遷移することを確認。iPhone physicalの表記違い正規化重複と重複通知「見る」は未再検証。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。正規化、HTTPS大文字、デフォルトポート、重複保存のiOS契約をURLRulesTests/URLRepositoryTestsで確認。物理iPhone UI通知は継続未検証。 2026-07-03追加: iOS手動保存フローをprepareManualSave/finishPreparedManualSaveへ分離し、保存成功・重複時はManualInputSheetを閉じてから通知を出すよう修正。これにより重複通知「このURLはすでに保存済みです」/「見る」がシート裏で消えるリスクを下げた。iOS generic simulator build成功、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。物理iPhoneには04:19署名済みDebug appを上書きインストールし04:20 devicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-notification-fix.json。 2026-07-03追加: iOS ManualSaveOutcomeにcompleted分岐を追加し、タグJSON読み込み時は既存のタグ読み込み通知だけにして、保存通知を重ねないよう副作用を修正。xcodebuild generic simulator build PASS、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>US-004は完全PASSではない。同一URL重複は両実機で進捗あり。残: 表記違いURLのnormalizedUrl重複、Android手動追加側の「見る」導線、iPhone通知/見る導線の表示確認または修正。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): 既存URL重複は2026-06-29に確認済み。2026-07-03追加確認で大文字HTTPS+デフォルトポート+fragment付き URL HTTPS://Example.COM:443/rinbam-normalize-fixed-direct-20260703003607/#frag が normalizedUrl https://example.com/rinbam-normalize-fixed-direct-20260703003607 として保存され、同じ正規化URLの小文字版 https://example.com/rinbam-normalize-fixed-direct-20260703003607 を保存してもDB上1件のまま。手動追加UIで既存URLを再保存し、重複通知「このURLはすでに保存済みです」+「見る」押下で詳細へ遷移。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-normalization-fixed-direct-after-first.png/xml, android-normalization-duplicate-before-save.png/xml, android-normalization-duplicate-after-save.png/xml, android-db-normalization-duplicate/url_saver.db*, android-manual-duplicate-snackbar-fast.png/xml, android-manual-duplicate-after-fast-open-existing.png/xml。</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-06-29 12:46:10 +0900</t>
+          <t>PARTIAL_PASS_WITH_UX_GAP(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8ea12d85-7105-48c3-ac0c-4b2b77650cf2): 既存URL https://example.com/rinbam-iphone-device-test-20260629-1226 を手動追加し、保存後にホームへ戻り既存1件表示のまま追加重複は見えなかった。証跡: iphone-us004-duplicate-before.png/xml, iphone-us004-duplicate-add-form.png/xml, iphone-us004-duplicate-filled.png/xml, iphone-us004-duplicate-result-after-save.png/xml。期待される「このURLはすでに保存済みです」+「見る」通知は証跡上未確認。表記違い正規化重複は未検証。 INSTALL/LAUNCH_ONLY: 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。 2026-07-03再確認: iPhone同一URL重複通知/見る/詳細遷移PASS。表記違い正規化重複は未検証。 2026-07-03再確認: iPhoneで HTTPS://EXAMPLE.COM:443/ が既存 https://example.com と重複扱いになり、「このURLはすでに保存済みです」/「見る」表示PASS。</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-07-03にAndroidで見つかった大文字HTTPSがテキストカード化される不具合を修正。Androidでは表記違い正規化重複と手動重複通知/見る導線まで実機確認済み。残: iPhone物理端末での表記違いURL重複、iPhone重複通知/見る導線の表示確認。iPhone実機へcom.mibu.codebridge.ios Debugビルドは上書きインストール済み。ただしAppium側usbmuxdが0件のため、iPhone物理UIでの同条件保存操作は未検証。Android/iOSのRepository回帰テストはPASS。 2026-07-03 04:20再確認: devicectlではiPhone 12にインストール/起動できるが、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723未起動、RemoteXPC 42314 timeout。このためiPhoneの重複通知「見る」実操作は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:22追加: Appium 3.5.0 serverを通常権限で起動しXCUITest session作成を再試行。RemoteXPC devices listing unavailable: tunnel registry timeout。fallback後も Unknown device or simulator UDID 00008101-00066D96340A001E でHTTP 500。ログ: artifacts/device-verification/2026-07-03-iphone-nonvideo/appium-server-retry.log。devicectl install/launchは可能だが、Appium/WDA UI操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:29追加: devicectl install/launchは成功。Appium/WDAはRemoteXPC tunnel timeout / Unknown device or simulator UDIDで継続失敗のため、iPhone物理UI操作は引き続き NOT VERIFIED on physical iPhone。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。 2026-07-03 06:11追加: iPhone手動追加の同一URL重複通知「このURLはすでに保存済みです」/「見る」/詳細遷移はAppium実機PASS。ただし表記違いURLの正規化重複までは未実施。 2026-07-03 06:16追加: iPhone physical via Appium session d4eefdfe-1201-414a-95f3-2700684a227e で HTTPS://EXAMPLE.COM:443/ を手動保存し、「このURLはすでに保存済みです」/「見る」通知を確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-normalized-duplicate-after-save.png。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:16:00 +0900</t>
         </is>
       </c>
     </row>
@@ -639,47 +1030,57 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhoneホーム/フィルター表示PASS、保存URL絞り込み操作未実施</t>
+          <t>PASS: Android/iPhone実機でホーム表示と自作タグ絞り込みPASS</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>iPhone保存済みURLを用いた絞り込み操作は未検証。Androidでは2026-07-03に自作タグクリックが即解除される不具合を修正済み。</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
+          <t>FIXED_AND_ANDROID_DEVICE_VERIFIED: Androidの自作タグチップ押下時、共通コンポーネントがonSelectService(ALL)を続けて呼んでホーム側selectedMainLocalTagIdを即nullへ戻す不具合を修正。</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): アプリ名「りんばむ」、ホーム表示、サービス/タグ系フィルタチップ、下部5アクションをXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml。保存済みURLを用いた絞り込み操作は未実施。</t>
+          <t>PASS(Android physical): ホーム4件表示から自作タグ「たな」チップ押下で紐付け済み1カードだけに絞り込まれること、カード内に自作タグチップが同じ行で表示されることをPNG/XMLで確認。iPhone保存済みURL絞り込み操作は未完了。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。iOSのサービス/自作タグ/検索フィルタ契約をServiceFilterTestsで確認。物理iPhone操作証跡は継続未検証。</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>iPhone Appium/WDAが復旧しホーム表示証跡を取得。データ作成を伴うURL一覧/絞り込み操作は次ループで非破壊手順を設計して確認する。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum をデータ保持上書きインストール後、ホーム4件表示から「たな」フィルタ押下で1件表示へ絞り込み。カード内にも「たな」「やあややた」の自作タグチップが同じ行で表示。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us005-fixed-home-before.png/xml, android-us005-fixed-after-tana.png/xml, android-db-us005-fixed/url_saver.db。</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-06-29 11:48:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): アプリ名「りんばむ」、ホーム表示、サービス/タグ系フィルタチップ、下部5アクションをXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml。保存済みURLを用いた絞り込み操作は未実施。 2026-07-03再確認: iPhone上段自作タグ「たらたらた」選択でタグ付きカード1件へ絞り込みPASS。</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Android自作タグフィルタは2026-07-03に実装修正と物理実機確認済み。iPhone側の保存済みURLフィルタ操作はAppium/usbmuxd未復旧のため未検証。動画/メディア保存設定は今回後回し。 2026-07-03 04:22追加: Appium 3.5.0 serverを通常権限で起動しXCUITest session作成を再試行。RemoteXPC devices listing unavailable: tunnel registry timeout。fallback後も Unknown device or simulator UDID 00008101-00066D96340A001E でHTTP 500。ログ: artifacts/device-verification/2026-07-03-iphone-nonvideo/appium-server-retry.log。devicectl install/launchは可能だが、Appium/WDA UI操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。 2026-07-03 06:16追加: iPhone physical via Appiumで上段自作タグ「たらたらた」を選択し、選択チップが青表示になり、該当タグ付きカード1件へ絞り込まれることを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-local-tag-filter-taratara.png。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:16:00 +0900</t>
         </is>
       </c>
     </row>
@@ -736,47 +1137,57 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で表示モード切替PASS、再起動後保持は未検証</t>
+          <t>PASS: Android/iPhone実機で表示モード切替と再起動後保持PASS</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests MainListViewModelTest.toggleEntryCardDisplayMode_updatesStore --tests ArchiveViewModelTest 成功。PASS: iOS generic simulator build成功。iOS RootView/AppChromeを@AppStorage保存へ修正。</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>物理Android/iPhoneでの表示モード切替と再起動後保持は未検証。以前のiOSは@Stateのみで再起動後保持しないギャップがあり、今回修正済み。</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>FIXED_LOCAL: iOS displayModeをEntryListDisplayMode.rawValue + @AppStorage("entryListDisplayMode")で永続化。</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PASS local retest: Android targeted unit、iOS generic build成功。物理端末再起動保持は未実施。</t>
+          <t>iPhone物理端末での再起動後保持は未検証。AndroidはDataStore保持を実機で確認済み。</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 表示モードボタンをタップし content-desc が「画像つき表示へ切り替える」へ変化。証跡: artifacts/device-verification/2026-06-29/android-pixel9a-display-toggle-after.png, android-pixel9a-display-toggle-after.xml。</t>
+          <t>FIXED_LOCAL_AND_ANDROID_DEVICE_VERIFIED: AndroidはDataStoreEntryCardDisplayModeStore、iOSは@AppStorage("entryListDisplayMode")に接続済み。Android実機でforce-stop後も表示モードが保持されることを確認。</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): 表示モードボタンをタップし、XMLで「画像なし表示へ切り替える」を確認。証跡: artifacts/device-verification/2026-06-29/iphone-ui-loop-display-toggle-after.png, iphone-ui-loop-display-toggle-after.xml。</t>
+          <t>PASS(Android physical): 表示モードボタンcontent-descが「画像つき表示へ切り替える」からタップ後「画像なし表示へ切り替える」に変化。adb force-stop後に再起動しても「画像なし表示へ切り替える」のまま保持。</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>物理端末で切替自体は確認済み。再起動後保持、Archive/Tag detail反映は次ループで確認が必要。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): 表示モード切替後、adb force-stop jp.miyamibu.urlalbum -&gt; launcher起動後も切替後状態を保持。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-display-mode-before.xml/png, android-display-mode-after-toggle.xml/png, android-display-mode-after-relaunch.xml/png。</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-06-29 12:03:48 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): 表示モードボタンをタップし、XMLで「画像なし表示へ切り替える」を確認。証跡: artifacts/device-verification/2026-06-29/iphone-ui-loop-display-toggle-after.png, iphone-ui-loop-display-toggle-after.xml。 2026-07-03再確認: iPhone表示モード切替後、アプリ終了/再起動後も保持PASS。</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Archive/Tag detailは同じentryCardDisplayModeStoreを注入していることをsource確認済み。iPhoneの@AppStorage保持はsource確認済みだが、物理iPhone再起動後保持は未確認。 2026-07-03 04:22追加: Appium 3.5.0 serverを通常権限で起動しXCUITest session作成を再試行。RemoteXPC devices listing unavailable: tunnel registry timeout。fallback後も Unknown device or simulator UDID 00008101-00066D96340A001E でHTTP 500。ログ: artifacts/device-verification/2026-07-03-iphone-nonvideo/appium-server-retry.log。devicectl install/launchは可能だが、Appium/WDA UI操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。 2026-07-03 06:17追加: iPhone physical via Appiumで表示モードボタンを押下し、ラベルが「画像なし表示へ切り替える」へ変化。terminate_app/activate_app後も同じラベルが維持され、表示モード保持PASS。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-display-mode-after-toggle.png, iphone-display-mode-after-relaunch.png。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:17:00 +0900</t>
         </is>
       </c>
     </row>
@@ -833,47 +1244,57 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で詳細からアーカイブ/復元PASS、スワイプ操作とUndo実行は未検証</t>
+          <t>PASS: Android/iPhone実機でActiveカード右スワイプ、アーカイブ通知、Undo復帰PASS</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>iPhoneの横スワイプアーカイブ/Undo実行は未検証。Androidは2026-07-03に右スワイプ、Snackbar「元に戻す」、DBのACTIVE復帰まで確認済み。</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): 詳細のアーカイブでactive一覧から消え、アーカイブ詳細でアーカイブ解除、active一覧へ復元。Undo表示は確認したが実行成功は未証明。証跡: android-us007-archive-after-tap.png, android-us007-archive-detail-open.png, android-us007-unarchive-after-tap.png。</t>
+          <t>FIXED_AND_ANDROID_DEVICE_VERIFIED: Androidはスワイプ後Snackbarの「元に戻す」を押してACTIVEへ戻ることを一時URLで確認。iPhoneは詳細アーカイブ/復元は確認済みだが横スワイプUndo未確認。2026-07-03追加: iOS ArchiveScreenをSwipeableArchivedEntryCardへ切り替え、右スワイプでアーカイブ解除、左スワイプで削除待ちへ送る配線を追加。</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 詳細のアーカイブでactive一覧から消え、アーカイブ一覧に移動、アーカイブ済み詳細で削除無効/アーカイブ解除、active一覧へ復元。スワイプ/Undo実行は未証明。証跡: iphone-us007-archive-after-tap.png, iphone-us007-archive-list.png, iphone-us007-archive-detail.png, iphone-us007-unarchive-home.png。</t>
+          <t>PASS(Android physical): 一時URLを保存後、ホームのカードを右スワイプし「アーカイブしました」「元に戻す」Snackbarを確認。元に戻す押下後、WAL込みDBコピーで同URLのrecordState=ACTIVEを確認。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。iOSの横スワイプ意図判定とAndroid閾値合わせをServiceFilterTestsで確認。物理iPhone Undo操作は継続未検証。2026-07-03追加 iOS local: xcodebuild build -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination generic/platform=iOS Simulator CODE_SIGNING_ALLOWED=NO 成功。ServiceFilterTestsのスワイプ判定5件PASS。 2026-07-03 04:10追加: devicectlで物理iPhone 12へcanonical bundle com.mibu.codebridge.ios をデータ保持の上書きインストール成功。同端末でdevicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-archive-swipe.json。ただしこれはインストール/起動証跡であり、Appium/WDAの画面操作証跡ではない。</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>この行の受入条件に含まれるスワイプ操作とUndo復帰は未完了。次ループで一時データを使い、猶予中Undoをタイミング込みで確認する。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): 一時URL https://example.com/rinbam-us007-undo-proof-202607030146 を保存し、ホームカード右スワイプでSnackbar「アーカイブしました」「元に戻す」を確認。Undo押下後、WAL込みDBで id=34 / recordState=ACTIVE を確認。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us007-undo-proof-home-before-swipe.png/xml, android-us007-undo-proof-after-swipe-before-undo.png/xml, android-us007-undo-proof-after-undo.png/xml, android-db-us007-undo-proof/url_saver.db*。</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-06-29 12:34:00 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 詳細のアーカイブでactive一覧から消え、アーカイブ一覧に移動、アーカイブ済み詳細で削除無効/アーカイブ解除、active一覧へ復元。スワイプ/Undo実行は未証明。証跡: iphone-us007-archive-after-tap.png, iphone-us007-archive-list.png, iphone-us007-archive-detail.png, iphone-us007-unarchive-home.png。 2026-07-03再確認: iPhoneでActiveカード右スワイプ、アーカイブ通知、元に戻す、復帰対象詳細表示PASS。</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AndroidのスワイプUndoは2026-07-03に一時URLでPASS。iPhoneの横スワイプUndoはAppium/usbmuxd未復旧のため未検証。動画/メディア保存設定は今回後回し。iOSアーカイブ一覧にもAndroid同様のスワイプ復元/削除配線を追加済み。ただし物理iPhoneでの実操作はAppium/usbmuxd未復旧のため未検証。 2026-07-03 04:10再確認: Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:22追加: Appium 3.5.0 serverを通常権限で起動しXCUITest session作成を再試行。RemoteXPC devices listing unavailable: tunnel registry timeout。fallback後も Unknown device or simulator UDID 00008101-00066D96340A001E でHTTP 500。ログ: artifacts/device-verification/2026-07-03-iphone-nonvideo/appium-server-retry.log。devicectl install/launchは可能だが、Appium/WDA UI操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。 2026-07-03 06:19追加: iPhone physical via Appiumで検証用example.comカードを右スワイプし、「アーカイブしました」/「元に戻す」を確認。元に戻す押下後、対象example.com詳細がactive状態で開けることを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-swipe-archive-after-right-swipe.png, iphone-swipe-archive-after-undo.png。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:19:00 +0900</t>
         </is>
       </c>
     </row>
@@ -935,42 +1356,52 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>PASS: 既存のローカル/ビルド検証に加え、2026-06-29に両実機で一時URLを使った削除猶予/Undo導線を確認。</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>過去試行ではAndroidの座標タップが5秒Undoに間に合わず復元未証明だったが、今回bounds由来のUndo中心タップで復元を確認。iPhoneもAppium/WDA連続操作で復元確認。製品ロジック上の不具合は今回未検出。</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>修正対象なし: 実機再検証で削除猶予/Undoの期待動作を確認。</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>PASS physical retest: Android Pixel 9a と iPhone 12 で削除確認文言、削除後通知「削除しました」「元に戻す」、Undo後のカード復帰を確認。</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 一時カード(保存 14:55/14:56系)で詳細削除確認「このURLは削除待ちに移動します。5秒以内なら元に戻せます。」、削除後Snackbar「削除しました」「元に戻す」、Undo後に一覧へ「保存 14:56」「保存 14:55」が復帰/残存することを確認。証跡: artifacts/device-verification/2026-06-29/us008/android-us008-delete-dialog-retry.*, android-us008-after-delete-retry.*, android-us008-after-undo-retry.*</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E, Appium/WDA, com.mibu.codebridge.ios): 一時URL https://example.com/rinbam-us008-iphone-202606291501 を追加し、詳細削除確認、削除後通知「削除しました」「元に戻す」、Undo後に「保存 15:03」のカードが一覧復帰することを確認。証跡: artifacts/device-verification/2026-06-29/us008/iphone-us008-temp-*.xml/png</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>通常端末の既存データは消さず、一時テストURLのみ使用。iPhoneはAppium/WDA、AndroidはADB/uiautomator/screencapで証跡取得。</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2026-06-29 15:07:47 +0900</t>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>通常端末の既存データは消さず、一時テストURLのみ使用。iPhoneはAppium/WDA、AndroidはADB/uiautomator/screencapで証跡取得。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-07-03 04:45:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1027,47 +1458,57 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で詳細遷移と外部で開く導線表示PASS、外部ブラウザ起動は未実行</t>
+          <t>PASS: Android/iPhone実機で詳細遷移/開く/外部ブラウザ遷移/復帰/コピー導線PASS</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): 一覧カードタップで詳細へ遷移し、開く/コピー/アーカイブ/削除/メモ編集/metadata失敗表示を確認。外部ブラウザ起動は未実行。証跡: android-us009-detail-open.png。</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): 一覧カードタップで詳細へ遷移し、開く/コピー/アーカイブ/削除/メモ編集/metadata失敗表示を確認。外部ブラウザ起動は未実行。証跡: iphone-us009-detail-open.png。</t>
+          <t>PASS(Android physical): 詳細画面の「開く」を押下してChromeへ遷移し、example.com表示を確認。Backでりんばむ詳細へ戻り、「コピー」押下後に「コピーしました」通知を確認。iPhone外部ブラウザ起動はAppium側usbmuxd 0件のため未再検証。</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>外部ブラウザ起動は別アプリ遷移を伴うため未実行。次ループで戻り動作も含めて確認する。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): 一覧カードから詳細に入り、開く/コピー/アーカイブ/削除/メモ編集/metadata失敗表示を確認。2026-07-03追加で「開く」押下によりChromeへ遷移しexample.com表示、Backで詳細へ復帰、「コピー」押下で「コピーしました」通知を確認。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us009-current.png/xml, android-us009-after-open.png/xml, android-us009-after-back.png/xml, android-us009-after-copy.png/xml。 2026-07-03追加: Android保存済みメディア詳細で「メディアを開く」を押下し、ビューアにタイトル、閉じるボタン、黒背景動画プレビュー、ファイル名表示が出ることを物理実機で確認。証跡: artifacts/device-verification/2026-07-03-android-media-viewer-parity/android-detail-iana-after-wrapcontent-fix.png/xml, android-media-viewer-open-after-wrapcontent-fix-valid.png/xml。 2026-07-03再確認: 最新Androidメディアビューアでタイトル、閉じるボタン、黒背景プレビュー、ファイル名表示PASS。証跡: artifacts/device-verification/2026-07-03-android-media-viewer-recheck/android-media-viewer-after-filename-fix.png/xml。</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-06-29 12:34:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 334b9c4b-b013-4a53-aa5f-9394f01adc7f): 一覧カードから詳細へ遷移し、開く/コピー/アーカイブ/削除/メモを編集/自作タグ/共有タグを確認。詳細の「開く」押下でSafari(com.apple.mobilesafari)へ遷移し、Safari表示後にりんばむを再アクティブ化すると同じ詳細画面へ戻ることを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us009-detail-before-open.png/xml, iphone-us009-after-open-safari.png/xml, iphone-us009-after-reactivate-detail.png/xml。</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>iPhoneの外部ブラウザ起動とアプリ復帰まで実機確認済み。動画/メディアresolver設定と指定SNSリンクの保存検証はユーザー指示により後回し。Android再確認はユーザー指示により後回し。</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:55:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1124,47 +1565,57 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でタイトル編集保存PASS、Undo実行は未検証</t>
+          <t>PASS: Android/iPhone実機でタイトル編集保存とUndo復帰PASS</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): タイトル編集UIを開き Rinbam Device Title を保存、詳細に反映。Undo表示は確認したが実行は未証明。証跡: android-us010-title-edit-open.png, android-us010-title-saved.png。</t>
+          <t>FIXED_AND_ANDROID_DEVICE_VERIFIED: Androidでタイトル保存Snackbarの「元に戻す」を押し、DB上のuserTitleが元のNULLへ戻ることを確認。iPhone Undoは未確認。</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): タイトル編集UIを開き Rinbam iPhone Title を保存、詳細に反映。Undo通知は取得時点で確認できず、Undo実行は未証明。証跡: iphone-us010-title-edit-open.png, iphone-us010-title-saved.png。</t>
+          <t>PASS(Android physical): 一時URL詳細でタイトルをUndo Proof Titleに変更し、「タイトルを保存しました」「元に戻す」を確認。Undo押下後、WAL込みDBでuserTitle=&lt;NULL&gt;を確認。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。iOSのタイトル/メモ正規化契約をURLRepositoryTestsで確認。物理iPhone Undo操作は継続未検証。</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>タイトルUndoは次ループで保存直後に通知捕捉と実行確認を行う。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 一時URL https://example.com/rinbam-us007-undo-proof-202607030146 の詳細でタイトル編集を開き、Undo Proof Titleを保存。Snackbar「タイトルを保存しました」「元に戻す」を確認し、Undo押下後にDBで userTitle=&lt;NULL&gt; を確認。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us010-undo-editor-open.png/xml, android-us010-undo-editor-filled.png/xml, android-us010-undo-after-save-before-undo.png/xml, android-us010-undo-after-undo.png/xml, android-db-us010-undo/url_saver.db*。</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-06-29 12:34:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session d4eefdfe-1201-414a-95f3-2700684a227e): 詳細画面でタイトルを一時名 UndoTemp0703 に編集保存し、保存直後の「元に戻す」を押下後、タイトルが Example Domain に復帰することを確認。検証前に残っていた一時名 Undo0619 も Example Domain へ復旧済み。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-title-restored-example-domain.png, iphone-title-undo-restored-example-domain.png。</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>タイトル編集保存とUndo復帰はAndroid/iPhone実機で確認済み。</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:35:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1226,42 +1677,52 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>現時点でメモ編集の実機確認上の未解決エラーなし。CoreSimulator/XCTest不整合はこの行の完了判定には使わず、物理実機証跡を正とする。</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>修正対象なし: Android/iPhone物理実機でメモ編集保存が期待通り動作することを確認済み。</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>PASS physical: Androidで Android device memo 1216、iPhoneで iPhone device memo 1228 を保存し、詳細画面に反映されることを確認。</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): メモ編集UIを開き Android device memo 1216 を保存、詳細に反映。証跡: android-us011-memo-edit-open.png, android-us011-memo-saved.png。</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): メモ編集ダイアログを開き iPhone device memo 1228 を保存、詳細に反映。証跡: iphone-us011-memo-edit-open.png, iphone-us011-memo-saved.png。</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>一時URLのメモ保存のみ確認。既存ユーザーデータは削除/リセットしていない。</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026-06-29 12:34:00 +0900</t>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>一時URLのメモ保存のみ確認。既存ユーザーデータは削除/リセットしていない。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-07-03 04:45:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1318,47 +1779,57 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でmetadata失敗状態表示PASS、成功取得は未検証</t>
+          <t>PASS: Android/iPhone実機でmetadata失敗状態表示と成功取得READYを確認</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>PASS: iOS MetadataStatusTextTests 5件成功し、BackgroundTaskRunnerの成功/失敗/expiration完了契約を確認。Android metadata系は既存unit/buildで通過済み。</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。 iOS実機BGTaskSchedulerの実スケジュール発火、Android WorkManager実機発火は未検証。</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PASS local retest: iOS MetadataStatusTextTests成功。実機バックグラウンド発火は未実施。</t>
+          <t>iPhoneのmetadata成功取得は未検証。Androidは失敗状態表示とIANAページの成功取得READYを物理実機DBで確認済み。</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PARTIAL(Android physical Pixel 9a 55211JEBF16639): example.com 一時URLで一覧/詳細に 自動取得できません と HTTP_404 系説明、再取得導線表示を確認。成功取得は未検証。証跡: android-us001-after-save-final.png, android-us009-detail-open.png。</t>
+          <t>DEVICE_VERIFIED_ANDROID: Androidはmetadata失敗表示と成功取得READYを確認済み。iPhone成功取得はAppium/usbmuxd未復旧のため未検証。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 67fd5d37-d355-4a41-8f4a-c0949754bfce): example.com 一時URLで一覧/詳細に 自動取得できません、ページが見つかりませんでした (HTTP_404)、再取得導線表示を確認。成功取得は未検証。証跡: iphone-us001-after-save-final.png, iphone-us009-detail-open.png。</t>
+          <t>PASS(Android physical): example.com系の失敗状態表示に加え、IANAの通常Webページを一時保存し、WAL込みDBでmetadataState=READY、fetchedTitle=IANA-managed Reserved Domainsを確認。iPhone成功取得は未検証。</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>iOS BGTaskScheduler/BackgroundTaskRunner coverage added 2026-06-29. 実機では失敗状態表示のみ確認。成功取得と再取得実行はUS-013側で継続確認する。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): example.com一時URLで一覧/詳細に自動取得失敗状態を確認済み。2026-07-03追加で https://www.iana.org/domains/reserved?rinbam_meta=202607030220 を共有保存し、20秒待機後のWAL込みDBで id=35 / metadataState=READY / fetchedTitle=IANA-managed Reserved Domains を確認。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us012-meta-share-before-save.png/xml, android-us012-meta-share-after-save.png/xml, android-us012-meta-home-immediate.png/xml, android-us012-meta-home-after-wait.png/xml, android-db-us012-meta/url_saver.db*。</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-06-29 12:34:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session d4eefdfe-1201-414a-95f3-2700684a227e): metadata失敗状態表示は既存証跡で確認済み。2026-07-03再確認で https://www.iana.org/domains/reserved を手動保存し、ホームカードに www.iana.org、タイトル「IANA-managed Reserved Domains」、本文要約「Certain domains are set aside...」が表示されることを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-metadata-success-iana-home.png/xml。</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>metadata失敗表示と成功取得表示はAndroid/iPhone実機で確認済み。</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:40:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1415,47 +1886,57 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_INTERNAL_CONTRACT_GAP: 両実機で失敗metadataの再取得UI導線と押下を確認。再enqueue/updatedAt不変は未検証。</t>
+          <t>PARTIAL_PASS_WITH_DEVICE_GAP: 両実機で失敗metadataの再取得UI導線と押下を確認。Android/iOSとも再取得・updatedAt不変のRepository契約テストPASS。</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。 / PASS device partial: 2026-06-29 Android/iPhone実機で失敗metadata詳細と再取得ボタン表示、押下操作を確認。</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>PARTIAL_DEVICE_GAP: 両実機で「再取得」ボタン表示と押下は確認。example.comのHTTP_404/ページ未検出状態のため、成功metadata取得は未確認。UI証跡だけでは再enqueue実行、WorkManager/MetadataCoordinator処理、metadata更新だけでupdatedAtを変えない契約は証明できない。</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>未修正: 今回は実機導線の確認と未検証内部契約の記録のみ。UI上の明確なクラッシュ/操作不能は未検出。必要ならログ/DB観測付きの非破壊検証を追加する。</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。 / RETEST NEEDED: 成功取得可能URLでのmetadata更新、再enqueueログ/DB観測、updatedAt不変確認。</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>PARTIAL_FIXED_WITH_CONTRACT_TESTS: AndroidはretryMetadataがFAILED/UNAVAILABLE/不足READY/ソーシャルbadge不足をPENDINGへ戻しschedulerへenqueueし、十分なREADY/PENDINGは再取得しないRepositoryテストを追加済み。iOSも同等のURLRepositoryTestsを追加。metadata更新だけでupdatedAtを変えない契約は両OS既存/継続テストで確認。</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>PASS(Android local): ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.RepositoryBehaviorTest.retryMetadata_acceptsFailedUnavailableAndReadyWithoutFetchedContent --tests jp.mimac.urlsaver.RepositoryBehaviorTest.metadataUpdate_doesNotChangeUpdatedAt 成功。PASS(iOS compile): xcodebuild build-for-testing -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination generic/platform=iOS Simulator CODE_SIGNING_ALLOWED=NO 成功。NOT RUN(iOS selected XCTest): 2026-07-03に既存Simulator id=2021719A-3EE0-4D14-8EFF-39758C799300で再試行したが、Simulator device failed to launch com.mibu.codebridge.ios / Application failed preflight checks / Busy で失敗。存在しない iPhone 16 指定はdestination not found。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。iOSのretryMetadataとmetadata更新時updatedAt不変契約をURLRepositoryTestsで実行確認。物理UIの再取得結果確認は継続未検証。</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639): 既存URL詳細で「このURLは自動取得できません」「ページが見つからないため、自動取得できませんでした。」と「再取得」ボタンを確認し、再取得をタップ。短時間後も同じ404失敗表示。証跡: artifacts/device-verification/2026-06-29/android-us013-detail-before-retry.png/xml, android-us013-after-retry-tap.png/xml, android-us013-after-retry-settled.xml。再enqueue/updatedAt不変は未検証。</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>PARTIAL_PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session c5da0df9-c429-41d4-acc2-c82b0575b95c): 既存URL詳細で「このURLは自動取得できません」「ページが見つかりませんでした (HTTP_404)」と「再取得」ボタンを確認し、再取得をタップ。短時間後も同じ404失敗表示。証跡: iphone-us013-detail-before-retry.png/xml, iphone-us013-after-retry-tap.png/xml, iphone-us013-after-retry-settled.xml。再enqueue/updatedAt不変は未検証。</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>US-013は実機UI導線の確認は前進。完全PASSには、成功取得可能URLまたはDB/ログ観測で再enqueueとupdatedAt不変を確認する必要がある。</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>2026-06-29 12:52:04 +0900</t>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>US-013は実機UI導線の確認に加え、Android内部契約はテストで固定済み。iOS内部契約は2026-07-03にURLRepositoryTestsで実行PASS。動画/メディア設定はユーザー指示により後回し。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-07-03 04:45:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1512,47 +1993,57 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_TAG_DELETE_AND_DUPLICATE_GAP: 両実機でローカルタグ作成とURLへの割当は確認。削除時関連付け解除、重複処理、タグ別件数は未確認。</t>
+          <t>PASS: Android/iPhone実機でタグ作成/重複/削除/件数表示/管理UI契約PASS</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>store_console</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>未完了範囲: タグ削除時の関連付け解除、重複タグ名/既割当時の文言、タグ別URL件数表示は今回未確認。iPhoneではタグ追加後にキーボード表示中のシートを閉じる操作がAppiumで安定せず、詳細画面へ戻した後の表示確認は未完了。</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>修正対象未確定: Android/iPhoneともローカルタグ作成・割当の実機導線は動作。iPhoneのタグ編集シート閉じ操作は追加調査対象。削除/重複/件数表示は次回以降の検証対象。</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Android physical retest PARTIAL_PASS: 詳細タグ欄 -&gt; 編集 -&gt; 新しいタグ -&gt; タグを作成して追加で、現在のタグと詳細タグ欄に作成タグが表示。iPhone physical retest PARTIAL_PASS: 詳細タグ欄 -&gt; 編集 -&gt; 新しいタグ -&gt; タグを作成して追加で、現在のタグに us014-ios-1314 が表示。削除/重複/件数表示は未実施。</t>
+          <t>未完了範囲: iPhone側のタグ管理削除実行、iPhone側の重複タグ名/既割当時文言、iPhone側のタグ別URL件数の物理UI確認。Androidはタグ管理のゴミ箱アイコンのみ表示、一時タグ削除、件数表示、重複/既割当契約を2026-07-03に確認済み。</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum 1.0.13/13): 既存URL詳細でタグ欄「まだタグは付いていません」と編集ボタンを確認。タグ編集シートで新規タグを作成して追加し、「現在のタグ」に作成タグが表示、閉じた後の詳細タグ欄にも表示を確認。証跡: android-us014-detail-start.png/xml, android-us014-tag-editor-open.png/xml, android-us014-tag-name-entered.png/xml, android-us014-after-create-assign.png/xml, android-us014-detail-after-tag.png/xml。削除/重複/件数表示は未確認。</t>
+          <t>PARTIAL_DEVICE_VERIFIED: Android/iPhoneともローカルタグ作成・割当の実機導線は動作。Androidはタグ管理のゴミ箱アイコンのみ表示、一時タグ削除実行、既存タグの件数表示、重複/既割当Repository契約まで確認済み。iPhone削除/重複/件数表示は追加確認対象。 2026-07-03追加: iOS ManualSaveOutcomeにcompleted分岐を追加し、タグJSON読み込み時は既存のタグ読み込み通知だけにして、保存通知を重ねないよう副作用を修正。xcodebuild generic simulator build PASS、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 31809d80-ed0b-4331-8c1f-fc32cc1ad527): 既存URL詳細でタグ欄「まだタグは付いていません」とローカルタグ編集ボタンを確認。タグ編集シートで us014-ios-1314 を入力し「タグを作成して追加」を実行、「現在のタグ」に us014-ios-1314 と「外す」が表示。証跡: iphone-us014-detail-tags-visible.png/xml, iphone-us014-tag-editor-open.png/xml, iphone-us014-tag-name-entered.png/xml, iphone-us014-after-create-assign.png/xml。キーボード表示中のシート閉じ/詳細戻り表示、削除/重複/件数表示は未確認。</t>
+          <t>PASS(Android physical): タグ管理シートで削除は「削除」文字なしのゴミ箱アイコンのみ、既存タグ「やあややた」「たな」に各1件表示を確認。検証用一時タグ「０２０９」は作成後に削除済み。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.TagRepositoryTest.localTagDuplicateAndAlreadyAssignedResults_areExplicit 成功し、既存タグ名Duplicateと同一URL再割当AlreadyAssignedを固定。iPhone側は未完了。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。iOSのローカルタグ作成先頭追加、並び替え、作成/割当ライフサイクル契約をURLRepositoryTestsで確認。物理iPhone削除/重複UIは継続未検証。 2026-07-03追加: iOS ManualSaveOutcomeにcompleted分岐を追加し、タグJSON読み込み時は既存のタグ読み込み通知だけにして、保存通知を重ねないよう副作用を修正。xcodebuild generic simulator build PASS、URLRulesTests 22件+ServiceFilterTestsスワイプ5件 PASS。 2026-07-03 04:29追加: iOS ManualSaveOutcome.completed副作用修正版を物理iPhone 12へ上書きインストールし、devicectl launch成功。Bundle ID com.mibu.codebridge.ios、アプリ表示 りんばむ 1.0.11 (11)。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-manual-completed-fix.json。これはinstall/launch証跡であり、Appium/WDA UI操作証跡ではない。</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Androidは端末キーボード変換により入力タグ名が全角混じりになったが、作成・割当・詳細表示は確認済み。US-014完全PASSには、両実機で重複タグ名/既割当時の文言、タグ削除時の関連付け解除、タグ管理/タグ詳細でURL件数表示を確認する必要がある。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 既存URL詳細でのタグ作成/割当証跡は継続有効。2026-07-03追加でホーム下部「タグ」からタグ管理シートを開き、削除は赤いゴミ箱アイコンのみで「削除」文字がカード内に表示されないことを確認。さらに検証用一時タグ「０２０９」を作成し、タグ管理のゴミ箱 -&gt; 確認「削除する」で削除、Snackbar「タグを削除しました」、DBで一時タグ行なしを確認。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us014-tag-manager-open2.png/xml, android-us014-numeric-create-filled.png/xml, android-us014-numeric-after-create.png/xml, android-us014-fullwidth-manager-open.png/xml, android-us014-fullwidth-delete-confirm2.png/xml, android-us014-fullwidth-after-delete4.png/xml, android-db-us014-fullwidth-delete4/url_saver.db*。 2026-07-03追加確認: ホーム下部「タグ」からタグ管理を開き、既存タグ「やあややた」「たな」がカード状に表示され、各タグは件数「1件」と赤いゴミ箱アイコンのみで、可視テキストの「削除」なし。Accessibility用content-desc=削除は保持。証跡: artifacts/device-verification/2026-07-03-us014-tag-management/android-tag-management-after-tap.png/xml。 2026-07-03追加確認: ホーム下部「タグ」からタグ管理を開き、既存タグ「やあややた」「たな」がカード状に表示され、各タグに「1件」が表示されること、削除はcontent-descのみで文字ラベルなしのゴミ箱アイコンであることを確認。証跡: artifacts/device-verification/2026-07-03-us001-016-continuation/android-us014-current-tag-manager-open.png/xml。</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-06-29 13:18:39 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 334b9c4b-b013-4a53-aa5f-9394f01adc7f): タグ管理でタグ名、件数、ゴミ箱アイコンのみを表示し、URL/JSONは非表示。tmp0703tagを作成後、修正版で同名作成が「このタグはすでにあります」となり重複作成されないことを確認。tmp0703tagのゴミ箱から削除確認「タグを削除」「tmp0703tag」を表示し、URL/JSONなしで削除、タグ列から消えることを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-tag-management-no-json-trash-only.png/xml, iphone-tag-duplicate-after-fix.png/xml, iphone-tag-management-tmp-trash-only-before-delete.png/xml, iphone-tag-delete-confirm-no-url-json.png/xml, iphone-tag-after-delete-tmp-gone.png/xml。</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>iPhone側の重複名作成が既存タグを新規作成成功扱いにしていたため、URLSaverAppModel.createLocalTagで既存localTagsと正規化名を比較し、重複時は作成せず「このタグはすでにあります」を表示するよう修正。Android側再確認はユーザー指示により後回し。</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-07-03 06:50:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1609,47 +2100,57 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>PHYSICAL_PASS_WITH_ANDROID_LOCAL_TAG_COPY_UX_GAP: 両実機でタグ選択/タグ詳細から対象URLだけの一覧と詳細遷移を確認。Androidローカルタグ詳細の共有タグ文言はUX不整合。</t>
+          <t>PASS: 両実機でタグ絞り込み/タグ詳細系導線PASS。Androidローカルタグ詳細の共有タグ文言混入は現行コードで解消済み。</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Android UX: ローカルタグ詳細でも「クラウド共有を使うにはサインインが必要です」「この共有タグを削除」など共有タグ文言が表示される。iPhoneはタグチップ選択で対象URL1件に絞り込みできるが、独立したタグ詳細画面ではなくホーム一覧フィルタとして実装されている。</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>未修正: Androidのローカルタグ詳細文言をローカルタグ向けに分岐する改善候補。iPhoneは現行設計上フィルタ導線で機能達成。</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Android physical PASS: DB読取で tagId=1/entryId=4 の割当を確認後、urlsaver://tag/1 でタグ詳細を開き、タグ名、1件表示、対象URLカード、カードから詳細遷移を確認。iPhone physical PASS: Appium/WDAで us014-ios-1314 チップを横スクロール後にタップし、表示URLが2件から対象1件へ絞り込まれ、カードから詳細へ遷移することを確認。</t>
+          <t>現行コード確認では、ローカル自作タグ詳細は isLocalTag 分岐により「自作タグ」文言、共有タグ専用のクラウドサインイン/共有/参加者表示はSYNCED時だけ表示。過去台帳に残っていたAndroid共有タグ文言混入は現行コードでは再現対象なし。</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PASS on physical Android Pixel 9a 55211JEBF16639: artifacts/device-verification/2026-06-29/us015/android-us015-tag-detail.xml/png と android-us015-tag-detail-open-entry.xml/png。</t>
+          <t>FIXED_LOCAL_AND_DEVICE_SUPPORTED: TagDetailScreen.kt は tag.scope == LOCAL_ONLY / SYNCED で文言とクラウド導線を分岐済み。自作タグ削除は「この自作タグ」、空状態も「この自作タグにはまだURLがありません」。</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>PASS source/current device context: 2026-07-03のAndroidホーム実機XMLで自作タグが上段同一行に表示されることを確認。TagDetailScreen.kt sourceでローカルタグ/共有タグ文言分岐を確認。既存の2026-06-29両実機タグ絞り込み/詳細証跡も継続参照。</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): ホーム上段で自作タグ「やあややた」「たな」が + / すべて と同一LazyRow内に表示。証跡: artifacts/device-verification/2026-07-03-nonvideo-continued/android-home-after-back.png/xml。タグ詳細文言は source確認でLOCAL_ONLY/SYNCED分岐済み。 2026-07-03 04:13追加: Android物理Pixel 9aでホームを再確認。自作タグは上段の＋/タグ/すべてと同じ横列に表示、共有タグは「共有タグ」見出し下の別セクションとして表示。証跡: artifacts/device-verification/2026-07-03-android-nonvideo/android-home-after-nonvideo.png と .xml。</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>PASS on physical iPhone 12 UDID 00008101-00066D96340A001E via Appium/WDA: artifacts/device-verification/2026-06-29/us015/iphone-us015-after-tag-tap-source.json と iphone-us015-tag-open-entry-source.json。</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>非破壊確認のみ。Android DBは run-as で url_saver.db/-wal/-shm を読み取りコピーし、タグ割当を現在状態として照合。iPhoneはAppium session 2a3a89b1-ee18-4c91-8099-a11a7b00dbbf。</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>2026-06-29 13:27:31 +0900</t>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>iPhoneは従来どおりタグチップ選択による絞り込み導線。Androidの「自作タグが別列」指摘は現行実機では再現せず、共有タグ行とは別に自作タグがサービスフィルタ同一行へ表示されている。 2026-07-03 04:13追加: Android物理Pixel 9aでホームを再確認。自作タグは上段の＋/タグ/すべてと同じ横列に表示、共有タグは「共有タグ」見出し下の別セクションとして表示。証跡: artifacts/device-verification/2026-07-03-android-nonvideo/android-home-after-nonvideo.png と .xml。 2026-07-03 04:43追加: 動画/メディアresolver設定をユーザー指示で後回しにした状態で、Android ./gradlew testDebugUnitTest はBUILD SUCCESSFUL。iOSはURLRulesTests/URLRepositoryTests/ServiceFilterTests/SharedTagCloudLiveSyncTests(testInviteFlow...) を実行し59件PASS、共有タグlive inviteは確認済みアカウント未設定のため1件skip。</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-07-03 04:45:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1696,57 +2197,67 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Android: SharedTagSyncRepositoryTest; iOS: SharedTagCloudLiveSyncTests(環境依存)</t>
+          <t>Android: SharedTagSyncRepositoryTest; iOS: SharedTagCloudLiveSyncTests(環境依存); 実機: サインイン案内/共有タグ移行導線</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>本番Supabase設定時のみ有効、未設定releaseでは非表示/無効</t>
+          <t>本番Supabase設定時のみ有効。未サインイン時はサインイン案内を出す。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PARTIAL_PASS_WITH_SUPABASE_AUTH_LIVE_GAP: Android/iPhone実機で未サインイン時の共有タグ+がサインイン案内へ進むことを確認。共有タグ移行本体は本番Supabase認証状態が必要。</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
+          <t>BLOCKED_EXTERNAL</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>supabase_auth;store_console</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>PASS: ./gradlew assembleDebug/testDebugUnitTest、iOS generic build、canonical story tracker verification 成功。過去connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>共有タグ移行本体は本番Supabaseサインイン/同期状態が必要。iPhoneは実機インストール/起動済みだが、Appium/WDAがusbmuxd 0件のためUI操作証跡は未復旧。Androidは未サインイン時に共有タグ作成フォームを出していたが、2026-07-03にサインイン案内へ修正済み。</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>PARTIAL_FIXED_ANDROID_DEVICE_VERIFIED: Androidの共有タグ+押下時、未サインインなら作成ダイアログではなくプロフィール/サインイン画面を開くよう修正。iOSは既存SharedTagCreateSheet内で未サインイン時にサインイン案内を出す構造をsource確認。 2026-07-03 04:37追加: iOS SharedTagCloudLiveSyncTestsのハーネスを修正し、Supabase URLだけでなくanon keyも環境変数/設定ファイル/Info.plistから読むようにした。これにより固定dev-anon-keyによるInvalid API key失敗を解消。 2026-07-03 04:40追加: iOS共有タグライブ招待テストを拡張し、URLSAVER_LIVE_SHARED_TAG_OWNER_EMAIL/PASSWORD と URLSAVER_LIVE_SHARED_TAG_COLLABORATOR_EMAIL/PASSWORD がある場合は新規signUpではなく既存確認済みアカウントでsignInして招待フローを検証できるようにした。</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS(Android physical): 共有タグ行の+押下後、プロフィール画面へ遷移し「共有タグに参加するにはサインインが必要です」「Googleで続ける」メール/パスワード欄を表示。PASS local: verify_mobile_ui_contract.py、assembleDebug成功。残: 共有タグ移行本体のSupabase live認証/同期とiPhone Appium UI操作。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。2026-07-03追加 local iOS: xcodebuild test -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination platform=iOS Simulator,id=2B32672C-37D7-418A-9BD9-5F868DC91130 -only-testing URLRulesTests/URLRepositoryTests/ServiceFilterTests は57 tests PASS。iOSの権限/共有キャッシュ系の近接契約はURLRulesTests/URLRepositoryTestsで確認。本番Supabase認証付き移行本体は継続未検証。 2026-07-03 04:37追加: xcodebuild test -only-testing:URLSaveriOSTests/SharedTagCloudLiveSyncTests/testInviteFlowLetsSecondIOSClientJoinAndReadSharedURL はTEST SUCCEEDED。結果は1 test skippedで、本番Supabase Authが新規テストユーザーにメール確認を要求するため「Live Supabase requires email confirmation for newly-created test users.」としてskip。Invalid API keyは再発せず、次の本番同期確認には確認済みテストアカウントまたはメール確認フローの実操作が必要。 2026-07-03 04:40追加: xcodebuild test -only-testing:URLSaveriOSTests/SharedTagCloudLiveSyncTests/testInviteFlowLetsSecondIOSClientJoinAndReadSharedURL はTEST SUCCEEDED。現環境は確認済みowner/collaboratorアカウント未設定のため、新規作成が本番メール確認必須で1 skipped。確認済み2アカウントを設定すれば同テストで本番共有タグ招待/参加/URL参照を完走できる。</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>外部Supabaseは資格情報なしでは未検証</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum v1.0.13): 共有タグ行の+押下で、旧「共有タグを作成」フォームではなくプロフィール/サインイン画面へ遷移。「共有タグに参加するにはサインインが必要です」「Googleで続ける」メール/パスワード欄を確認。共有タグ移行本体はSupabaseサインインが必要なため未実行。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-us016-before-shared-plus.png/xml, android-us016-after-shared-plus.png/xml, android-us016-fixed-after-shared-plus.png/xml。</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 334b9c4b-b013-4a53-aa5f-9394f01adc7f): ホーム共有タグ行の+を押下し、「共有タグを作成」シートで「共有タグを作るにはサインインが必要です」「共有タグはクラウド同期を使うため、先に共有タグクラウド画面でサインインしてください。」「サインインへ」ボタンを確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us016-shared-tag-plus-signin-required.png/xml。</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>未サインイン時の共有タグ入口はAndroid/iPhone実機でサインイン案内を確認済み。共有タグ移行本体の完了には、本番Supabase認証済み状態、実共有タグ/URL同期、招待/参加のlive確認が必要。Android再確認はユーザー指示により後回し。</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:00:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1803,47 +2314,57 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>PHYSICAL_PARTIAL_PASS_WITH_INVITE_UX_GAPS: 両実機で urlsaver://invite と https://miyamibu.xyz/invite が招待確認導線へ入ることを確認。Android HTTPSはローディング継続、iPhoneはraw error露出。実招待作成/参加は未検証。</t>
+          <t>PHYSICAL_PARTIAL_PASS_WITH_LIVE_INVITE_GAP</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console;public_web</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Android HTTPS invite: 30秒以上「招待リンクを確認しています」から進まず、無効/失敗状態へ遷移しない。iPhone invalid invite: 「invalid_or_expired_invite」のraw errorが画面に露出し日本語UXになっていない。実招待作成/acceptは未検証。</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>未修正: 今回は検証・記録のみ。修正候補はAndroid invite previewのタイムアウト/失敗表示、iOS remote errorの日本語マッピング。</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>今回の再検証: Android physical Pixel 9aで urlsaver://invite は無効表示PASS、https inviteはローディング継続FAIL。iPhone physical + Appium/WDAで両形式とも招待確認画面遷移PASS、invalid raw error表示UX_FAIL。</t>
+          <t>実招待作成/acceptはSupabase liveユーザー状態が必要なため未検証。iPhone実機のinvalid raw error修正後再確認はAppium/usbmuxd復旧待ち。</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PHYSICAL_PARTIAL: Pixel 9a 55211JEBF16639 / jp.miyamibu.urlalbum v1.0.13。urlsaver://invite/codex-invalid-us017-20260629 は「招待リンクが無効か期限切れです」表示。https://miyamibu.xyz/invite/codex-invalid-us017-https-20260629 は招待確認画面へ入るが30秒以上ローディング継続。証跡: artifacts/device-verification/2026-06-29/us017/android-us017-*.png/xml</t>
+          <t>FIXED_LOCAL: Android招待プレビューに12秒タイムアウトを追加し、HTTPS inviteでローディング継続しないようにした。iOSは invalid_or_expired_invite など既知raw errorを日本語文言へ正規化。</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PHYSICAL_PARTIAL: iPhone 12 UDID 00008101-00066D96340A001E / com.mibu.codebridge.ios v1.0.11 / Appium WDA session 1bf0b8f3-5c1a-49c8-8bf3-8f672e3ea7b0。urlsaver://invite と https://miyamibu.xyz/invite は招待確認画面へ遷移。無効時に「招待リンクを確認できませんでした」+ raw `invalid_or_expired_invite` 表示。証跡: artifacts/device-verification/2026-06-29/us017/iphone-us017-*.png/json</t>
+          <t>PASS: ./gradlew assembleDebug testDebugUnitTest --tests SharedTagAuthViewModelTest --tests ShareReceiverActivityEntrypointTest 成功。PASS: xcodebuild generic iOS Simulator build 成功。PASS Android physical: HTTPS無効招待が「招待リンクが無効か期限切れです」表示へ遷移。iPhone物理再確認はAppium/usbmuxd未復旧のため未実施。</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>US-017はDeep Link受信/画面遷移は両実機で確認済み。実際の有効招待作成・参加・権限同期はSupabase liveユーザー状態が必要なため未完了。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): https://miyamibu.xyz/invite/codex-invalid-us017-timeout-20260703 を開き、15秒後にローディングではなく「招待リンクが無効か期限切れです」を確認。証跡: artifacts/device-verification/2026-07-03-us017-invite-ux/android-https-invalid-after-timeout.png/xml。urlsaver://invite無効表示の既存PASS証跡も継続有効。</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-06-29 14:49:26 +0900</t>
+          <t>PARTIAL(source/build fixed, physical retest pending): iOS SharedTagCloudError.userMessageで invalid_or_expired_invite / invalid invite / expired invite を「招待リンクが無効か期限切れです」へ正規化。generic iOS Simulator build成功。物理iPhoneの再操作証跡はAppium/usbmuxd 0件のため未取得。</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Deep Link受信/画面遷移は既存の両実機証跡で確認済み。無効リンクUXはAndroid物理PASS、iOSはsource/build修正済み。実際の有効招待作成・参加・権限同期はSupabase liveサインインが必要なためUS-018/US-032側で追跡。</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:59:28 +0900</t>
         </is>
       </c>
     </row>
@@ -1900,47 +2421,57 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PARTIAL_PASS_WITH_AUTH_LIVE_GAP: Android実機で未ログイン時の共有タグサインイン案内PASS。共有タグ同期/グループ作成編集の本番Auth/Supabase完了確認は未完了。</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>PASS: iOS MetadataStatusTextTests 5件成功。SharedTagCloud migrationのdisplay_name追加をaddColumnIfMissingへ変更し、重複カラムログが消えたことを/tmp/rinbam-metadata-test.logで確認。</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>物理端末での共有タグ同期/グループ同期、Supabase live syncは未検証。iOS simulatorではApp Group entitlement警告とCoreSimulator WebCore/WebKit重複クラス警告が残るが、display_name重複カラムログは解消。</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>FIXED_LOCAL: SharedTagCloud migrationのtry? ALTER TABLEをSQLiteDatabase.addColumnIfMissingへ置換し、既存DBでの冪等性を改善。</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>PASS local retest: xcodebuild test -only-testing:URLSaveriOSTests/MetadataStatusTextTests 成功、重複display_name migrationログなし。</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: 共有タグ/グループ同期は未検証。</t>
+          <t>PASS local retest: xcodebuild test -only-testing:URLSaveriOSTests/MetadataStatusTextTests 成功、重複display_name migrationログなし。 2026-07-03 Android physical: 未ログイン共有タグ+からサインイン案内表示PASS。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 共有タグ作成導線で未ログイン時のサインイン案内を確認。「共有タグを作るにはサインインが必要です」「サインインへ」を表示。プロフィール/認証画面側にメールアドレス、パスワード、サインイン要素が出ることも確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。実共有タグ同期はAuth/Supabase live未検証。</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>iOS shared tag display_name migration idempotency fixed 2026-06-29.</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): ホームの共有タグ行「+」を押すとプロフィール/サインイン画面へ遷移し、「共有タグに参加するにはサインインが必要です」「Googleで続ける」「メールアドレス」「パスワード」が表示されることを確認。共有タグの本番同期/作成/招待参加はSupabase/Auth live環境のため未完了。証跡: artifacts/device-verification/2026-07-03-us018-shared-tag-signin/android-home-before-shared-tag-plus.png/xml, android-shared-tag-plus-result.png/xml。</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-06-29 01:02:48 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 共有タグ作成導線で未ログイン時のサインイン案内を確認。「共有タグを作るにはサインインが必要です」「サインインへ」を表示。プロフィール/認証画面側にメールアドレス、パスワード、サインイン要素が出ることも確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。実共有タグ同期はAuth/Supabase live未検証。</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>iOS shared tag display_name migration idempotency fixed 2026-06-29. Android実機の未ログイン案内は確認済み。共有タグのlive同期、グループ作成/編集、招待参加は外部Auth/Supabaseゲートとして継続。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -1997,47 +2528,57 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PARTIAL_PASS_WITH_AUTH_LIVE_GAP: Android実機で未ログイン時の共有タグサインイン案内PASS。共有タグ同期/グループ作成編集の本番Auth/Supabase完了確認は未完了。</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>PASS: iOS MetadataStatusTextTests 5件成功。SharedTagCloud migrationのdisplay_name追加をaddColumnIfMissingへ変更し、重複カラムログが消えたことを/tmp/rinbam-metadata-test.logで確認。</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>物理端末での共有タグ同期/グループ同期、Supabase live syncは未検証。iOS simulatorではApp Group entitlement警告とCoreSimulator WebCore/WebKit重複クラス警告が残るが、display_name重複カラムログは解消。</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>FIXED_LOCAL: SharedTagCloud migrationのtry? ALTER TABLEをSQLiteDatabase.addColumnIfMissingへ置換し、既存DBでの冪等性を改善。</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>PASS local retest: xcodebuild test -only-testing:URLSaveriOSTests/MetadataStatusTextTests 成功、重複display_name migrationログなし。</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: 共有タグ/グループ同期は未検証。</t>
+          <t>PASS local retest: xcodebuild test -only-testing:URLSaveriOSTests/MetadataStatusTextTests 成功、重複display_name migrationログなし。 2026-07-03 Android physical: 未ログイン共有タグ+からサインイン案内表示PASS。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 共有タグ/グループ系導線で未ログイン時のサインイン案内を確認。グループ本体の作成/編集はサインイン後のSupabase liveが必要なため未実行。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>iOS shared tag display_name migration idempotency fixed 2026-06-29.</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): ホームの共有タグ行「+」を押すとプロフィール/サインイン画面へ遷移し、「共有タグに参加するにはサインインが必要です」「Googleで続ける」「メールアドレス」「パスワード」が表示されることを確認。共有タグの本番同期/作成/招待参加はSupabase/Auth live環境のため未完了。証跡: artifacts/device-verification/2026-07-03-us018-shared-tag-signin/android-home-before-shared-tag-plus.png/xml, android-shared-tag-plus-result.png/xml。</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-06-29 01:02:48 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 共有タグ/グループ系導線で未ログイン時のサインイン案内を確認。グループ本体の作成/編集はサインイン後のSupabase liveが必要なため未実行。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>iOS shared tag display_name migration idempotency fixed 2026-06-29. Android実機の未ログイン案内は確認済み。共有タグのlive同期、グループ作成/編集、招待参加は外部Auth/Supabaseゲートとして継続。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -2099,40 +2640,50 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): プロフィール画面で「Googleで続ける」「サインイン後に利用できます」を確認。実OAuthは未実施。証跡: android-pixel9a-profile-open-portrait.png/xml。</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): プロフィールシートでアカウント表示、ChatGPT連携トグル、サインアウトボタンを確認。サインアウト/OAuth callbackは未実施。証跡: iphone-ui-loop-profile-open.png/xml, iphone-ui-loop-after-inquiry-close-correct.png/xml。</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>秘密情報入力や外部OAuthは実行せず、画面表示のみ確認。</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>2026-06-29 12:03:48 +0900</t>
         </is>
@@ -2196,40 +2747,50 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>store_console</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): プロフィール写真、プロフィール名、写真追加、画面モード、保存ボタンを確認。編集保存は未実施。証跡: android-pixel9a-profile-open-portrait.png/xml。</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): プロフィール名、メール、写真追加、画面モード、保存ボタンを確認。編集保存は未実施。証跡: iphone-ui-loop-profile-open.png/xml。</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>ユーザーデータ変更を避けるため、編集・保存は未実施。</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>2026-06-29 12:03:48 +0900</t>
         </is>
@@ -2293,40 +2854,50 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): プロフィール画面で問い合わせ導線を確認。削除/送信は未実施。証跡: android-pixel9a-profile-open-portrait.png/xml。</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): プロフィールシートで問い合わせ、アカウント削除、サインアウトを確認し、問い合わせシートのメール/氏名/内容/送信UIを表示。送信/削除は未実施。証跡: iphone-ui-loop-profile-open.png/xml, iphone-ui-loop-after-closing-profile.png/xml, iphone-ui-loop-after-inquiry-close-correct.png/xml。</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>破壊的なアカウント削除と問い合わせ送信は実行していない。</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>2026-06-29 12:03:48 +0900</t>
         </is>
@@ -2385,47 +2956,57 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>LOCAL_PASS_WITH_PROMO_LIVE_GAP</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests EntitlementResolverTest 成功。PASS: iOS URLRulesTests LimitChecker対象2件成功。SharedTagAuthViewModelTestは直近実行済み。</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>本番Supabase RPC/get_my_entitlement_grants/redeem_promo_code live実行、実メール/リンクからの優待適用、物理端末操作は未検証。</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>修正なし: ローカルテスト上のエラー未検出。Entitlement cache/remote/usage summaryのcode_basisを補強。</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>PASS local retest: Android entitlement targeted test、iOS limit checker targeted tests成功。</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
-        </is>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS local retest: Android entitlement targeted test、iOS limit checker targeted tests成功。PASS Android physical UI: プロフィール内に優待コード入力欄と「優待Proを受け取る」ボタンを確認。live適用は外部環境待ち。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール画面を確認し、優待コード欄と「優待Proを受け取る」ボタンが表示されることを確認。未ログイン/未入力状態ではボタンは無効。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実コード適用はSupabase live未検証。</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>entitlement cache/remote coverage refreshed 2026-06-29.</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): プロフィール画面で優待コード入力欄と「優待Proを受け取る」ボタンを確認。未サインイン状態のためボタンは無効。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-profile-scroll-auth-plan.png/xml。</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-06-29 01:00:20 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール画面を確認し、優待コード欄と「優待Proを受け取る」ボタンが表示されることを確認。未ログイン/未入力状態ではボタンは無効。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実コード適用はSupabase live未検証。</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>entitlement cache/remote coverage refreshed 2026-06-29. 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -2482,47 +3063,57 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>LOCAL_PASS_WITH_LIMIT_LIVE_GAP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests EntitlementResolverTest 成功。PASS: iOS URLRulesTests LimitChecker対象2件成功。</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>物理端末で実使用量が上限に達した時のUI文言/ブロック、Supabase live grant反映は未検証。</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>修正なし: ローカル制限判定テスト上のエラー未検出。</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>PASS local retest: Android/iOS limit checker targeted tests成功。</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
-        </is>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS local retest: Android/iOS limit checker targeted tests成功。PASS Android physical UI: プロフィール内に使用状況、保存タグ/共有タグ/グループ、Standard/Proコース表示を確認。上限到達時のlive文言は外部状態待ち。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィールの使用状況で保存タグ5、共有タグ0、グループ0の表示を確認。有料コース/サインイン必須表示も確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実上限 enforcement はAuth/Supabase/live契約側の確認が残る。</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>usage/limit checker coverage refreshed 2026-06-29.</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): プロフィール画面で使用状況、保存タグ/共有タグ/グループ件数、有料コース、Standard月額/年払い、Pro月額/年払いを確認。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-us036-profile-signin-no-chatgpt.png/xml, android-profile-scroll-auth-plan.png/xml。</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-06-29 01:00:20 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィールの使用状況で保存タグ5、共有タグ0、グループ0の表示を確認。有料コース/サインイン必須表示も確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実上限 enforcement はAuth/Supabase/live契約側の確認が残る。</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>usage/limit checker coverage refreshed 2026-06-29. 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -2584,40 +3175,50 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests ExportRepositoryTest --tests ExportScreenTest 成功。PASS: iOS ExportArchiveBuilderTests/ServiceFilterTests 対象実行19件中Export関連17件成功。</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>物理Android/iPhoneでの共有シート、ファイル保存、ファイル受け渡し先アプリでの実確認は未検証。iOS simulator test中にApp Group entitlement警告と重複display_name migrationログあり、テスト失敗はなし。</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>修正なし: ローカルテスト上のエラー未検出。台帳code_basisに共有シート/保存先実装を補強。</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>PASS local retest: Android export targeted tests、iOS export/filter targeted tests成功。物理共有先は未実施。</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639): エクスポート画面で「共有タグだけ」「ZIP」「JSON」「共有シート」「ファイルに保存」「書き出す」を確認。出力実行は未実施。証跡: android-pixel9a-export-open-portrait.png/xml。</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): エクスポート画面で「ZIP」「JSON」「共有シート」「ファイルに保存」「書き出す」を確認。UIActivityViewController/fileExporter実行は未実施。証跡: iphone-ui-loop-export-open-final.png/xml。</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>実ファイル生成、共有先アプリ、ファイル保存先確認は次ループで実施。</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>2026-06-29 12:03:48 +0900</t>
         </is>
@@ -2681,40 +3282,50 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): ブック/使い方ボタンをタップし、初回spotlightではなく使い方リストへ遷移。「まず覚える」「便利な操作」「共有とAI」をXMLで確認し、戻るでホーム復帰。証跡: artifacts/device-verification/2026-06-29/iphone-appium-usage.png, iphone-appium-usage-source.xml, iphone-appium-home-after-usage-back.png, iphone-appium-home-after-usage-back-source.xml。</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>iPhone実機で下部バー非表示の使い方リストと戻る復帰を確認。</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>2026-06-29 11:48:00 +0900</t>
         </is>
@@ -2778,40 +3389,50 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): ホーム下部に グループ/エクスポート/中央＋/タグ/アーカイブ が表示され、中央＋が突出。使い方画面では下部バーが表示されないことをPNG/XMLで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml; artifacts/device-verification/2026-06-29/iphone-appium-usage.png, iphone-appium-usage-source.xml, iphone-appium-home-after-usage-back.png, iphone-appium-home-after-usage-back-source.xml。</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>iPhone実機でホーム下部5アクションと使い方画面の下部バー非表示を確認。</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>2026-06-29 11:48:00 +0900</t>
         </is>
@@ -2870,47 +3491,57 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>PASS_COMPILE_PRODUCTION_EQUIVALENT_LOCAL_ONLY</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>LOCAL_ONLY</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>public_web</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
-        </is>
-      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>Release compile上の失敗なし。署名付き配布や外部console設定はこのストーリーの対象外。</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
+          <t>修正なし: Android/iOS Release compile条件を再確認し、台帳の物理操作ゲート表現を整理。</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
+          <t>PASS: ./gradlew assembleRelease 成功。PASS: xcodebuild -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -configuration Release -destination generic/platform=iOS CODE_SIGNING_ALLOWED=NO build 成功。Android release manifestのtools:node remove警告とSwift await警告は残るがbuild失敗なし。</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t/>
+          <t>N/A: US-028はAndroid release compile確認ストーリーで、物理端末操作は受け入れ条件外。</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-06-29 06:32:51 +0900</t>
+          <t>N/A: US-028はiOS Release generic compile確認ストーリーで、物理iPhone操作は受け入れ条件外。</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>本番相当local-only buildのcompile確認は2026-07-03に再実行済み。署名付き配布は別ゲートで扱う。</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:54:50 +0900</t>
         </is>
       </c>
     </row>
@@ -2972,40 +3603,50 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>store_console</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): canonical package jp.miyamibu.urlalbum をADBで起動しホーム証跡を取得。</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): bundleId com.mibu.codebridge.ios のAppium sourceを取得し、Application name/label が「りんばむ」であることを確認。devicectl apps JSONでも表示名「りんばむ」を確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml; artifacts/device-verification/2026-06-29/iphone-rinbam-apps-after-rename.json。</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>実機上の正準Android package/iOS bundle IDは確認済み。App Store/Google Play Console上の表示は未操作。</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>2026-06-29 11:48:00 +0900</t>
         </is>
@@ -3069,40 +3710,50 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug assembleRelease 成功。connectedDebugAndroidTestはurlsaverParityApi35 AVDでPASS。 / PARTIAL: iOS Release generic build と build-for-testing 成功。XCTest実行はCoreSimulator不整合で未実施。</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): noResetのAppiumセッションでホーム、使い方遷移、戻る復帰を確認。アンインストール、pm clear、DB削除、データリセットなし。証跡: artifacts/device-verification/2026-06-29/iphone-appium-home-after-rename.png, iphone-appium-home-source-after-rename.xml; artifacts/device-verification/2026-06-29/iphone-appium-usage.png, iphone-appium-usage-source.xml, iphone-appium-home-after-usage-back.png, iphone-appium-home-after-usage-back-source.xml。</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>iPhone Appium/WDA復旧後も非破壊確認のみ実施。Android connectedDebugAndroidTestや物理端末データ削除系コマンドは未実行。</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>2026-06-29 11:48:00 +0900</t>
         </is>
@@ -3166,40 +3817,38 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
         <is>
           <t>秘密値は扱わない</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
@@ -3263,40 +3912,34 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
@@ -3360,40 +4003,38 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>supabase_auth;resend_live</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
         <is>
           <t>実送信は承認なしにしない</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
@@ -3457,40 +4098,34 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
@@ -3554,40 +4189,34 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
@@ -3651,40 +4280,34 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>supabase_auth;resend_live</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。 / PASS: web/admin npm run typecheck と npm run build 成功。</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
         </is>
@@ -3748,40 +4371,50 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>PASS: 既存45件に今回追加5件を追記し、CSV/XLSXを同一内容で更新。共有保存タグ選択、コレクション、ChatGPT連携、問い合わせ監査、公開Web/リンクを追加。</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。 Supabase local lint: ローカルPostgres 127.0.0.1:55422 が接続拒否。</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>FIXED_LOCAL: XLSXの_FilterDatabase定義をA1:S57へ更新し、summaryシートもCSV最新ステータス集計と残ゲート集計から再生成。</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>PASS: CSV 56行、XLSX dimension A1:S57、_FilterDatabase A1:S57、CSV/XLSXセル差分0、summaryステータス集計一致、summary残ゲート集計生成、XLSX zip integrity確認済み。</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>未実機操作: 代表導線のみ確認。データ作成/削除を伴う操作は未実施。</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>US-034/US-035/US-036/AS-008/ES-006を追加。 US-037/US-038/US-039/US-040/TS-001を追加。 AS-009を追加し、US-039に公開reset-passwordページを追記。 US-006のiOS表示モード永続化ギャップを修正し、US-012にiOS BGTaskScheduler証跡を追記。 US-025/US-023/US-024のexport/entitlement近接テスト結果を更新。US-040にiOS PrivacyInfo証跡を補強。 iOS SharedTagCloud display_name migrationの冪等性を修正し、US-018/US-019/ES-003へ反映。2026-06-29にXLSXフィルタ範囲、summaryステータス集計、残ゲート集計を実データへ修正。Public privacy stale検出後にsummary再生成。 Release privacy/store docsのpublic privacy stale反映後にsummary再生成。 Public web verifier追加後にsummary再生成。 Android privacy dialog文言更新後にsummary再生成。 iOS PrivacyInfoSheet反映後にsummary再生成。 connectedDebugAndroidTest AVD PASS反映後にsummary再生成。</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>2026-06-29 06:32:51 +0900</t>
         </is>
@@ -3845,40 +4478,46 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>PASS: 2026-06-29 ./gradlew assembleDebug testDebugUnitTest lintDebug 成功。PASS: ./gradlew assembleRelease 成功。PASS: urlsaverParityApi35 AVDで connectedDebugAndroidTest 成功（17 tests、SharedTagCloudLiveDeviceTest 1件はlive Supabase設定なしでSKIP）。対象追加確認として SharedTagAuthViewModelTest/TagRepositoryTest 単独実行も成功。</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Release manifestで広告/AD_ID削除指定の対象なしwarning、MenuBook deprecated warningあり。どちらもbuild失敗ではない。物理共有、購入操作は未検証。SharedTagCloudLiveDeviceTestはlive Supabase設定なしでSKIPし、Supabase/Auth live側に残す。</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>PASS local + connected retest。connectedDebugAndroidTestはテスト専用AVD urlsaverParityApi35で成功。物理共有/購入操作は各ユーザーストーリー側で別ゲートとして追跡。</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
         <is>
           <t>connectedDebugAndroidTestは通常端末では承認なし実行しない。テスト専用AVDでは2026-06-29に実行済み。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。 2026-06-29 connectedDebugAndroidTestをテスト専用AVDで実行し成功。</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>2026-06-29 06:32:51 +0900</t>
         </is>
@@ -3942,42 +4581,48 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>PASS: iOS MetadataStatusTextTests 5件成功。display_name duplicate column migrationログとApp Group container_create_or_lookup警告は修正後に消失。</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>iOS simulator testでCoreSimulator WebCore/WebKit重複クラス警告は残存。物理iPhone UI操作は未検証。</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>PARTIAL_FIXED_LOCAL: SharedTagCloud migrationの重複カラムログとSharedContainerのXCTest時App Group lookup警告を修正。残る警告はCoreSimulator runtime由来として継続記録。</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>PASS local retest: MetadataStatusTextTests成功、duplicate display_nameログなし、container_create_or_lookupログなし。</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI取得不可。Bundle ID確認とlaunchのみ。</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>App Group XCTest warning fixed 2026-06-29; CoreSimulator UIAccessibilityLoaderWebShared warning remains.</t>
-        </is>
-      </c>
+          <t>PASS local retest: MetadataStatusTextTests成功、duplicate display_nameログなし、container_create_or_lookupログなし。 2026-07-03追加: xcodebuild selected local/simulator tests PASS 26 tests。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-06-29 01:07:00 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>App Group XCTest warning fixed 2026-06-29; CoreSimulator UIAccessibilityLoaderWebShared warning remains. 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:10追加: devicectlで物理iPhone 12へcanonical bundle com.mibu.codebridge.ios をデータ保持の上書きインストール成功。同端末でdevicectl launch成功。証跡: artifacts/device-verification/2026-07-03-iphone-nonvideo/iphone-devicectl-launch-after-archive-swipe.json。ただしこれはインストール/起動証跡であり、Appium/WDAの画面操作証跡ではない。 2026-07-03 04:10再確認: Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:20再確認: devicectlではiPhone 12にインストール/起動できるが、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723未起動、RemoteXPC 42314 timeout。このためiPhoneの重複通知「見る」実操作は継続して NOT VERIFIED on physical iPhone。 2026-07-03 04:22追加: Appium 3.5.0 serverを通常権限で起動しXCUITest session作成を再試行。RemoteXPC devices listing unavailable: tunnel registry timeout。fallback後も Unknown device or simulator UDID 00008101-00066D96340A001E でHTTP 500。ログ: artifacts/device-verification/2026-07-03-iphone-nonvideo/appium-server-retry.log。devicectl install/launchは可能だが、Appium/WDA UI操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4039,40 +4684,34 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>PASS: 2026-06-29 web/admin npm run typecheck と npm run build 成功。Next.js buildで管理API route生成まで確認。</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
         <is>
           <t>修正なし: typecheck/buildエラー未検出。</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>PASS local retest。本番env/API実動作は未検証。</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>2026-06-29 00:39:51 +0900</t>
         </is>
@@ -4136,42 +4775,44 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>PASS: 2026-06-29 deno check supabase/functions/verify-store-purchase/index.ts 成功。BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 connection refused。</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>linked DB schema/RPC validationは実施済み。残りはDB advisorsの既存WARN確認と、ローカルDB起動なしによりlocal lintが未実施である点。</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>APPLIED_LINKED_DB: 未適用だったshared group/profile、promo delivery inbox、contact support request、store purchase verification系schemaをlinked DBへ適用。PUBLIC実行権限が残っていたSECURITY DEFINER RPCをhardenし、anon実行は招待preview系だけに限定。</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>PASS linked DB: db query --linkedで主要table/RPC存在確認成功。PASS functions: contact-support/contact-support-resend-webhook/verify-store-purchase deploy成功。PASS advisors improvement: anon executable SECURITY DEFINERはpreview系3件のみ。Remaining advisors WARN: function search_path、signed-in SECURITY DEFINER、RLS initplan、multiple policies、leaked password protection。</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>linked project xocumgxbylmpoobfqows。db pushはremote migration history driftにより不可だったため、必要migrationをdb query --linkedで個別適用。</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>2026-06-29 07:25:00 +0900</t>
+          <t>PASS linked DB: db query --linkedで主要table/RPC存在確認成功。PASS functions: contact-support/contact-support-resend-webhook/verify-store-purchase deploy成功。PASS advisors improvement: anon executable SECURITY DEFINERはpreview系3件のみ。Remaining advisors WARN: function search_path、signed-in SECURITY DEFINER、RLS initplan、multiple policies、leaked password protection。 2026-07-03追加: deno check supabase/functions/verify-store-purchase/index.ts、contact-support/index.ts、contact-support-resend-webhook/index.ts は全てPASS。</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>linked project xocumgxbylmpoobfqows。db pushはremote migration history driftにより不可だったため、必要migrationをdb query --linkedで個別適用。 2026-07-03確認: Supabase vanity domain linbam.supabase.co は未解決で、vanity-subdomains APIはPro/Team/Enterprise plan requiredを返す。現行project ref xocumgxbylmpoobfqowsは到達するが匿名healthは401。</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2026-07-03 03:36:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4839,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ローカルタグ共有リンク/JSON export/import</t>
+          <t>ローカルタグ共有リンク/JSON export/import（正準仕様で不採用）</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4208,67 +4849,77 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ユーザーとして、ローカルタグを他端末や共有先へ渡し、受け取った側でタグ名・URL・タイトル・メモを可能な範囲で復元できる。</t>
+          <t>ユーザーとして、自作タグ管理/自作タグ詳細ではリンクやJSONなどの技術的な共有導線を見ず、タグ名と件数と必要な操作だけを見られる。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Androidはタグ詳細から同端末リンクとJSONタグデータを共有できる。iOSはタグJSONをexport/importでき、Share Extensionで受け取ったタグJSONを取り込める。既存URLは上書きせず、作成/統合/重複/失敗件数を返す。</t>
+          <t>自作タグ管理にリンク/JSON/文字付き削除を出さない。自作タグ詳細にこの端末用リンクやタグデータ(JSON)共有を出さない。共有タグのクラウド招待リンクは共有タグ専用導線として維持する。</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Android: assembleDebug/testDebugUnitTest/lintDebug; iOS: URLRepositoryTests testLocalTagPayloadExportImportTracksCreatedMergedAndSkipped; iOS generic build; source inspection</t>
+          <t>Android assembleDebug、mobile UI contract、source inspection、Android physical UI XML/PNG。iOS source inspection。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>正準アプリIDで共有入口が残り、Share Extension/Intent経由でも同じimport契約を使うこと</t>
+          <t>正準アプリIDの通常UIから自作タグリンク/JSON共有導線へ到達できないこと。</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>REMOVED_BY_CANONICAL_SPEC</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest lintDebug 成功。PASS: iOS URLRepositoryTests単独成功、generic iOS Simulator build成功。</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>物理Android共有シート操作と物理iPhone Share Extension操作は未検証。iOS全体XCTestはlive Supabase 3件がInvalid API keyで失敗したが、このストーリー対象外。</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>実装済み: Androidタグ詳細のリンク/JSON共有、iOSタグJSON export/import、Share Extension importを追加。</t>
+          <t>過去実装としてローカルタグ共有リンク/JSON export/importは存在したが、現行の正準仕様では不採用。一般のエクスポート画面のJSON出力とは別扱い。</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>PASS local retest。実機共有操作は未実施。</t>
+          <t>仕様衝突: docs/rinbam-canonical-spec.md と docs/mobile-ui-regression-contract.md は自作タグ管理/詳細にリンク/JSON共有導線を戻さないと定義している一方、Android TagDetailScreen.kt にこの端末用リンク/タグデータ(JSON)共有が残っていた。</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>未実機操作: 共有シートからのタグJSON受け渡しは未検証。</t>
+          <t>FIXED_LOCAL: Android TagDetailScreen.kt から自作タグ詳細のリンク/JSON共有選択肢を削除し、共有タグのクラウド招待だけを表示する条件へ限定。</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Share Extension操作は未検証。</t>
+          <t>PASS: rgで禁止文言の残存なし。python3 scripts/verify_mobile_ui_contract.py 成功。./gradlew assembleDebug 成功。</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>実装コミット 7a2aba31。旧タグ共有復元の独立ストーリーとして追加。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 上書きインストール後、ホームとタグ管理シートを確認。自作タグ管理にリンク/JSON文言なし、削除はゴミ箱アイコンのみ。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-after-tag-share-removal-tag-management.png/xml。</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-06-29 00:36:46 +0900</t>
+          <t>PASS(source/current spec): iOS側の通常タグ管理/共有タグ管理に自作タグリンク/JSON共有導線のUI残存なし。Appium実機操作はusbmuxd/Appium復旧待ちのため追加スクリーン証跡なし。</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>US-031は旧復元候補だったが、第1〜16回の採用仕様では不採用。今後は一般エクスポート機能と共有タグクラウド招待を別ストーリーとして扱う。</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:49:54 +0900</t>
         </is>
       </c>
     </row>
@@ -4325,47 +4976,57 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PARTIAL_PASS_WITH_AUTH_LIVE_GAP: Android実機で共有タグ導線からサインイン案内PASS。実招待リンク保留/サインイン後再開はAuth/Supabase live未検証。</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>PASS: Android SharedTagAuthViewModelTest/TagRepositoryTest対象実行成功。PASS: iOS PendingInviteStoreTests単独成功。Android全体build/test/lint成功。</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>OAuth実ブラウザ往復、Supabase live invite accept、物理iPhone Appium操作は未検証。</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>実装済み: AndroidにもPendingInviteStoreと再開カードを追加。iOSの既存pending invite再開と合わせた。</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>PASS local retest。live invite再開は外部Auth/Supabase環境待ち。</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>未実機操作: 実OAuth/招待リンク受け取りは未検証。</t>
-        </is>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Appium/WDA UI操作未検証。</t>
+          <t>PASS local retest。live invite再開は外部Auth/Supabase環境待ち。 2026-07-03 Android physical: 共有タグ導線からサインイン案内表示PASS。実OAuth/招待リンク再開は未検証。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 未ログイン時の共有タグ参加/作成導線としてサインイン案内、メール/パスワード入力欄、サインインボタン要素を確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。実招待リンク保留とサインイン後再開はAuth/Supabase live未検証。</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>実装コミット 7a2aba31。US-017の招待参加から保留再開を分離して追跡。</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 共有タグ行「+」からサインイン画面へ遷移し、共有タグ参加にはサインインが必要である旨、Google/メール/パスワード導線が表示されることを確認。実OAuth往復と招待リンク保留/再開は未実施。証跡: artifacts/device-verification/2026-07-03-us018-shared-tag-signin/android-shared-tag-plus-result.png/xml。</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-06-29 00:36:46 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 未ログイン時の共有タグ参加/作成導線としてサインイン案内、メール/パスワード入力欄、サインインボタン要素を確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。実招待リンク保留とサインイン後再開はAuth/Supabase live未検証。</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>実装コミット 7a2aba31。US-017の招待参加から保留再開を分離して追跡。 Android実機で「サインインしていなければ押した時にサインイン案内を出す」挙動は確認済み。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4422,47 +5083,57 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_EXTERNAL_STORE_GAP</t>
+          <t>PARTIAL_PASS_WITH_EXTERNAL_STORE_GAP: Android実機でプラン/優待コード表示PASS。実Google Play購入、StoreKit sandbox、ストア設定は未検証。</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>PASS: Android build/test/lint/release build成功。PASS: iOS generic build成功。PASS: deno check supabase/functions/verify-store-purchase/index.ts 成功。</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Google Play sandbox purchase、StoreKit sandbox purchase、RTDN/App Store Server Notificationsは未検証。linked DB schemaとverify-store-purchase Function deployは確認済み。</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>実装済み: Store purchase verification table/migrationとEdge Functionを追加し、client purchase serviceから呼ぶ契約を整備。本番Function version 13へdeploy済み。</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>PASS local/type/build retest。PASS linked DB: public.store_purchase_verifications と user_entitlement_grants 制約確認。PASS Function deploy/list: verify-store-purchase ACTIVE version 13。未実施: 外部ストアsandbox購入と通知。</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>未実機操作: Google Play Billing実購入フロー未検証。</t>
-        </is>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: StoreKit sandbox購入フロー未検証。</t>
+          <t>PASS local/type/build retest。PASS linked DB: public.store_purchase_verifications と user_entitlement_grants 制約確認。PASS Function deploy/list: verify-store-purchase ACTIVE version 13。未実施: 外部ストアsandbox購入と通知。 2026-07-03 Android physical: プラン/優待コード表示PASS。実購入はStore外部ゲートとして未実施。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール画面の有料コース欄で Standard 月額/年払い、Pro 月額/年払いボタンが表示されることを確認。現在は無効状態。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。StoreKit sandbox/実購入は外部ストア設定が必要で未検証。</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>実装コミット 7a2aba31。ストア側product/価格/審査設定は外部ゲート。</t>
+          <t>PARTIAL_PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): プロフィールをスクロールし、有料コースに「Standard 月額」「Standard 年払い」「Pro 月額」「Pro 年払い」、優待コード欄と「優待Proを受け取る」ボタンが表示されることを確認。実Google Play購入/課金検証は実行していない。証跡: artifacts/device-verification/2026-07-03-us033-plan-android/android-profile-plan-scroll1.png/xml。</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-06-29 07:25:00 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール画面の有料コース欄で Standard 月額/年払い、Pro 月額/年払いボタンが表示されることを確認。現在は無効状態。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。StoreKit sandbox/実購入は外部ストア設定が必要で未検証。</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>実装コミット 7a2aba31。ストア側product/価格/審査設定は外部ゲート。 Android実機のプラン表示/優待コード表示は確認済み。Google Play Billing実購入・ストア商品設定・iPhone StoreKit sandboxは外部/未検証ゲートとして継続。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4524,40 +5195,42 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>supabase_auth;store_console</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>PASS: deno check Edge Function成功。SQL migrationはsource確認済み。BLOCKED_LOCAL: supabase db lint --local はローカルDB接続拒否。</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>ストア実通知、sandbox購入、管理画面からの実監査操作は未検証。linked DB migration/RLS/schema validationは実施済み。</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>APPLIED_LINKED_DB: store purchase verification table/RLS/index、transaction unique index、grant作成処理をlinked DBへ適用。本番verify-store-purchase Functionもdeploy済み。</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>PASS linked DB: store_purchase_verifications columns/RLS policy確認。PASS Function: verify-store-purchase no-session request is rejected with 401. Remaining: Google Play/App Store sandbox実取引と通知イベント。</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
         <is>
           <t>実装コミット 7a2aba31。AS系に課金監査ストーリーを追加。</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>2026-06-29 07:25:00 +0900</t>
         </is>
@@ -4616,47 +5289,57 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
+          <t>PHYSICAL_PASS: Android/iPhone実機で保存/追加時の自作タグ選択UIとタグ追加操作PASS</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>PASS: ShareReceiverActivityEntrypointTest/RepositoryBehaviorTest対象実行成功。PASS: iOS generic buildとURLRepositoryTests成功。Source inspectionでiOS Share Extension tag picker/create/save確認。</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>物理Android共有シート操作、物理iPhone Share Extension操作は未検証。</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>修正なし: コード上はAndroid/iOSとも保存前タグ選択/作成UIあり。</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>PASS local/source retest。実機共有シートは未実施。</t>
+          <t>解消済み: Android側で見えていなかった自作タグ追加ボタン、iPhone側の+ボタン文言差分、タグ選択UIの単一選択化は現行実機で修正済み。</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>未実機操作: Android share sheetからタグ選択/作成は未検証。</t>
+          <t>FIXED_LOCAL_AND_DEVICE_VERIFIED: Android/iPhoneとも自作タグ追加は+のみ、選択シートは複数選択後に追加ボタンで確定する。</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: Share Extensionタグ選択/作成は未検証。</t>
+          <t>PASS physical retest: Android/iPhoneでタグ追加シートを開き、複数タグを同時選択し、追加ボタンでカードへ反映されることを確認。iPhone Safari共有拡張でも保存先タグ画面のタグ表示と+作成欄、保存完了を確認。</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Androidで消えていたと報告された旧実装UIの追跡行。iOSにも対応UIあり。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 自作タグ行の+、タグ追加シート、複数タグ選択、追加ボタン、適用後カードへのタグ表示を確認。長いタグ名対策・FlowRow系UIはコード/実機証跡で継続確認対象。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/android-batch-tag-sheet-after-fix.png/xml, android-batch-tag-sheet-two-selected.png/xml, android-batch-tag-after-apply.png/xml。</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-06-29 00:43:50 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA): +のみの自作タグ追加、タグ追加シート、複数タグ選択、追加ボタン、適用後カードへのタグ表示を確認。Safari共有拡張の保存先タグ画面も保存完了まで確認。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/iphone-batch-tag-sheet-after-fix.png/source, iphone-batch-tag-sheet-two-selected-2.png/source, iphone-batch-tag-after-apply.png/source, iphone-share-extension-after-click.png/source, iphone-share-extension-after-save.png/source。</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>保存先タグ/自作タグUIの基本動作は物理PASS。US-003のiPhone複数URL共有入力元ギャップ、動画/メディア保存は別行で残す。</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4683,7 +5366,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>受信箱/自作コレクション作成・移動・並び替え</t>
+          <t>受信箱/自作コレクション基盤（現行正準UIでは非公開）</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4693,67 +5376,77 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ユーザーとして、保存URLを受信箱以外の自作コレクションへ整理し、一覧上部のコレクションを並べ替えて絞り込める。</t>
+          <t>開発者として、コレクションDB/Repository基盤が残っている一方、現行のユーザー向けUIでは自作タグ/保存先タグを正準導線として使い、コレクション作成・移動UIを出さないことを追跡できる。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>デフォルト受信箱を保持し、自作コレクション作成/重複検出/削除時の受信箱戻し/同名ローカルタグ連携/並び替え/フィルタが動く。</t>
+          <t>Android SHOW_COLLECTION_UI=false、iOS showsCollectionUI=false のまま、通常UIにコレクション作成/管理/保存先指定を出さない。既存DB/Repositoryテストは維持する。将来公開する場合は別途採用判断して再有効化する。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Android: RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest. iOS: URLRepositoryTests collection lifecycle. Future iOS collection UI tests.</t>
+          <t>source inspection、Android/iOS collection lifecycle tests、mobile UI contract、physical home/profile smoke where available。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Room migration後もcollectionsとurl_entries.collectionIdが保持され、削除時にURL本体は削除されないこと。</t>
+          <t>正準アプリIDの通常UIでコレクションUIへ到達できないこと。</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>BLOCKED_DEVICE_UI_DISABLED: コレクション保存先UIがAndroid/iOS現行ビルドで無効化されており、作成/移動/削除/並び替えを実機操作できない。</t>
+          <t>FOUNDATION_ONLY_NOT_CANONICAL_UI</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PASS: Android RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。PASS: iOS URLRepositoryTests 12件成功、受信箱/作成/重複/移動/並び替え/削除時受信箱戻し/削除時同名ローカルタグ削除を確認。PASS: iOS ServiceFilterTests 18件成功、RootView/AppChrome/DetailViewのコレクション作成/選択/移動/削除/並び替え/検索/同名ローカルタグ込みフィルタ契約を確認。</t>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Device/source gap: Androidは UrlSaverRoot.kt の SHOW_COLLECTION_UI=false によりコレクション作成/選択/並び替え/手動保存先指定が非表示。iOSは RootView.swift/DetailView.swift の showsCollectionUI=false により collectionCreateAction/collectionManageAction/collections、手動保存先、詳細の保存先変更が無効。iPhone実機に見える「+保存先」「保存先管理」「受信箱」はServiceFilterRow上のローカルタグ系チップで、コレクション作成「＋ コレクションを作成」やコレクション文言は表示されない。</t>
+          <t>public_web;design_required</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>未修正: US-035を実機操作可能にするには、現行デザイン/仕様に沿ってAndroid SHOW_COLLECTION_UI と iOS showsCollectionUI の有効化方針を決め、コレクション作成/管理/詳細移動/削除/並び替えUIを有効化またはストーリー範囲をローカルタグへ再定義する必要がある。</t>
+          <t>PASS: Android RepositoryBehaviorTest/MainListViewModelTest/ListFilterStateTest/TopFilterOrderResolutionTest対象実行成功。PASS: iOS URLRepositoryTests/ServiceFilterTestsでcollection lifecycle基盤確認済み。</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>BLOCKED physical retest 2026-06-29: Android/iPhone実機でホーム画面を確認したが、コレクション作成/管理/移動UIが無効化されており、US-035 acceptance criteriaの作成/保存先選択/既存URL移動/削除/並び替えを操作できなかった。</t>
+          <t>現行正準仕様 docs/rinbam-canonical-spec.md は保存先タグ/自作タグ中心で、コレクション作成・移動UIを採用項目に含めていない。旧台帳ではユーザー機能として残していたため、実機未到達ゲートとして誤追跡していた。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NOT VERIFIED / BLOCKED(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): ホーム画面にりんばむ、共有タグ、タグ、保存カードは表示。SHOW_COLLECTION_UI=false のためコレクション作成/管理/選択/並び替えUIは表示されず、コレクション作成/移動/削除/並び替えは実機操作不能。証跡: artifacts/device-verification/2026-06-29/us035/android-start.xml, android-start.png。</t>
+          <t>FIXED_TRACKING: US-035を現行正準UIの未完了機能ではなく、将来用/基盤のみの追跡へ再分類。Android SHOW_COLLECTION_UI=false と iOS showsCollectionUI=false は現行仕様に沿う。</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NOT VERIFIED / BLOCKED(iPhone physical 00008101-00066D96340A001E, Appium/WDA, com.mibu.codebridge.ios): ホーム画面に「+保存先」「保存先管理」「受信箱」等は見えるが、source上「コレクション」「＋ コレクションを作成」は表示なし。showsCollectionUI=false のためコレクション作成/管理/保存先指定/詳細移動UIは無効で、US-035の実機操作は不能。証跡: artifacts/device-verification/2026-06-29/us035/iphone-start-source.xml, iphone-start.png。</t>
+          <t>PASS: source inspectionで Android SHOW_COLLECTION_UI=false、iOS showsCollectionUI=false を確認。python3 scripts/verify_mobile_ui_contract.py 成功。既存collection基盤テスト証跡は継続有効。</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-06-29 physical/source audit: US-035はローカル実装済み扱いだったが、現行UIフラグで実機から到達不能。iOSの「保存先」表示はローカルタグ系導線と混同しやすいため、コレクション機能としては未提供扱い。</t>
+          <t>N/A current canonical UI: Android現行正準UIではコレクション作成/管理/保存先指定を出さない。自作タグ/保存先タグ導線は別ストーリーで実機PASS済み。</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-06-29 15:32:41 +0900</t>
+          <t>N/A current canonical UI: iPhone現行正準UIではコレクション作成/管理/保存先指定を出さない。自作タグ/保存先タグ導線は別ストーリーで実機PASS済み。</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>今後コレクションをユーザー機能として再採用する場合は、保存先タグ/自作タグとの関係、表示名、移動/削除/並び替えUIを新ストーリーとして決め直してからフラグを有効化する。</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2026-07-03 03:00:24 +0900</t>
         </is>
       </c>
     </row>
@@ -4780,7 +5473,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ChatGPT personal link sync</t>
+          <t>ChatGPT personal link sync（通常UI非表示）</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4790,67 +5483,77 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ユーザーとして、サインイン後に保存中/アーカイブ済みリンクをChatGPT提案対象として同期し、本文取得の送信有無も選べる。</t>
+          <t>ユーザーとして、未完成/未運用のChatGPT連携や公開ページ同期の設定欄を通常UIでは見ず、AI向け活用はエクスポート画面から使える。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>サインイン必須。enabled/contentFetchEnabledをSupabase RPCへ保存し、有効化時にactive+archivedの個人リンクをupsert_link opsとして同期する。本文送信はcontentFetchEnabled=trueのときだけ行う。</t>
+          <t>プロフィール、共有タグクラウド、通常設定画面にChatGPT連携欄と公開ページも同期欄を出さない。エクスポート画面のChatGPT/Codex/Claude向け説明は維持する。将来用の内部基盤は通常UIへ露出しない。</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Android: SharedTagAuthViewModelTest/build source inspection. iOS: source inspection/generic build. Supabase: RPC/migration source inspection; local DB live validation pending.</t>
+          <t>source inspection、Android physical UI XML/PNG、mobile UI contract、assembleDebug。iOS source inspection。</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>本番Supabase RPC set_personal_link_chatgpt_sync/apply_personal_link_opsが適用済みで、ユーザー権限と本文送信設定が一致すること。</t>
+          <t>正準アプリIDの通常UIで未運用設定欄へ到達できないこと。</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LINKED_RPC_PASS_WITH_CHATGPT_CONSUMPTION_GAP</t>
+          <t>HIDDEN_BY_CANONICAL_SPEC</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PASS: Android/iOS build系成功。Source inspectionでAndroid/iOSのUI toggle、AuthRequired、ops生成、content_fetch_allowed確認。</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>ChatGPT側実消費と物理端末toggle操作は未検証。linked DB上のpersonal link table/RPC存在は確認済み。</t>
+          <t>supabase_auth;public_web</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>修正なし: ローカルビルド/ソース上の明確なエラー未検出。</t>
+          <t>過去には個人リンク同期基盤と設定状態が存在したが、第1〜16回の正準仕様では通常UIに出さない方針。</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>PASS linked DB: personal_link_sync_settings/personal_saved_links と set_personal_link_chatgpt_sync/apply_personal_link_ops RPC存在確認。Remaining: ChatGPT側実消費、サインイン済みユーザーによるtoggle実行。</t>
+          <t>仕様衝突: 旧台帳ではChatGPT連携toggleの実機検証を残ゲートにしていたが、現行仕様ではChatGPT連携欄とパブリックページ同期欄を通常UIに出さない。</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>未実機操作: ChatGPT連携toggle未検証。</t>
+          <t>FIXED_TRACKING: 実装は通常UIにtoggleを出していないため、台帳を非表示仕様へ一本化。</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: ChatGPT連携toggle未検証。</t>
+          <t>PASS: rgで通常UI表示はエクスポート説明のみ。python3 scripts/verify_mobile_ui_contract.py 成功。./gradlew assembleDebug 成功。</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>本文送信のprivacy影響あり。store/privacy文言と継続照合が必要。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): プロフィール/サインイン画面を確認し、ChatGPT連携欄と公開ページも同期欄が表示されないことを確認。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-us036-profile-signin-no-chatgpt.png/xml。</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-06-29 07:25:00 +0900</t>
+          <t>PASS(source/current spec): iOS通常UIもChatGPT連携/公開ページ同期の設定欄を通常表示していない。Appium実機追加証跡はusbmuxd/Appium復旧待ち。</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>AI向け導線はエクスポート画面の説明に限定。将来、個人リンク同期を正式機能にする場合は別ストーリーとして再採用判断する。</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:52:00 +0900</t>
         </is>
       </c>
     </row>
@@ -4912,40 +5615,42 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>supabase_auth;resend_live</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>PASS: ContactSupportClientTest成功。PASS: deno check contact-support と contact-support-resend-webhook 成功。Web admin buildも成功。</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Resend delivered/bounced/complained等の実webhookイベント反映は未確認。問い合わせ送信、Resend accepted相当のemail.sent、DB監査row、message id保存は確認済み。</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>FIXED_LIVE: contact-support-resend-webhookを本番deploy。contact-support Functionをpublic.contact_support_requests契約へ修正し、問い合わせ本文/メール/名前の原文を監査DBへ保存しない形へ変更。Resend message idを保存し、webhookが後続更新できる状態にした。</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>PASS live send: contact-support POST returned 202 accepted requestId=56d99d04-bbea-4b48-be13-eef62cb1f8d4。PASS DB: delivery_status=sent, delivery_provider=resend, has_message_id=true, delivery_event_type=email.sent。PASS webhook smoke: unsigned webhook returns 401 Invalid webhook secret。15秒後の確認ではdelivered webhook未反映。</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
         <is>
           <t>Resend配送完了truthはResend側webhook実イベントまたはResend API照会が必要。</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>2026-06-29 07:25:00 +0900</t>
         </is>
@@ -5009,40 +5714,42 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>store_console;public_web</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>PARTIAL: 2026-06-29 live curlで privacy/account-deletion はHTTP 200、assetlinks.json/AASA はJSON parse成功。assetlinksは jp.miyamibu.urlalbum、AASAは 8R3B5675ZJ.com.mibu.codebridge.ios を含む。</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Play App Signing final SHA-256はNEEDS_USER_ACTION。公開privacy staleは2026-06-29本番deploy後に解消済み。</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>FIXED_PUBLIC_DEPLOY: web/invite-link をVercel project invite-linkへproduction deployし、miyamibu.xyzへalias済み。未修正: final Play SHA-256差し替えはGoogle Play Consoleの外部操作が必要。</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>PASS: npx --yes vercel@latest --prod --yes 成功。deployment dpl_8WZa3BBdqQs4f8s8mKcvxzaspVdv / alias https://miyamibu.xyz。PASS: scripts/verify_public_web_release.sh は privacy/account-deletion HTTP 200、assetlinks/AASA ID、Standard / Pro、Google Play Billing、StoreKit、stale no-real-billing文言なしを全て確認。</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
         <is>
           <t>2026-06-29 live privacy staleはproduction deployで解消。残りはPlay Console final SHA-256など外部Console確認のみ。</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>2026-06-29 07:25:00 +0900</t>
         </is>
@@ -5081,17 +5788,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ユーザーとして、保存済みリンクをタイトル、URL、ホスト、コレクション、タグ名で検索し、目的のリンクだけを一覧に絞り込める。</t>
+          <t>ユーザーとして、保存済みリンクをタイトル、URL、本文、投稿内容、メモ、自作タグ名、共有タグ名、サービス名、投稿主名で検索し、目的のリンクだけを一覧に絞り込める。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。Android/iOSともタイトル/URL/ホスト/コレクション名/割当ローカルタグ名を検索対象にする。未割当タグ名ではヒットしない。</t>
+          <t>検索アイコンで検索欄を表示し、入力中はActive一覧が絞り込まれる。Android/iOSともタイトル/URL/ホスト/本文/投稿内容/説明/メモ/割当自作タグ名/割当共有タグ名/サービス名/投稿主名を検索対象にする。未割当タグ名ではヒットしない。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Android: MainListViewModelTest search tests. iOS: ServiceFilterTests search tests. Future UI test: search input, clear, no-result, guide-to-search transition.</t>
+          <t>Android: MainListViewModelTest search tests + physical UI search. iOS: ServiceFilterTests search tests + physical UI search. Future UI test: no-result, guide-to-search transition, iPhone real-data filtering.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5101,47 +5808,57 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で検索欄表示・入力・クリアPASS、実データ絞り込みは未検証</t>
+          <t>PARTIAL_PASS: Android実機で検索欄表示・実データ絞り込みPASS、両OS検索対象unit PASS、iPhone実データ絞り込みは未検証</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/ServiceFilterTests 成功、17 tests。</t>
+          <t>BLOCKED_EXTERNAL</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>物理Android/iPhoneでの検索欄表示、入力、クリア、戻る操作は未検証。iOSのコレクション名検索はRootView/AppChrome経由で接続済みだが実機UI操作は未検証。</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>FIXED_LOCAL: Androidのタグ名検索が任意タグ名一致で全件ヒットし得る誤爆を修正。Android/iOSとも割当ローカルタグ名だけを検索対象にし、iOSもコレクション名検索を追加。</t>
+          <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/ServiceFilterTests 成功、19 tests。</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>PASS local retest: Android MainListViewModelTest、iOS ServiceFilterTests 17件成功。UI実操作は未実施。</t>
+          <t>iPhone物理実機での実データ絞り込み、no-result、検索から詳細/戻るの連続操作は未検証。Appium/usbmuxd未復旧のため追加操作証跡なし。</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PASS(Android physical Pixel 9a 55211JEBF16639): 検索アイコンから検索欄表示、入力、クリアを確認。IME影響で入力値は「りんばｍてｓｔ」になったが、EditText入力状態とクリア後空欄復帰をXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/android-us037-search-open-retry.png/xml, android-us037-search-input-rinbamtest.png/xml, android-us037-search-cleared.png/xml。</t>
+          <t>FIXED_LOCAL: Android/iOSの検索対象を正準仕様へ拡張。AndroidはfetchedAuthorName/fetchedBody/bodySummary/description/memo/service labelを追加し、タグ割当参照をLOCAL_ONLY限定から可視タグ名照合用の全割当へ拡張。iOSは既存の本文/メモ/投稿主名検索にservice labelを追加。</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>PASS local: Android MainListViewModelTestで本文/投稿内容、メモ、投稿主名、サービス名、割当共有タグ名検索を追加確認。PASS local: iOS ServiceFilterTestsで本文/投稿内容、メモ、投稿主名、サービス名検索を追加確認。PASS Android physical: IANA実データ検索で1件絞り込み確認。</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 検索欄へ IANA を入力し、www.iana.org / IANA-managed Reserved Domains の1件だけが表示され、example.comカードが非表示になることを確認。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-us037-search-iana-focused-result.png/xml。検索クリア後の通常復帰も保存: android-us037-search-cleared.png。</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session cca5fad7-b2ae-491d-a4ac-95499e1ed33b): 検索ボタンからTextField表示、rinbamtest入力、クリアボタン表示、クリア後ホーム復帰を確認。証跡: artifacts/device-verification/2026-06-29/iphone-us037-search-open.png/source.xml, iphone-us037-search-input.png/source.xml, iphone-us037-search-cleared.png/source.xml。</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>物理Android/iPhoneで検索欄の表示・入力・クリアは確認済み。保存済み実データに対するタイトル/URL/ホスト/コレクション/タグ絞り込み結果は、テスト用データ作成許可後に確認が必要。</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>2026-06-29 12:12:03 +0900</t>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Androidでは既存IANAカードを使った実データ検索まで物理PASS。iPhone側の実データ絞り込みはAppium/usbmuxd未復旧のため未検証。共有タグ名検索の物理実データはSupabase/live共有タグ状態が必要。動画/メディア保存設定は今回後回し。</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2026-07-03 03:16:04 +0900</t>
         </is>
       </c>
     </row>
@@ -5198,47 +5915,57 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>PHYSICAL_PASS_WITH_ANDROID_SELECTION_BUTTON_UX_GAP</t>
+          <t>PASS: Android/iPhone実機で複数選択バー、一括アーカイブ/削除、Undo導線PASS</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MainListViewModelTest 成功。PASS: xcodebuild test -only-testing:URLSaveriOSTests/URLRepositoryTests 成功、10 tests。PHYSICAL PASS: 2026-06-29にAndroid/iPhone実機で複数選択、一括アーカイブUndo、一括削除Undoを確認。</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Android physical UX/logical gap: ヘッダーの「選択」を押しても selectedEntryIds が空のため MainEntryList の selectionMode が false のままで、カードタップが詳細遷移した。コード上 selectionMode = selectedEntryIds.isNotEmpty() が selectionModeActive を見ていない。長押し選択、2件選択、一括アーカイブUndo、一括削除Undoは両実機で確認済み。</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>未修正: Androidヘッダー選択ボタンの空選択モードをカード選択に反映する修正候補あり。US-038の一括削除Undo未証明は2026-06-29実機再検証で解消。</t>
-        </is>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>PASS physical retest: Android長押し選択 -&gt; 2件選択 -&gt; 2件一括アーカイブ -&gt; Undo復帰、2件一括削除 -&gt; Undo復帰を確認。iPhone選択ボタン -&gt; 2件選択 -&gt; 2件一括アーカイブ -&gt; Undo復帰、2件一括削除 -&gt; Undo復帰を確認。Androidヘッダー「選択」単体の空選択UXのみ未修正。</t>
+          <t>解消済み: 2026-06-29時点のAndroidヘッダー「選択」単体UXギャップは、2026-07-03現行実機で「選択」押下後にカード選択と選択バー表示へ進むことを確認。</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PASS_WITH_UX_GAP(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): 長押しで1件選択、2件選択、選択バー「すべて選択/アーカイブ/削除/キャンセル」、一括アーカイブ通知「2件をアーカイブしました」「元に戻す」、Undo後に保存 14:56/14:55 復帰、一括削除通知「2件を削除しました」「元に戻す」、Undo後に保存 14:56/14:55 復帰を確認。ヘッダー「選択」単体は空選択状態からカード選択に繋がらず詳細遷移。証跡: artifacts/device-verification/2026-06-29/us038/android-us038-longpress2.*, android-us038-two-selected.*, android-us038-after-batch-archive.*, android-us038-after-batch-archive-undo.*; artifacts/device-verification/2026-06-29/us038-delete-undo/android-two-selected-before-delete.*, android-after-batch-delete.*, android-after-batch-delete-undo.*</t>
+          <t>FIXED_LOCAL_AND_DEVICE_VERIFIED: Android/iPhoneとも選択バーの件数表示は「1件」形式、すべて選択は文字のみ、タグアイコン、アーカイブ、削除が表示される。</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PASS(iPhone physical 00008101-00066D96340A001E, Appium/WDA, com.mibu.codebridge.ios): ヘッダー「選択」で2件選択、選択バー「すべて選択/アーカイブ/削除/キャンセル」、一括アーカイブ通知「2件をアーカイブしました」「元に戻す」、Undo後に保存 15:03/保存 12:27/Rinbam iPhone Title 復帰、一括削除通知「2件を削除しました」「元に戻す」、Undo後に保存 15:03/保存 12:27/Rinbam iPhone Title 復帰を確認。証跡: artifacts/device-verification/2026-06-29/us038/iphone-us038-after-select-button.*, iphone-us038-after-batch-archive.*, iphone-us038-after-batch-archive-undo.*; artifacts/device-verification/2026-06-29/us038-delete-undo/iphone-two-selected-before-delete.*, iphone-after-batch-delete.*, iphone-after-batch-delete-undo.*</t>
+          <t>PASS physical retest: Androidはヘッダー「選択」押下 -&gt; 1件選択 -&gt; 「1件」「すべて選択」タグアイコン/アーカイブ/削除表示を確認。iPhoneもヘッダー「選択」押下 -&gt; 1件選択 -&gt; 同等選択バー表示を確認。既存の一括アーカイブUndo/一括削除Undo証跡も継続有効。</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>既存データ保護のため物理端末では一時/検証カードのみ対象。Androidのヘッダー選択不具合はコード上も再現理由を確認済み。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): ヘッダー「選択」から選択モードに入り、1件選択時に「1件」「すべて選択」、タグアイコン、アーカイブ、削除が表示されることを確認。「1件選択」表記ではない。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/android-batch-tag-sheet-after-fix.png/xml, android-batch-tag-sheet-two-selected.png/xml, android-batch-tag-after-apply.png/xml。2026-06-29の一括アーカイブ/削除Undo証跡も継続参照。</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-06-29 15:27:27 +0900</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA, bundle com.mibu.codebridge.ios): ヘッダー「選択」から選択モードに入り、1件選択時に「1件」「すべて選択」、タグ、アーカイブ、削除、キャンセルを確認。「1件選択」表記ではない。タグシートで複数自作タグを同時選択して追加できることも確認。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/iphone-batch-tag-sheet-after-fix.png/source, iphone-batch-tag-sheet-two-selected-2.png/source, iphone-batch-tag-after-apply.png/source。2026-06-29の一括アーカイブ/削除Undo証跡も継続参照。</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>既存データ保護のため物理端末では一時/検証カードのみ対象。動画/メディア保存とは別の非動画選択操作としてPASS。</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5295,47 +6022,57 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
+          <t>LOCAL_SOURCE_PASS_WITH_AUTH_MAIL_LIVE_GAP</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>supabase_auth;public_web</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests SharedTagAuthViewModelTest 成功。Source inspectionでAndroid/iOS resendEmailConfirmation/sendPasswordRecovery経路確認。 PASS(source): reset-password static pageのexchangeCodeForSession/updateUser/signOut経路を確認。</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Supabase本番メール送信/到達、redirect挙動、物理端末操作は未検証。 公開reset-passwordページのlive到達と実メールリンクからの更新は未検証。</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Supabase本番メール送信/到達、redirect挙動、物理端末操作は未検証。実メールリンクからのパスワード更新は未検証。</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>修正なし: US-020から独立した補助機能として台帳追加。</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>未実施: live auth mailが必要。</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>未実機操作: 確認メール再送/パスワード再設定は未検証。</t>
-        </is>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on physical iPhone: 確認メール再送/パスワード再設定は未検証。</t>
+          <t>PASS: Android SharedTagAuthViewModelTest継続。PASS Android physical UI: プロフィール/サインイン画面で確認メール再送とパスワード再設定ボタンを確認。live auth mailは外部メール環境待ち。 PASS public web: https://miyamibu.xyz/auth/reset-password はHTTP 200で到達し、パスワード入力/確認、8文字以上、確認一致、updateUser経路の本文を確認。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール/サインイン欄で「確認メール再送」「パスワード再設定」ボタン要素を確認。未入力状態では無効。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実メール送信は本番Supabase auth/SMTP live未検証。</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>US-020は基本サインイン系。メール補助は外部メール到達が別ゲート。 targeted unit pass 2026-06-29. reset-password public page source-confirmed 2026-06-29.</t>
+          <t>PASS/PARTIAL(Android physical Pixel 9a 55211JEBF16639, jp.miyamibu.urlalbum): プロフィール/サインイン画面でメールアドレス/パスワード、確認メール再送、パスワード再設定を確認。未入力のためボタンは無効。証跡: artifacts/device-verification/2026-07-03-nonvideo-after-video-defer/android-profile-scroll-auth-plan.png/xml。</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-06-29 00:52:34 +0900</t>
+          <t>PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール/サインイン欄で「確認メール再送」「パスワード再設定」ボタン要素を確認。未入力状態では無効。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実メール送信は本番Supabase auth/SMTP live未検証。</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>US-020は基本サインイン系。メール補助は外部メール到達が別ゲート。 targeted unit pass 2026-06-29. reset-password public page source-confirmed 2026-06-29. reset-password public live HTTP 200確認 2026-07-03。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:12:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5397,42 +6134,52 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>store_console;public_web</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS: ./gradlew assembleDebug 成功。PASS: xcodebuild -quiet -project ios/URLSaveriOS.xcodeproj -scheme URLSaveriOS -destination generic/platform=iOS Simulator CODE_SIGNING_ALLOWED=NO build 成功。Source inspectionでAndroid privacy_dialog strings/UrlSaverRoot AlertDialogとiOS RootView PrivacyInfoSheet/info.circle入口を確認。</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>物理端末でのAndroidプライバシーダイアログ/iOSデータ取り扱いシート表示とPlay Console/App Store最終申告一致は未検証。修正前のAndroidアプリ内privacy dialogは共有タグクラウド、問い合わせ、Standard/Pro購入を説明していなかった。修正前のiOSはPrivacyInfo.xcprivacyはあったが、アプリ内でユーザーが確認できる同等シートがなかった。live privacy pageの課金なし文言staleは2026-06-29本番deploy後に解消済み。</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>PARTIAL_FIXED_LOCAL_AND_PUBLIC: Androidアプリ内privacy dialogを、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ送信、Standard/Pro Google Play Billing、広告/分析/クラッシュ収集なしの文言へ更新。iOSはRootViewにinfo.circle入口とPrivacyInfoSheetを追加し、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ、Standard/Pro StoreKit、広告/分析なしを表示。web/invite-link production deployでpublic privacy staleを解消。未修正: store console最終申告一致、物理UI表示確認。</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>PASS local: ./gradlew assembleDebug 成功。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS local: iOS generic simulator build成功。PASS public: scripts/verify_public_web_release.sh 成功。NOTE: 最初の jp.mimac.urlsaver.AdsConfigTest 指定はテストフィルタ不一致で失敗し、正しい完全修飾名で再実行済み。</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>PASS local: ./gradlew assembleDebug 成功。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS local: iOS generic simulator build成功。PASS public: scripts/verify_public_web_release.sh 成功。NOTE: 最初の jp.mimac.urlsaver.AdsConfigTest 指定はテストフィルタ不一致で失敗し、正しい完全修飾名で再実行済み。 2026-07-03再確認: ./scripts/verify_public_web_release.sh PASS。</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
         <is>
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): プライバシー情報ボタンから「データの取り扱い」ダイアログを表示。端末内保存、メタデータ取得、共有タグクラウド、問い合わせ、Standard / Pro Google Play Billing、広告/分析/第三者クラッシュ収集なしの文言をXML/PNGで確認。証跡: artifacts/device-verification/2026-06-29/android-us040-home-before.png/xml, android-us040-privacy-dialog.png/xml。</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8eb5a3bf-b1a1-4d77-85ce-b691a9b44192): info.circle からデータ取り扱いシートを表示。「端末内に保存する情報」「メタデータ取得」「共有タグクラウド」と閉じるボタンをPNG/XMLで確認。証跡: artifacts/device-verification/2026-06-29/iphone-appium-privacy.png, iphone-appium-privacy-source.xml。</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Android/iPhoneアプリ内データ取り扱い表示は実機確認済み。Google Play/App Storeのデータセーフティ/広告申告画面は未操作。</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>2026-06-29 12:12:03 +0900</t>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Android/iPhoneアプリ内データ取り扱い表示は実機確認済み。Google Play/App Storeのデータセーフティ/広告申告画面は未操作。 2026-07-03時点でも公開privacy/account deletion/AASA/assetlinksはPASS。</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2026-07-03 03:36:00 +0900</t>
         </is>
       </c>
     </row>
@@ -5494,40 +6241,50 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>store_console;public_web;design_required</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests MigrationDedupTest.migration_8_9_preservesExistingData_andCreatesUserLabels 成功。DAO/Entity/Repository/APIはsource確認。追加監査でAndroid UI/testsにUserLabel操作参照なし、iOSに同等UserLabelモデル/APIなし、git履歴上もdata foundation由来で旧UI削除ではないことを確認。</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>機能基礎はあるが現行ユーザーUI未実装。iOS側にも同等UserLabelモデル/API/UIなし。旧UI復元対象ではなく、公開ユーザー機能にするなら新規仕様判断が必要。</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>未修正: DESIGN.mdでadvanced taggingは明示承認なしに広げない方針。既存のローカルタグ/コレクションと重複するため、現状は未公開基盤として維持。</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>PASS: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MigrationDedupTest.migration_8_9_preservesExistingData_andCreatesUserLabels 成功。PASS audit: Android/iOS UI入口なしをrgで再確認。UI実装は未実施。</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>該当UIなし。</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>該当UIなし。</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>ユーザー依頼の「基礎は作ったが実装していないもの」候補として追跡。2026-06-29追加監査で旧実装UIの削除ではなくfoundation-onlyと判断。</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>2026-06-29 01:49:20 +0900</t>
         </is>
@@ -5591,56 +6348,285 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>supabase_auth;resend_live</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
           <t>PASS: npm run typecheck &amp;&amp; npm run build 成功。Next build route一覧に /api/admin/promo-codes/[id]/delivery が含まれることを確認。Source inspectionでResend API照会経路確認。</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Resend live API照会、実message id、管理画面ボタン/表示の操作は未検証。</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>修正なし: AS-006 webhook追跡とは別の手動配送照会機能として台帳追加。</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>未実施: live Resend APIと管理者セッションが必要。</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
         <is>
           <t>AS-006はwebhook反映、AS-009はResend APIへの手動照会。</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>2026-06-29 00:53:06 +0900</t>
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>US-041</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>テキストカード</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>URLなしテキスト保存</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>UrlRules.kt; URLRules.swift; ShareReceiverActivity.kt; DefaultUrlRepository.kt; URLRepository.swift; UrlSaverRoot.kt; DetailView.swift; RootView.swift</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ユーザーとして、URLを含まないテキストも保存し、通常カードと同じ一覧・詳細・タグ・メモ・検索対象として扱える。</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>URLなし本文は本文完全一致を重複キーとするテキストカードとして保存される。カードにはテキスト種別と自動タイトルが表示され、詳細に開くボタン/メディア保存ボタンは出さず、コピーは本文全体、詳細情報は保存時刻のみ表示する。</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Android/iPhone実機: URLなしテキストを保存し、一覧/詳細/詳細情報/ボタン表示を確認。Android/iOS unit: URLRulesTests/UrlRulesTest and repository tests.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>正準Android package jp.miyamibu.urlalbum と正準iOS bundle com.mibu.codebridge.ios で実機保存・詳細確認すること。</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>PASS: Android/iPhone実機でURLなしテキストカード保存・一覧・詳細表示PASS</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>PASS local: Android assembleDebug/testDebugUnitTest/lintDebug、iOS generic build成功後に実機確認。</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>現時点でURLなしテキストカードの実機保存/表示/詳細ボタン条件に明確なエラーなし。外部共有元からのURLなし共有は代表確認外。</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>FIXED_LOCAL_AND_DEVICE_VERIFIED: 既存url_entriesとtext.rinbam.local系の内部表現で、ユーザー向けにはURLを出さないテキストカードとして表示できることを確認。</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>PASS physical retest: Android/iPhoneでURLなしテキストを保存し、一覧カード、詳細ボタン、タグ/共有タグ、詳細情報の保存時刻のみを確認。</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): URLなしテキスト「URLなしテキストカード実機確認 20260703 買い物メモ りんご 牛乳」を共有/保存。ホームに「テキスト」「投稿」「保存 23:41」「URLなしテキストカード実機確認」を確認。詳細で開く/メディア保存/メディアを開くなし、コピー/アーカイブ/削除/メモを編集/自作タグ/共有タグ/詳細情報あり。詳細情報展開後は保存時刻あり、正規化URL/text.rinbam.local非表示。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/android-text-home-after-close.png/xml, android-text-detail.png/xml, android-text-detail-info-open.png/xml。</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA, bundle com.mibu.codebridge.ios): URLなしテキスト「URLなしテキストカードiPhone実機確認 20260703 買い物メモ たまご 牛乳」を手動追加から保存。ホームに「テキスト」「投稿」「保存 23:46」とタイトル表示を確認。詳細で開く/メディア保存/メディアを開くなし、コピー/自作タグ/共有タグ/詳細情報あり。詳細情報展開後は保存時刻あり、正規化URL/text.rinbam.local非表示。証跡: artifacts/device-verification/2026-07-03-goal-nonvideo/iphone-text-after-save.png/source, iphone-text-detail.png/source, iphone-text-detail-info-open.png/source。</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>動画/メディア保存とは別の非動画ストーリーとして追加。本文完全一致重複の実機確認は未実施だが、保存・表示・詳細契約は実機PASS。</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:05:00 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>US-042</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Android/iOS/Render</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>メディア保存</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TikTok/Instagram/YouTube投稿メディア保存</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>scripts/media_resolver_backend.py; VideoRepository.kt; VideoResolveWorker.kt; DetailView.swift; DetailViewModel.kt; URLSaverAppModel.swift</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ユーザーとして、TikTok/Instagram/YouTubeの投稿URLを保存し、詳細からメディアを保存してアプリ内で開ける。</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>対象投稿だけにメディアを保存を表示し、保存成功後はメディアを開くへ切り替わる。動画、画像、複数画像、YouTube Shorts、通常YouTubeを区別して保存/表示できる。Xは対象外。</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Render /health と /resolve、Android/iPhone実機の保存・ボタン押下・ビューア確認。</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Render本番Secret FileにYouTube/Instagram cookieを設定し、指定リンクでassetが返ること。</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>BLOCKED_EXTERNAL: TikTokは本番resolverで成功。InstagramはAUTH_REQUIRED、YouTubeはRESOLVE_FAILED。Render Secret Fileのcookie内容がYouTube/Instagramドメインを含んでいない。</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>render_media</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>PARTIAL: /healthは本番commit f9aeaf0f を返すが、youtube/instagram cookie domainが未設定。TikTok /resolve はassetを返す。</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Instagram指定リンクはAUTH_REQUIRED。YouTube Shorts/通常動画はyt-dlp CLI returned no usable video formats。Xはメディア保存対象外。</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>未修正: Render Secret FileへNetscape cookieを安全に設定し、アプリ側の保存済み判定/ビューアを再検証する必要がある。</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>未実施: Secret File設定後に再実行する。</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on current physical Android for media save after latest backend state.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on current physical iPhone for media save after latest backend state.</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-07-05追加。Xは対象外としてmedia blockerから除外。写真アプリ保存はDeferred。</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00 +0900</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:U59"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5652,651 +6638,193 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLOCKED_DEVICE_UI_DISABLED: コレクション保存先UIがAndroid/iOS現行ビルドで無効化されており、作成/移動/削除/並び替えを実機操作できない。</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>BLOCKED_EXTERNAL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LINKED_RPC_PASS_WITH_CHATGPT_CONSUMPTION_GAP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>LOCAL_ONLY</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOCAL_PASS: Web build/typecheck成功。本番DB/API実動作は未検証</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_DEVICE_GAP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_EXTERNAL_STORE_GAP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_IPHONE_DEVICE_GAP: Android/iOS compile系成功、iPhone UI操作未検証</t>
+          <t>remaining_gate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>story_ids</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_RESEND_LIVE_GAP</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>physical_android</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP: Android/iPhone実機データ取り扱い表示PASS、コード/公開WebローカルPASS、ストア申告未検証</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>physical_iphone</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_SUPABASE_MAIL_GAP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>render_media</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US-042</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でmetadata失敗状態表示PASS、成功取得は未検証</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>supabase_auth</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-011,US-013,US-015,US-016,US-017,US-018,US-019,US-020,US-022,US-023,US-024,US-025,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-032,US-033,AS-007,US-036,AS-008,US-037,US-039,AS-009</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でエクスポート設定画面PASS、共有シート/ファイル保存実行は未検証</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>store_console</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US-002,US-006,US-014,US-015,US-016,US-017,US-021,US-023,US-029,US-032,US-033,AS-007,ES-006,US-040,TS-001</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でタイトル編集保存PASS、Undo実行は未検証</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>resend_live</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AS-003,AS-006,AS-008,AS-009</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でプロフィール編集画面表示PASS、編集保存は未検証</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>public_web</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US-017,US-028,US-035,US-036,ES-006,US-039,US-040,TS-001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で問い合わせ/アカウント導線表示PASS、送信/削除は未検証</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で手動貼り付け保存PASS、重複時挙動は未検証</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で検索欄表示・入力・クリアPASS、実データ絞り込みは未検証</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で表示モード切替PASS、再起動後保持は未検証</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で詳細からアーカイブ/復元PASS、スワイプ操作とUndo実行は未検証</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で詳細遷移と外部で開く導線表示PASS、外部ブラウザ起動は未実行</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android/iPhone実機で認証関連画面表示PASS、OAuth/サインアウト実行は未検証</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS: Android実機PASS、iPhoneホーム/フィルター表示PASS、保存URL絞り込み操作未実施</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS_WITH_INTERNAL_CONTRACT_GAP: 両実機で失敗metadataの再取得UI導線と押下を確認。再enqueue/updatedAt不変は未検証。</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS_WITH_IPHONE_INPUT_GAP: Android実機の複数URL共有保存はPASS。iPhone実機は複数URL共有入力を生成できず、実保存未検証。</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS_WITH_IPHONE_SHARE_EXTENSION_ERROR: Android実機の単一URL共有保存はPASS。iPhone実機は共有シートにりんばむ表示まで確認したが、選択後の保存引き継ぎが失敗。</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS_WITH_NORMALIZATION_AND_IPHONE_UX_GAP: 両実機で同一URL重複は確認済み。表記違い正規化とiPhone通知導線は未完了。</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PARTIAL_PASS_WITH_TAG_DELETE_AND_DUPLICATE_GAP: 両実機でローカルタグ作成とURLへの割当は確認。削除時関連付け解除、重複処理、タグ別件数は未確認。</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PASS: Android/iPhone実機でホーム下部5アクションと使い方画面非表示を確認</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PASS: Android/iPhone実機でメモ編集保存PASS</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PASS: Android/iPhone実機で使い方リストと戻る復帰を確認</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PASS: Android/iPhone実機で非破壊の起動・画面証跡を取得</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>PASS: Web管理画面 typecheck/build 成功</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PASS: 正準スプレッドシート/CSV更新済み</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PASS_LINKED_DB_WITH_ADVISORY_WARNINGS</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PASS_LINKED_DB_WITH_STORE_WEBHOOK_GAP</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PASS_PUBLIC_WEB_WITH_FINAL_SHA_GAP</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PASS_RESEND_SENT_WITH_DELIVERY_EVENT_GAP</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PASS_WITH_PHYSICAL_OPERATION_GAP</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PASS_WITH_STORE_GAP: Android/iPhone実機の正準IDとiPhone表示名PASS、ストア表示未検証</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PHYSICAL_PARTIAL_PASS_WITH_INVITE_UX_GAPS: 両実機で urlsaver://invite と https://miyamibu.xyz/invite が招待確認導線へ入ることを確認。Android HTTPSはローディング継続、iPhoneはraw error露出。実招待作成/参加は未検証。</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>PHYSICAL_PASS_WITH_ANDROID_LOCAL_TAG_COPY_UX_GAP: 両実機でタグ選択/タグ詳細から対象URLだけの一覧と詳細遷移を確認。Androidローカルタグ詳細の共有タグ文言はUX不整合。</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PHYSICAL_PASS_WITH_ANDROID_SELECTION_BUTTON_UX_GAP</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>PHYSICAL_PASS_WITH_TEMP_DATA: 両実機で一時URLを使い、削除確認、5秒Undo通知、Undo後の一覧復帰を確認。</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>remaining_gate</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>story_ids</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>physical_Android</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>US-016,US-018,US-019,US-023,US-024,US-028,US-031,US-032,US-033,US-034,US-035,US-036,US-039</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>physical_iPhone</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>US-003,US-016,US-018,US-019,US-023,US-024,US-028,ES-003,US-031,US-032,US-033,US-034,US-035,US-036,US-039</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>supabase_or_auth_live</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>US-016,US-017,US-018,US-019,US-020,US-023,US-024,US-031,US-032,US-039</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>store_or_public_console</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>US-029,US-033,AS-007,ES-006,US-039,US-040,TS-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>resend_live</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AS-008,AS-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>connected_android_instrumentation</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
+          <t>design_required</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US-035,TS-001</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -7,12 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="canonical_story_status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stories" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'canonical_story_status'!$A$1:$U$59</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -418,29 +416,6 @@
   </sheetPr>
   <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6549,7 +6524,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL: TikTokは本番resolverで成功。InstagramはAUTH_REQUIRED、YouTubeはRESOLVE_FAILED。Render Secret Fileのcookie内容がYouTube/Instagramドメインを含んでいない。</t>
+          <t>PARTIAL: TikTok/InstagramはRender本番resolverでasset取得確認済み。YouTube Shorts/通常動画はRender本番では取得不可のためRailway専用resolverへ移管中。Xは対象外。</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6559,52 +6534,51 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>render_media</t>
+          <t>render_media;physical_android;physical_iphone</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PARTIAL: /healthは本番commit f9aeaf0f を返すが、youtube/instagram cookie domainが未設定。TikTok /resolve はassetを返す。</t>
+          <t>PARTIAL: Render /health は本番commit d43253a49d1ae6f4cd083ca2884371fb03885157、YouTube cookie fileReadable=true、Instagram cookie contentConfigured=true。Instagram Reel/写真/複数投稿はasset取得確認済み。</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Instagram指定リンクはAUTH_REQUIRED。YouTube Shorts/通常動画はyt-dlp CLI returned no usable video formats。Xはメディア保存対象外。</t>
+          <t>YouTube Shorts/通常動画は同じcookieでローカルyt-dlp取得成功だが、Render本番では formats=4 with_url=0 となり、fallbackは240秒超でtimeout。Render egress/IP/HTTP fingerprint制限の可能性が高い。</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>未修正: Render Secret FileへNetscape cookieを安全に設定し、アプリ側の保存済み判定/ビューアを再検証する必要がある。</t>
+          <t>IN_PROGRESS: MEDIA_RESOLVER_YOUTUBE_DELEGATE_URLによるYouTube委譲実装を追加し、Railway新規resolverへ移管する。Renderはアプリ向け入口として維持する。</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>未実施: Secret File設定後に再実行する。</t>
+          <t>PENDING: Railway /health、Railway /resolve、Render委譲後の /resolve、両実機のメディア保存/メディアを開く操作を再検証する。</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on current physical Android for media save after latest backend state.</t>
+          <t>NOT VERIFIED on current physical Android for media save after latest backend state. adb devices に端末が出た後、jp.miyamibu.urlalbum をデータ保持上書きで検証する。</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on current physical iPhone for media save after latest backend state.</t>
+          <t>NOT VERIFIED on current physical iPhone for media save after latest backend state. Appium serverは起動確認済みだがRemoteXPC 127.0.0.1:42314 の待受確認後にWDA操作証跡を取る。</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-07-05追加。Xは対象外としてmedia blockerから除外。写真アプリ保存はDeferred。</t>
+          <t>2026-07-05更新。Xは対象外としてmedia blockerから除外。写真アプリ直接保存はDeferred。YouTubeはRailway専用resolver、Render入口委譲方式で本番化する。</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-07-05 00:00:00 +0900</t>
+          <t>2026-07-05 21:45:26 +0900</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6617,11 +6591,6 @@
   </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6641,8 +6610,10 @@
           <t>BLOCKED_EXTERNAL</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>29</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -6651,8 +6622,10 @@
           <t>DEFERRED</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -6661,8 +6634,10 @@
           <t>LOCAL_ONLY</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -6671,8 +6646,10 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -6681,8 +6658,10 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>23</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -6691,8 +6670,10 @@
           <t>REMOVED</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -6718,10 +6699,16 @@
           <t>physical_android</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US-042</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6729,10 +6716,16 @@
           <t>physical_iphone</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US-042</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6740,8 +6733,10 @@
           <t>render_media</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6755,8 +6750,10 @@
           <t>supabase_auth</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>35</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6770,8 +6767,10 @@
           <t>store_console</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>15</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6785,8 +6784,10 @@
           <t>resend_live</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>4</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6800,8 +6801,10 @@
           <t>public_web</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>8</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6815,8 +6818,10 @@
           <t>design_required</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>2</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -1,421 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="stories" sheetId="1" r:id="rId1"/>
+    <sheet name="summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3805,7 +3399,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3816,8 +3414,16 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>秘密値は扱わない</t>
@@ -3900,7 +3506,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3911,9 +3521,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -3991,7 +3613,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4002,8 +3628,16 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>実送信は承認なしにしない</t>
@@ -4086,7 +3720,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4097,9 +3735,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4177,7 +3827,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4188,9 +3842,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4268,7 +3934,11 @@
           <t>BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。 / PASS: web/admin npm run typecheck と npm run build 成功。</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4279,9 +3949,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4486,7 +4168,11 @@
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>connectedDebugAndroidTestは通常端末では承認なし実行しない。テスト専用AVDでは2026-06-29に実行済み。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。 2026-06-29 connectedDebugAndroidTestをテスト専用AVDで実行し成功。</t>
@@ -4584,7 +4270,11 @@
           <t>PASS local retest: MetadataStatusTextTests成功、duplicate display_nameログなし、container_create_or_lookupログなし。 2026-07-03追加: xcodebuild selected local/simulator tests PASS 26 tests。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
@@ -4672,7 +4362,11 @@
           <t>PASS: 2026-06-29 web/admin npm run typecheck と npm run build 成功。Next.js buildで管理API route生成まで確認。</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>修正なし: typecheck/buildエラー未検出。</t>
@@ -4683,9 +4377,21 @@
           <t>PASS local retest。本番env/API実動作は未検証。</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2026-06-29 00:39:51 +0900</t>
@@ -4778,8 +4484,16 @@
           <t>PASS linked DB: db query --linkedで主要table/RPC存在確認成功。PASS functions: contact-support/contact-support-resend-webhook/verify-store-purchase deploy成功。PASS advisors improvement: anon executable SECURITY DEFINERはpreview系3件のみ。Remaining advisors WARN: function search_path、signed-in SECURITY DEFINER、RLS initplan、multiple policies、leaked password protection。 2026-07-03追加: deno check supabase/functions/verify-store-purchase/index.ts、contact-support/index.ts、contact-support-resend-webhook/index.ts は全てPASS。</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T42" t="inlineStr">
         <is>
           <t>linked project xocumgxbylmpoobfqows。db pushはremote migration history driftにより不可だったため、必要migrationをdb query --linkedで個別適用。 2026-07-03確認: Supabase vanity domain linbam.supabase.co は未解決で、vanity-subdomains APIはPro/Team/Enterprise plan requiredを返す。現行project ref xocumgxbylmpoobfqowsは到達するが匿名healthは401。</t>
@@ -5198,8 +4912,16 @@
           <t>PASS linked DB: store_purchase_verifications columns/RLS policy確認。PASS Function: verify-store-purchase no-session request is rejected with 401. Remaining: Google Play/App Store sandbox実取引と通知イベント。</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>実装コミット 7a2aba31。AS系に課金監査ストーリーを追加。</t>
@@ -5618,8 +5340,16 @@
           <t>PASS live send: contact-support POST returned 202 accepted requestId=56d99d04-bbea-4b48-be13-eef62cb1f8d4。PASS DB: delivery_status=sent, delivery_provider=resend, has_message_id=true, delivery_event_type=email.sent。PASS webhook smoke: unsigned webhook returns 401 Invalid webhook secret。15秒後の確認ではdelivered webhook未反映。</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T50" t="inlineStr">
         <is>
           <t>Resend配送完了truthはResend側webhook実イベントまたはResend API照会が必要。</t>
@@ -5717,8 +5447,16 @@
           <t>PASS: npx --yes vercel@latest --prod --yes 成功。deployment dpl_8WZa3BBdqQs4f8s8mKcvxzaspVdv / alias https://miyamibu.xyz。PASS: scripts/verify_public_web_release.sh は privacy/account-deletion HTTP 200、assetlinks/AASA ID、Standard / Pro、Google Play Billing、StoreKit、stale no-real-billing文言なしを全て確認。</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T51" t="inlineStr">
         <is>
           <t>2026-06-29 live privacy staleはproduction deployで解消。残りはPlay Console final SHA-256など外部Console確認のみ。</t>
@@ -6351,8 +6089,16 @@
           <t>未実施: live Resend APIと管理者セッションが必要。</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>AS-006はwebhook反映、AS-009はResend APIへの手動照会。</t>
@@ -6524,73 +6270,66 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>PARTIAL: TikTok/InstagramはRender本番resolverでasset取得確認済み。YouTube Shorts/通常動画はRender本番では取得不可のためRailway専用resolverへ移管中。Xは対象外。</t>
+          <t>PARTIAL: Render入口からYouTube Shorts/通常動画のRailway委譲asset取得PASS。Instagram Reel/写真/複数投稿もRender本番resolverでasset取得確認済み。iPhone実機でYouTube Shortsの保存、メディアを保存、メディアを開くPASS。Android実機とiPhone全リンク全形式の網羅は未完了。Xは対象外。</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>render_media;physical_android;physical_iphone</t>
+          <t>physical_android;physical_iphone</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PARTIAL: Render /health は本番commit d43253a49d1ae6f4cd083ca2884371fb03885157、YouTube cookie fileReadable=true、Instagram cookie contentConfigured=true。Instagram Reel/写真/複数投稿はasset取得確認済み。</t>
+          <t>PASS: Render /health は本番commit cdfbb72418dad30b55bcf4b1dade063b189394c7、youtube.delegateConfigured=true、delegateHost=rinbam-youtube-resolver-production.up.railway.app。Railway /health はYouTube cookie contentConfigured=true。</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>YouTube Shorts/通常動画は同じcookieでローカルyt-dlp取得成功だが、Render本番では formats=4 with_url=0 となり、fallbackは240秒超でtimeout。Render egress/IP/HTTP fingerprint制限の可能性が高い。</t>
+          <t>解消済み: Render単体YouTube取得失敗はRailway専用resolverへの委譲で回避。未完了: Androidはadb devices 0件のため最新backend状態の実機メディア保存未確認。iPhoneはYouTube Shortsのみ実機PASSで、Instagram/YouTube通常/複数画像など全リンク網羅は未完了。</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>IN_PROGRESS: MEDIA_RESOLVER_YOUTUBE_DELEGATE_URLによるYouTube委譲実装を追加し、Railway新規resolverへ移管する。Renderはアプリ向け入口として維持する。</t>
+          <t>FIXED_BACKEND_PARTIAL_DEVICE: scripts/media_resolver_backend.py に MEDIA_RESOLVER_YOUTUBE_DELEGATE_URL 委譲とループ防止を追加。Railway resolverを新規作成し、Render DashboardでMEDIA_RESOLVER_YOUTUBE_DELEGATE_URLを設定。Xはメディア保存対象外として除外。</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PENDING: Railway /health、Railway /resolve、Render委譲後の /resolve、両実機のメディア保存/メディアを開く操作を再検証する。</t>
+          <t>PASS backend: Railway /resolve は YouTube Shorts/通常動画で VIDEO asset + downloadUrl を返す。PASS Render入口: https://rinbam-media-resolver.onrender.com/resolve でも同2件が HTTP 200 ok=true provider=youtube assets=1。PASS iPhone partial: YouTube Shortsを手動追加保存し、詳細でメディアを保存、保存後メディアを開く表示、ビューア表示まで確認。</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on current physical Android for media save after latest backend state. adb devices に端末が出た後、jp.miyamibu.urlalbum をデータ保持上書きで検証する。</t>
+          <t>NOT VERIFIED on current physical Android after Render YouTube delegate: adb devices が空のため、jp.miyamibu.urlalbum でYouTube/Instagramメディア保存とメディアを開く操作は未完了。</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on current physical iPhone for media save after latest backend state. Appium serverは起動確認済みだがRemoteXPC 127.0.0.1:42314 の待受確認後にWDA操作証跡を取る。</t>
+          <t>PARTIAL PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 3d33f82b-f41e-416f-89d3-cbe1f16d93af, bundle com.mibu.codebridge.ios): YouTube Shorts https://youtube.com/shorts/ct-lmvk6mO0 を手動追加で保存し、ホームカード表示、詳細のメディアを保存表示、押下後メディアを開くへの切替、メディアビューア表示を確認。証跡: artifacts/device-verification/2026-07-05-final-gates/iphone-after-youtube-save-3.png/xml, iphone-youtube-detail.png/xml, iphone-after-media-save.png/xml, iphone-media-viewer.png/xml。未完了: iPhoneのInstagram Reel/写真/複数投稿、YouTube通常動画、TikTokの全リンク網羅。</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-07-05更新。Xは対象外としてmedia blockerから除外。写真アプリ直接保存はDeferred。YouTubeはRailway専用resolver、Render入口委譲方式で本番化する。</t>
+          <t>2026-07-05 23:59更新。Railway project rinbam-youtube-resolver / domain https://rinbam-youtube-resolver-production.up.railway.app をYouTube専用delegateとして作成。Render入口は維持。Render/Railway検証JSONは artifacts/render-verification/2026-07-05-final-gates/ に保存。Android未接続とiPhone全リンク未網羅は完了扱いにしない。</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-07-05 21:45:26 +0900</t>
+          <t>2026-07-05 23:59:00 +0900</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6612,7 +6351,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6387,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6474,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US-042</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6830,6 +6569,5 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -1,15 +1,446 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="stories" sheetId="1" r:id="rId1"/>
-    <sheet name="summary" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'stories'!$A$1:$U$59</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3399,11 +3830,7 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3414,16 +3841,8 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>秘密値は扱わない</t>
@@ -3506,11 +3925,7 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3521,21 +3936,9 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -3613,11 +4016,7 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3628,16 +4027,8 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
           <t>実送信は承認なしにしない</t>
@@ -3720,11 +4111,7 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3735,21 +4122,9 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -3827,11 +4202,7 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3842,21 +4213,9 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -3934,11 +4293,7 @@
           <t>BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。 / PASS: web/admin npm run typecheck と npm run build 成功。</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3949,21 +4304,9 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4168,11 +4511,7 @@
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
           <t>connectedDebugAndroidTestは通常端末では承認なし実行しない。テスト専用AVDでは2026-06-29に実行済み。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。 2026-06-29 connectedDebugAndroidTestをテスト専用AVDで実行し成功。</t>
@@ -4270,11 +4609,7 @@
           <t>PASS local retest: MetadataStatusTextTests成功、duplicate display_nameログなし、container_create_or_lookupログなし。 2026-07-03追加: xcodebuild selected local/simulator tests PASS 26 tests。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
@@ -4362,11 +4697,7 @@
           <t>PASS: 2026-06-29 web/admin npm run typecheck と npm run build 成功。Next.js buildで管理API route生成まで確認。</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>修正なし: typecheck/buildエラー未検出。</t>
@@ -4377,21 +4708,9 @@
           <t>PASS local retest。本番env/API実動作は未検証。</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2026-06-29 00:39:51 +0900</t>
@@ -4484,16 +4803,8 @@
           <t>PASS linked DB: db query --linkedで主要table/RPC存在確認成功。PASS functions: contact-support/contact-support-resend-webhook/verify-store-purchase deploy成功。PASS advisors improvement: anon executable SECURITY DEFINERはpreview系3件のみ。Remaining advisors WARN: function search_path、signed-in SECURITY DEFINER、RLS initplan、multiple policies、leaked password protection。 2026-07-03追加: deno check supabase/functions/verify-store-purchase/index.ts、contact-support/index.ts、contact-support-resend-webhook/index.ts は全てPASS。</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
           <t>linked project xocumgxbylmpoobfqows。db pushはremote migration history driftにより不可だったため、必要migrationをdb query --linkedで個別適用。 2026-07-03確認: Supabase vanity domain linbam.supabase.co は未解決で、vanity-subdomains APIはPro/Team/Enterprise plan requiredを返す。現行project ref xocumgxbylmpoobfqowsは到達するが匿名healthは401。</t>
@@ -4912,16 +5223,8 @@
           <t>PASS linked DB: store_purchase_verifications columns/RLS policy確認。PASS Function: verify-store-purchase no-session request is rejected with 401. Remaining: Google Play/App Store sandbox実取引と通知イベント。</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
           <t>実装コミット 7a2aba31。AS系に課金監査ストーリーを追加。</t>
@@ -5340,16 +5643,8 @@
           <t>PASS live send: contact-support POST returned 202 accepted requestId=56d99d04-bbea-4b48-be13-eef62cb1f8d4。PASS DB: delivery_status=sent, delivery_provider=resend, has_message_id=true, delivery_event_type=email.sent。PASS webhook smoke: unsigned webhook returns 401 Invalid webhook secret。15秒後の確認ではdelivered webhook未反映。</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
           <t>Resend配送完了truthはResend側webhook実イベントまたはResend API照会が必要。</t>
@@ -5447,16 +5742,8 @@
           <t>PASS: npx --yes vercel@latest --prod --yes 成功。deployment dpl_8WZa3BBdqQs4f8s8mKcvxzaspVdv / alias https://miyamibu.xyz。PASS: scripts/verify_public_web_release.sh は privacy/account-deletion HTTP 200、assetlinks/AASA ID、Standard / Pro、Google Play Billing、StoreKit、stale no-real-billing文言なしを全て確認。</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
           <t>2026-06-29 live privacy staleはproduction deployで解消。残りはPlay Console final SHA-256など外部Console確認のみ。</t>
@@ -6089,16 +6376,8 @@
           <t>未実施: live Resend APIと管理者セッションが必要。</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
           <t>AS-006はwebhook反映、AS-009はResend APIへの手動照会。</t>
@@ -6270,66 +6549,79 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>PARTIAL: Render入口からYouTube Shorts/通常動画のRailway委譲asset取得PASS。Instagram Reel/写真/複数投稿もRender本番resolverでasset取得確認済み。iPhone実機でYouTube Shortsの保存、メディアを保存、メディアを開くPASS。Android実機とiPhone全リンク全形式の網羅は未完了。Xは対象外。</t>
+          <t>PASS: Render/Railway本番resolverとAndroid/iPhone実機で、指定TikTok/Instagram/YouTubeリンクの保存、メディア保存、メディアを開く、ビューア表示を確認。Xはユーザー指定どおりメディア保存対象外。</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>physical_android;physical_iphone</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PASS: Render /health は本番commit cdfbb72418dad30b55bcf4b1dade063b189394c7、youtube.delegateConfigured=true、delegateHost=rinbam-youtube-resolver-production.up.railway.app。Railway /health はYouTube cookie contentConfigured=true。</t>
+          <t>PASS: Render /health は本番commit e083730771fbf268816da78018cb7e52f5018680でYouTube delegate設定済み。Railway /health はYouTube cookie contentConfigured=true。2026-07-07追加: Railwayに a9ce0238 をdeployし、YouTube通常動画は server-download fallback で /files mp4 を返すことを確認。</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>解消済み: Render単体YouTube取得失敗はRailway専用resolverへの委譲で回避。未完了: Androidはadb devices 0件のため最新backend状態の実機メディア保存未確認。iPhoneはYouTube Shortsのみ実機PASSで、Instagram/YouTube通常/複数画像など全リンク網羅は未完了。</t>
+          <t>解消済み: Android実機未接続はPixel 9a 55211JEBF16639接続で解消。iPhone全リンク未網羅はAppium/WDAで再検証し解消。YouTube通常動画のRailway direct proxy 502は、server-download有効時にcached /filesを返す修正で解消。</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>FIXED_BACKEND_PARTIAL_DEVICE: scripts/media_resolver_backend.py に MEDIA_RESOLVER_YOUTUBE_DELEGATE_URL 委譲とループ防止を追加。Railway resolverを新規作成し、Render DashboardでMEDIA_RESOLVER_YOUTUBE_DELEGATE_URLを設定。Xはメディア保存対象外として除外。</t>
+          <t>FIXED_BACKEND_AND_DEVICE: AndroidはDetailViewModelでメディア保存押下時に常に再resolveし、VideoResolverでURL中の\%を正規化。BackendはYouTube direct proxyで安全なyt-dlp headersを保持し、server-download有効時はproxyではなくcached /filesを返す。Xは対象外維持。</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PASS backend: Railway /resolve は YouTube Shorts/通常動画で VIDEO asset + downloadUrl を返す。PASS Render入口: https://rinbam-media-resolver.onrender.com/resolve でも同2件が HTTP 200 ok=true provider=youtube assets=1。PASS iPhone partial: YouTube Shortsを手動追加保存し、詳細でメディアを保存、保存後メディアを開く表示、ビューア表示まで確認。</t>
+          <t>PASS backend: Railway /resolve とRender入口 /resolve でYouTube通常動画が /files/df856baf91a5288eded2bdf5.mp4 を返し、GETで video/mp4 139792928 bytes を取得可能。PASS backend: TikTok、Instagram Reel、Instagram写真、Instagram複数/混在、YouTube Shorts、YouTube通常動画のasset取得確認。PASS local: python3 -m unittest tests/test_media_resolver_backend.py、./gradlew assembleDebug、./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.MediaResolveErrorReasonTest、verify_mobile_ui_contract、verify_canonical_story_tracker、git diff --check。</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>NOT VERIFIED on current physical Android after Render YouTube delegate: adb devices が空のため、jp.miyamibu.urlalbum でYouTube/Instagramメディア保存とメディアを開く操作は未完了。</t>
+          <t>PASS(Android physical Pixel 9a 55211JEBF16639, package jp.miyamibu.urlalbum): 指定6リンクを実機で保存/詳細/メディア保存/メディアを開く/ビューア表示まで確認。TikTok video、Instagram Reel video、Instagram写真複数画像、Instagram混在/動画、YouTube Shorts video、YouTube通常動画 video を確認。Android写真リンクは stale/null asset により一度失敗し、再resolve + URL正規化修正後にPASS。証跡: artifacts/device-verification/2026-07-07-media-e2e/android-*。</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>PARTIAL PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 3d33f82b-f41e-416f-89d3-cbe1f16d93af, bundle com.mibu.codebridge.ios): YouTube Shorts https://youtube.com/shorts/ct-lmvk6mO0 を手動追加で保存し、ホームカード表示、詳細のメディアを保存表示、押下後メディアを開くへの切替、メディアビューア表示を確認。証跡: artifacts/device-verification/2026-07-05-final-gates/iphone-after-youtube-save-3.png/xml, iphone-youtube-detail.png/xml, iphone-after-media-save.png/xml, iphone-media-viewer.png/xml。未完了: iPhoneのInstagram Reel/写真/複数投稿、YouTube通常動画、TikTokの全リンク網羅。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA sessions d291e3f9-0568-4081-828b-ef0bb130f8c3 and 893decce-78d6-4d47-9096-3b04d9875ac1, bundle com.mibu.codebridge.ios): 検証用共有元アプリから指定6リンクを共有し、各URLが共有シート/りんばむ共有拡張に出ていることと保存しましたを確認。TikTok、Instagram Reel、Instagram写真複数画像、Instagram混在、YouTube Shorts、YouTube通常動画を本体詳細でメディア保存し、保存後メディアを開くへ切替、ビューア表示まで確認。YouTube通常動画はRailway /files修正後に最終PASS。証跡: artifacts/device-verification/2026-07-07-media-e2e/iphone-*retry3*, iphone-*retry4*, iphone-youtube-normal-*railway-files*。</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-07-05 23:59更新。Railway project rinbam-youtube-resolver / domain https://rinbam-youtube-resolver-production.up.railway.app をYouTube専用delegateとして作成。Render入口は維持。Render/Railway検証JSONは artifacts/render-verification/2026-07-05-final-gates/ に保存。Android未接続とiPhone全リンク未網羅は完了扱いにしない。</t>
+          <t>2026-07-07更新: Railway project rinbam-youtube-resolver へ a9ce0238 をdeploy。Render入口は維持。検証JSON: artifacts/render-verification/2026-07-07-media-e2e/。実機証跡: artifacts/device-verification/2026-07-07-media-e2e/。未追跡artifactは証跡としてローカル保持し、ソースコミットには含めない。</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-07-05 23:59:00 +0900</t>
+          <t>2026-07-08 00:25:00 +0900</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U59"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6387,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6691,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -6440,14 +6732,10 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US-042</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6457,14 +6745,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>US-042</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6477,11 +6761,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6569,5 +6849,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3830,7 +3830,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3841,8 +3845,16 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>秘密値は扱わない</t>
@@ -3925,7 +3937,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -3936,9 +3952,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4016,7 +4044,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4027,8 +4059,16 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>実送信は承認なしにしない</t>
@@ -4111,7 +4151,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4122,9 +4166,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4202,7 +4258,11 @@
           <t>PASS: web/admin npm run typecheck と npm run build 成功。 / BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4213,9 +4273,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4293,7 +4365,11 @@
           <t>BLOCKED_LOCAL: supabase db lint --local は 127.0.0.1:55422 接続拒否。ローカルDB未起動。本番/linked DBは秘密値なしで未接続。 / PASS: web/admin npm run typecheck と npm run build 成功。</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>修正なし: エラー未検出。</t>
@@ -4304,9 +4380,21 @@
           <t>再テスト不要: 変更なし。</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2026-06-27 15:51:33 +0900</t>
@@ -4511,7 +4599,11 @@
           <t>PASS(Android physical Pixel 9a 55211JEBF16639): jp.miyamibu.urlalbum 起動、ホーム、下部5アクション、使い方リスト、戻る復帰をXML/PNGで確認。</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>connectedDebugAndroidTestは通常端末では承認なし実行しない。テスト専用AVDでは2026-06-29に実行済み。2026-06-29にステータスをPASSからLOCAL_PASS_WITH_CONNECTED_TEST_GAPへ修正し、未検証ゲートを分離。 2026-06-29 connectedDebugAndroidTestをテスト専用AVDで実行し成功。</t>
@@ -4609,7 +4701,11 @@
           <t>PASS local retest: MetadataStatusTextTests成功、duplicate display_nameログなし、container_create_or_lookupログなし。 2026-07-03追加: xcodebuild selected local/simulator tests PASS 26 tests。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA + devicectl): com.mibu.codebridge.ios 1.0.11(11) を実機に上書きインストール済み。Appium/WDAでホーム、共有タグサインイン案内、プロフィール/プラン画面のUIツリーとスクリーンショット取得に成功。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us023-us024-us033-profile-scrolled.png/xml。SimulatorのCoreSimulator warningとは別に物理iPhone UI取得は復旧済み。</t>
@@ -4697,7 +4793,11 @@
           <t>PASS: 2026-06-29 web/admin npm run typecheck と npm run build 成功。Next.js buildで管理API route生成まで確認。</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>修正なし: typecheck/buildエラー未検出。</t>
@@ -4708,9 +4808,21 @@
           <t>PASS local retest。本番env/API実動作は未検証。</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2026-06-29 00:39:51 +0900</t>
@@ -4803,8 +4915,16 @@
           <t>PASS linked DB: db query --linkedで主要table/RPC存在確認成功。PASS functions: contact-support/contact-support-resend-webhook/verify-store-purchase deploy成功。PASS advisors improvement: anon executable SECURITY DEFINERはpreview系3件のみ。Remaining advisors WARN: function search_path、signed-in SECURITY DEFINER、RLS initplan、multiple policies、leaked password protection。 2026-07-03追加: deno check supabase/functions/verify-store-purchase/index.ts、contact-support/index.ts、contact-support-resend-webhook/index.ts は全てPASS。</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T42" t="inlineStr">
         <is>
           <t>linked project xocumgxbylmpoobfqows。db pushはremote migration history driftにより不可だったため、必要migrationをdb query --linkedで個別適用。 2026-07-03確認: Supabase vanity domain linbam.supabase.co は未解決で、vanity-subdomains APIはPro/Team/Enterprise plan requiredを返す。現行project ref xocumgxbylmpoobfqowsは到達するが匿名healthは401。</t>
@@ -5223,8 +5343,16 @@
           <t>PASS linked DB: store_purchase_verifications columns/RLS policy確認。PASS Function: verify-store-purchase no-session request is rejected with 401. Remaining: Google Play/App Store sandbox実取引と通知イベント。</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>実装コミット 7a2aba31。AS系に課金監査ストーリーを追加。</t>
@@ -5643,8 +5771,16 @@
           <t>PASS live send: contact-support POST returned 202 accepted requestId=56d99d04-bbea-4b48-be13-eef62cb1f8d4。PASS DB: delivery_status=sent, delivery_provider=resend, has_message_id=true, delivery_event_type=email.sent。PASS webhook smoke: unsigned webhook returns 401 Invalid webhook secret。15秒後の確認ではdelivered webhook未反映。</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T50" t="inlineStr">
         <is>
           <t>Resend配送完了truthはResend側webhook実イベントまたはResend API照会が必要。</t>
@@ -5742,8 +5878,16 @@
           <t>PASS: npx --yes vercel@latest --prod --yes 成功。deployment dpl_8WZa3BBdqQs4f8s8mKcvxzaspVdv / alias https://miyamibu.xyz。PASS: scripts/verify_public_web_release.sh は privacy/account-deletion HTTP 200、assetlinks/AASA ID、Standard / Pro、Google Play Billing、StoreKit、stale no-real-billing文言なしを全て確認。</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T51" t="inlineStr">
         <is>
           <t>2026-06-29 live privacy staleはproduction deployで解消。残りはPlay Console final SHA-256など外部Console確認のみ。</t>
@@ -6376,8 +6520,16 @@
           <t>未実施: live Resend APIと管理者セッションが必要。</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>AS-006はwebhook反映、AS-009はResend APIへの手動照会。</t>
@@ -6600,6 +6752,113 @@
       <c r="U59" t="inlineStr">
         <is>
           <t>2026-07-08 00:25:00 +0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CH-013</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ユーザー</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Android/iOS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AI引き渡し</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>第13章 ChatGPT活用例の受け側契約</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ExportRepository.kt; ExportArchiveBuilder.swift; ExportScreen.kt; ExportSheet.swift; docs/ai/chapter13-chatgpt-use-cases.md</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Google Doc第13章の34項目を添付後のChatGPTで依頼できる例として確認し、りんばむ側は自作タグ選択・対象/出力内容確認・ZIP作成・OS共有までに限定する。</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>README_FOR_AI.mdに34項目を1から34まで含める。質問入力・自動入力・自動送信・OpenAI API/OAuth/MCPは含めない。共有前に未知の秘密が残る可能性を警告し明示確認を要求する.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Android/iOS単体テスト; README 34項目照合; iPhone Appium/WDA composer添付確認; Androidは実機/AVD接続後に同一手順を再実行。</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>提出binaryのAndroid/iOS両方で同じ34項目と責務境界が表示されること。</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED_LOCAL_WITH_DEVICE_GATES</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>android_device;distribution_signing;public_privacy;store_console</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Android/iOS source and unit tests pass. iPhone physical reaches normal ChatGPT composer with ZIP attached and question field empty; Android physical unavailable.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>未署名AAB・Android物理E2E・iOS Distribution/TestFlight・公開Privacy反映・Store申告は外部ゲート。</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>FAIL_CLOSED_AND_BOUNDARY_HARDENED</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>iOS saved-session plus unavailable config now fails closed. Android Release Ads references removed and ChatGPT share intent/cache/25MiB/10000-entry guards added. Redaction now occurs before excerpt clipping with boundary regression tests。未実施: Android物理端末/AVDで直接共有とchooser fallback、Release cold start。iOS最終送信は仕様上実施しない。</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED on Android physical: device/AVD unavailable.</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>PASS iPhone physical via Appium/WDA: ZIP attachment in normal ChatGPT composer and empty question field; send intentionally not tapped.</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Chapter 13 is a receiving-side use-case list・not 34 in-app AI features. Canonical fixture: docs/ai/chapter13-chatgpt-use-cases.md.</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2026-07-18 00:00:00 +0900</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6938,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6994,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6748,7 +7011,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6761,7 +7028,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6788,12 +7059,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US-002,US-006,US-014,US-015,US-016,US-017,US-021,US-023,US-029,US-032,US-033,AS-007,ES-006,US-040,TS-001</t>
+          <t>US-002,US-006,US-014,US-015,US-016,US-017,US-021,US-023,US-029,US-032,US-033,AS-007,ES-006,US-040,TS-001,CH-013</t>
         </is>
       </c>
     </row>

--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="stories" sheetId="1" state="visible" ns1:id="rId1"/>
+    <sheet name="summary" sheetId="2" state="visible" ns1:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'stories'!$A$1:$U$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'stories'!$A$1:$U$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -612,7 +612,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>解消済み: Android/iPhone物理実機で手動保存、正規化重複通知、既存詳細への復帰を確認。Supabaseはこの端末内保存ストーリーの完了条件ではない。</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-07-03 06:11:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>解消済み: 2026-06-29時点のiPhone共有拡張保存引き継ぎ失敗は、2026-07-02/03の物理iPhone Safari共有再検証で再現せず、保存完了まで確認。CoreSimulator/XCTest不整合は別ゲートとして継続。</t>
+          <t>解消済み: Android ACTION_SENDとiPhone Safari共有拡張で、保存先タグ選択から保存完了・共有元復帰まで物理実機確認済み。Supabase/Store consoleはこの共有受信ストーリーの完了条件ではない。</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-07-03 04:45:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>iPhone physical US-003 input source gap: Safari通常共有は単一URLのみ。Web Share API一時ページでは共有シート生成不可。Notesに2件URL本文を作り、その他アプリ一覧にりんばむは表示されたが、Notes側が共同作業リンク作成フローへ遷移し、Share Extension保存画面まで到達しなかった。 2026-07-03 07:05追加: iPhone実機で追加確認。Notes共有は共有先一覧にりんばむが表示されても、選択後にNotesの「リンクを作成」共同作業UIへ遷移しShare Extensionに渡らない。Safari Web Share検証はCloudflare Quick Tunnelが404、localhost.runがTLS不可。LAN HTTPページは表示できたがSafariで navigator.share is not a function となり、HTTPS入力元なしでは共有シート生成不可。 2026-07-03 07:18追加: HTTPS example.com 上でSafariアドレスバーから javascript:navigator.share(...) を実行する方式も試したが、iPhone Safariが「スクリプトを実行できません。JavaScriptは、この方法で使用することが許されていません。」を表示し共有シートは出なかった。</t>
+          <t>解消済み: 署名済み一時共有元アプリからURLオブジェクト2件をiPhone Share Extensionへ渡し、2件保存完了を物理実機で確認。Android ACTION_SEND_MULTIPLEも物理実機確認済み。</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-07-03 22:48:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PARTIAL_DEVICE_GAP: Android/iPhone実機で同一URL重複判定は確認。表記違いURLの正規化重複は未検証。iPhone手動追加の重複保存後、コード上は「このURLはすでに保存済みです」+「見る」通知を5秒表示する設計だが、Appium証跡では保存後ホームに戻り通知が見えなかった。</t>
+          <t>解消済み: Android/iPhone物理実機で大文字HTTPS、既定port、fragment差を含む表記違いURLが同一normalizedUrlとして重複扱いになり、重複通知と「見る」導線を確認。</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-07-03 06:16:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>iPhone保存済みURLを用いた絞り込み操作は未検証。Androidでは2026-07-03に自作タグクリックが即解除される不具合を修正済み。</t>
+          <t>解消済み: Android/iPhone物理実機で保存済みデータを用いた自作タグ絞り込みを確認。Supabaseはローカル一覧フィルターの完了条件ではない。</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-07-03 06:16:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>iPhone物理端末での再起動後保持は未検証。AndroidはDataStore保持を実機で確認済み。</t>
+          <t>解消済み: Android/iPhone物理実機で表示モード切替とアプリ再起動後の保持を確認。Supabase/Store consoleはこの端末内設定の完了条件ではない。</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-07-03 06:17:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>iPhoneの横スワイプアーカイブ/Undo実行は未検証。Androidは2026-07-03に右スワイプ、Snackbar「元に戻す」、DBのACTIVE復帰まで確認済み。</t>
+          <t>解消済み: Android/iPhone物理実機でActiveカード右スワイプ、アーカイブ通知、Undo、対象のActive復帰を確認。</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-07-03 06:19:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>PHYSICAL_PASS_WITH_TEMP_DATA: 両実機で一時URLを使い、削除確認、5秒Undo通知、Undo後の一覧復帰を確認。</t>
+          <t>PASS: Android/iPhone物理実機で削除猶予、Undo通知、対象カード復帰PASS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>過去試行ではAndroidの座標タップが5秒Undoに間に合わず復元未証明だったが、今回bounds由来のUndo中心タップで復元を確認。iPhoneもAppium/WDA連続操作で復元確認。製品ロジック上の不具合は今回未検出。</t>
+          <t>解消済み: Android Pixel 9aとiPhone 12で削除確認、削除後通知「削除しました」「元に戻す」、Undo後のカード復帰を確認。Supabaseはこの端末内状態遷移の完了条件ではない。</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-07-03 04:45:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>現時点でメモ編集の実機確認上の未解決エラーなし。CoreSimulator/XCTest不整合はこの行の完了判定には使わず、物理実機証跡を正とする。</t>
+          <t>解消済み: Android/iPhone物理実機でメモ編集・保存・詳細反映を確認。Supabaseは端末内メモ編集の完了条件ではない。</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-07-03 04:45:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_DEVICE_GAP: 両実機で失敗metadataの再取得UI導線と押下を確認。Android/iOSとも再取得・updatedAt不変のRepository契約テストPASS。</t>
+          <t>PARTIAL: local retry contractと両実機の再取得操作は確認、成功metadata更新E2Eは未確認</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>android_device;iphone_device</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-07-03 04:45:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>store_console</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>未完了範囲: iPhone側のタグ管理削除実行、iPhone側の重複タグ名/既割当時文言、iPhone側のタグ別URL件数の物理UI確認。Androidはタグ管理のゴミ箱アイコンのみ表示、一時タグ削除、件数表示、重複/既割当契約を2026-07-03に確認済み。</t>
+          <t>解消済み: Android/iPhone物理実機でタグ作成、同名重複防止、件数表示、ゴミ箱のみの削除UI、削除後の消失を確認。Store consoleはローカルタグ管理の完了条件ではない。</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-07-03 06:50:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>現行コード確認では、ローカル自作タグ詳細は isLocalTag 分岐により「自作タグ」文言、共有タグ専用のクラウドサインイン/共有/参加者表示はSYNCED時だけ表示。過去台帳に残っていたAndroid共有タグ文言混入は現行コードでは再現対象なし。</t>
+          <t>解消済み: 両実機でタグ絞り込み/詳細導線を確認し、現行コードでもLOCAL_ONLY/SYNCED分岐によりローカルタグへ共有タグ専用文言・クラウド操作が混入しない。</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-07-03 04:45:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-07-03 07:00:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console;public_web</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>実招待作成/acceptはSupabase liveユーザー状態が必要なため未検証。iPhone実機のinvalid raw error修正後再確認はAppium/usbmuxd復旧待ち。</t>
+          <t>実招待作成/acceptはSupabase liveユーザー状態が必要なため未検証。iPhone実機のinvalid raw error修正後再確認はAppium/usbmuxd復旧待ち。公開invite/reset/privacy/App Links契約は2026-08-13のproduction verifierでPASS。</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FIXED_LOCAL: Android招待プレビューに12秒タイムアウトを追加し、HTTPS inviteでローディング継続しないようにした。iOSは invalid_or_expired_invite など既知raw errorを日本語文言へ正規化。</t>
+          <t>FIXED_LOCAL_AND_PUBLIC_WEB_VERIFIED: Android招待プレビューに12秒タイムアウトを追加し、iOS既知raw errorを日本語文言へ正規化。Vercel production deployment dpl_52Tc5XaiiLeV9F1EkxTLPXssqRmq の公開invite復帰導線を検証済み。</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PASS: ./gradlew assembleDebug testDebugUnitTest --tests SharedTagAuthViewModelTest --tests ShareReceiverActivityEntrypointTest 成功。PASS: xcodebuild generic iOS Simulator build 成功。PASS Android physical: HTTPS無効招待が「招待リンクが無効か期限切れです」表示へ遷移。iPhone物理再確認はAppium/usbmuxd未復旧のため未実施。</t>
+          <t>PASS local/mobile dated evidence。PASS public 2026-08-13: scripts/verify_public_web_release.shでinvite HTTP 200、コピー/公式Store fallback、reset/privacy/App Links/Universal Links契約を確認。実招待作成・accept・権限同期はSupabase live未検証。</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Deep Link受信/画面遷移は既存の両実機証跡で確認済み。無効リンクUXはAndroid物理PASS、iOSはsource/build修正済み。実際の有効招待作成・参加・権限同期はSupabase liveサインインが必要なためUS-018/US-032側で追跡。</t>
+          <t>公開Webゲートは2026-08-13に解消。実際の有効招待作成・参加・権限同期はSupabase liveサインインが必要なためUS-018/US-032側と合わせて継続追跡。</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-07-03 02:59:28 +0900</t>
+          <t>2026-08-13 15:57:37 +0900</t>
         </is>
       </c>
     </row>
@@ -2742,17 +2742,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でプロフィール編集画面表示PASS、編集保存は未検証</t>
+          <t>PARTIAL: Android/iPhone実機で編集UI表示PASS、プロフィール編集保存は未検証</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>store_console</t>
+          <t>android_device;iphone_device</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>Android/iPhone物理実機でプロフィール名・写真・テーマの編集UIは確認したが、既存ユーザーデータを変更しないため編集保存は未実施。Store consoleはこの未確認操作と無関係。</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-06-29 12:03:48 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-07-03 07:12:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -3170,17 +3170,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android/iPhone実機でエクスポート設定画面PASS、共有シート/ファイル保存実行は未検証</t>
+          <t>PARTIAL: local export testsと両実機の設定画面PASS、物理共有/ファイル保存E2Eは未検証</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>android_device;iphone_device</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-06-29 12:03:48 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>public_web</t>
+          <t>distribution_signing</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Release compile上の失敗なし。署名付き配布や外部console設定はこのストーリーの対象外。</t>
+          <t>Release compileは両OSでPASS。署名付き配布binaryはこのlocal-only検証では作成・実行しておらず、配布署名は別の外部ゲート。</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-07-03 02:54:50 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>PASS_WITH_STORE_GAP: Android/iPhone実機の正準IDとiPhone表示名PASS、ストア表示未検証</t>
+          <t>PASS_WITH_CONFIRMED_APP_STORE_LOCALIZATION_PACKAGING_GAP: 正準ID/公開1.0.17/archive一致PASS、archiveは英語development region・日本語localizationなし</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>store_console</t>
+          <t>distribution_signing;store_console</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3618,17 +3618,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>iOS XCTest/UI操作: CoreSimulator不整合またはAppium RemoteXPC tunnel未起動により未完了。</t>
+          <t>2026-08-13公式App Storeは1.0.17・言語EN。署名済み配布archiveはversion 1.0.17/build 19/canonical bundleとTeam一致、CFBundleDevelopmentRegion=en、CFBundleLocalizationsなし、.lprojなし。current sourceの日本語宣言がarchiveへ反映されていない。</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>修正対象なし: 環境/外部接続ブロックまたは未検証。コードのロジスティカル/UXエラーは今回の検証では未検出。</t>
+          <t>SOURCE_DECLARATION_PRESENT / ARCHIVE_NOT_FIXED: current sourceは日本語を宣言するが、公開対応archiveは英語のみ。日本語が実際に含まれる新しい署名archiveを生成・検査してからStore表示を再確認する。</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>再テスト未実施: 修正なし。ブロック解除後に再実行。 PASS connected Android instrumentation: 2026-06-29 urlsaverParityApi35 AVDで URLSAVER_ALLOW_CONNECTED_ANDROID_TESTS=true URLSAVER_APPROVE_ANDROID_APP_DATA_RESET=true ./gradlew connectedDebugAndroidTest 成功。</t>
+          <t>PASS exact archive/public boundary 2026-08-13: 公開1.0.17とarchive 1.0.17 (19)/canonical bundle/Teamを照合。archiveはdevelopment region en・localizationなしで、公開EN表示と一致。NOT VERIFIED: corrected archive / App Store Connect post-change localization。</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>実機上の正準Android package/iOS bundle IDは確認済み。App Store/Google Play Console上の表示は未操作。</t>
+          <t>正準ID証拠は維持。App Store EN表示はconsole誤表示ではなく現archiveを正しく反映するため、localization packagingの確認済みMinorとしてdistribution_signing/store_consoleで追跡する。</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-06-29 11:48:00 +0900</t>
+          <t>2026-08-13 17:09:21 +0900</t>
         </is>
       </c>
     </row>
@@ -3832,29 +3832,29 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>本番管理者セッションとSupabase Auth/admin権限を使うログイン・非管理者拒否E2Eは未実施。秘密値は表示せず、local build/typecheckのみ確認。</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>修正なし: エラー未検出。</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>再テスト不要: 変更なし。</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>秘密値は扱わない</t>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -3939,37 +3939,37 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>本番Supabase管理者セッションでの最新100件一覧・status_label表示E2Eは未実施。local API/source/build検証のみ。</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>修正なし: エラー未検出。</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>再テスト不要: 変更なし。</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -4046,29 +4046,29 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>本番Supabase管理者セッションとResend live設定を使う優待コード実送信・一度だけの結果確認は未実施。実メール送信はphase 1対象外。</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>修正なし: エラー未検出。</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>再テスト不要: 変更なし。</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>実送信は承認なしにしない</t>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -4153,37 +4153,37 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>本番Supabase管理者セッションでの取消POST、revoked_reason永続化、一覧反映E2Eは未実施。</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>修正なし: エラー未検出。</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>再テスト不要: 変更なし。</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -4260,37 +4260,37 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>本番Supabase Auth管理API権限を使うメール断片検索・非管理者拒否E2Eは未実施。</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>修正なし: エラー未検出。</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>再テスト不要: 変更なし。</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -4367,37 +4367,37 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
+          <t>本番Resend webhook署名付きイベントとSupabase実DBを使うdelivered/bounced等の反映E2Eは未実施。</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>修正なし: エラー未検出。</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>再テスト不要: 変更なし。</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>修正なし: エラー未検出。</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>再テスト不要: 変更なし。</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-06-27 15:51:33 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS_WITH_CORE_SIMULATOR_WARNING</t>
+          <t>PASS_LOCAL_BUILD_TEST_WITH_NONBLOCKING_SIMULATOR_WARNING</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>iOS simulator testでCoreSimulator WebCore/WebKit重複クラス警告は残存。物理iPhone UI操作は未検証。</t>
+          <t>非ブロッキング警告: iOS SimulatorのCoreSimulator WebCore/WebKit重複クラス警告は残るが、選択test・署名なしRelease compile・物理iPhone Appium/WDA画面取得はPASS。</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-07-03 07:12:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>supabase_auth;store_console</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>OAuth実ブラウザ往復、Supabase live invite accept、物理iPhone Appium操作は未検証。</t>
+          <t>OAuth実ブラウザ往復、Supabase live invite accept、物理iPhone Appium操作は未検証。公開invite復帰導線は2026-08-13 production verifierでPASS。</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PASS local retest。live invite再開は外部Auth/Supabase環境待ち。 2026-07-03 Android physical: 共有タグ導線からサインイン案内表示PASS。実OAuth/招待リンク再開は未検証。 2026-07-03追加 local/simulator: xcodebuild test -only-testing SharedTagVisibilityTests, SharedTagSyncExecutorTests, URLRulesTests は26 tests PASS。 2026-07-03追加 local: ./gradlew testDebugUnitTest --tests EntitlementResolverTest --tests TagRepositoryTest --tests DetailTagUiStateTest はBUILD SUCCESSFUL。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): 未ログイン時の共有タグ参加/作成導線としてサインイン案内、メール/パスワード入力欄、サインインボタン要素を確認。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-remaining-app-current.png/xml, iphone-us018-us019-us032-shared-signin-destination.png/xml。実招待リンク保留とサインイン後再開はAuth/Supabase live未検証。</t>
+          <t>PASS local/device dated evidence。PASS public 2026-08-13: scripts/verify_public_web_release.shでinvite HTTP 200とコピー/公式Store fallbackを確認。live invite保留・Auth往復・参加再開は外部Auth/Supabase環境待ち。</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>実装コミット 7a2aba31。US-017の招待参加から保留再開を分離して追跡。 Android実機で「サインインしていなければ押した時にサインイン案内を出す」挙動は確認済み。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+          <t>公開Webゲートは2026-08-13に解消。Android/iOSのpending invite実装は既存証拠どおり。実OAuth/メールサインインとlive invite accept後の再開だけをsupabase_authゲートとして残す。</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-07-03 07:12:00 +0900</t>
+          <t>2026-08-13 15:57:37 +0900</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>FOUNDATION_ONLY_NOT_CANONICAL_UI</t>
+          <t>REMOVED_FROM_CANONICAL_USER_SURFACE_COMPATIBILITY_ONLY</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>public_web;design_required</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>現行正準仕様 docs/rinbam-canonical-spec.md は保存先タグ/自作タグ中心で、コレクション作成・移動UIを採用項目に含めていない。旧台帳ではユーザー機能として残していたため、実機未到達ゲートとして誤追跡していた。</t>
+          <t>解消済み: source-of-truthをdocs/rinbam-canonical-spec.mdへ一本化し、Collection DB/Repositoryは既存データ読込・移行の互換基盤のみ、現行ユーザー機能ではないと明記。再採用は別要件・設計・parity testが必要。</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-07-03 03:00:24 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>supabase_auth;public_web</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-07-03 02:52:00 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -5845,17 +5845,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>PASS_PUBLIC_WEB_WITH_FINAL_SHA_GAP</t>
+          <t>PUBLIC_WEB_VERIFIED_WITH_STORE_ACCURACY_GATES</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>BLOCKED_EXTERNAL</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>store_console;public_web</t>
+          <t>store_console</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5865,17 +5865,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Play App Signing final SHA-256はNEEDS_USER_ACTION。公開privacy staleは2026-06-29本番deploy後に解消済み。</t>
+          <t>2026-08-13 production verifierはprivacy/account-deletion/reset/invite/assetlinks/AASAを全件PASS。未解決は、cloud-enabled Android v21に対するGoogle Play Data safety不一致、local-only iOS archiveに対するApp Store cloud機能説明不一致、Play App Signing最終SHA-256。Apple privacy Majorはarchive証拠で反証済み。</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>FIXED_PUBLIC_DEPLOY: web/invite-link をVercel project invite-linkへproduction deployし、miyamibu.xyzへalias済み。未修正: final Play SHA-256差し替えはGoogle Play Consoleの外部操作が必要。</t>
+          <t>FIXED_AND_PUBLICLY_VERIFIED: reset/inviteと公開Webは修正・公開済み。Google Data safety MajorとApp Store listing Majorは外部未修正。Apple privacy Majorはmatching local-only archiveによりFALSE_POSITIVE。</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PASS: npx --yes vercel@latest --prod --yes 成功。deployment dpl_8WZa3BBdqQs4f8s8mKcvxzaspVdv / alias https://miyamibu.xyz。PASS: scripts/verify_public_web_release.sh は privacy/account-deletion HTTP 200、assetlinks/AASA ID、Standard / Pro、Google Play Billing、StoreKit、stale no-real-billing文言なしを全て確認。</t>
+          <t>PASS public 2026-08-13: scripts/verify_public_web_release.sh。BLOCKED_EXTERNAL: Google Data safety修正、App Store product copy/localization修正、Play signing fingerprint照合、post-change公開ページ再確認。</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2026-06-29 live privacy staleはproduction deployで解消。残りはPlay Console final SHA-256など外部Console確認のみ。</t>
+          <t>公開Web stale/deployゲートは解消。2026-08-13 C0 read-only Play ConsoleでStep 2 collect/share=yes、Step 5 no collection+shared Web browsing history、account creation does not allow、deletion unansweredを確認。変更/保存は未実施で、Web PASSをStore GOとして扱わない。</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-29 07:25:00 +0900</t>
+          <t>2026-08-13 17:09:21 +0900</t>
         </is>
       </c>
     </row>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>PARTIAL_PASS: Android実機で検索欄表示・実データ絞り込みPASS、両OS検索対象unit PASS、iPhone実データ絞り込みは未検証</t>
+          <t>PARTIAL: Android実データ検索と両OSunit/UI操作PASS、iPhone実データ絞り込みE2Eは未検証</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>iphone_device</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-07-03 03:16:04 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LOCAL_SOURCE_PASS_WITH_AUTH_MAIL_LIVE_GAP</t>
+          <t>PUBLIC_RESET_PASS_WITH_AUTH_MAIL_LIVE_GAP</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>supabase_auth;public_web</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6186,17 +6186,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Supabase本番メール送信/到達、redirect挙動、物理端末操作は未検証。実メールリンクからのパスワード更新は未検証。</t>
+          <t>Supabase本番メール送信/到達、redirect挙動、実メール recovery code交換とパスワード更新は未検証。公開reset routeのHTTP/CSP契約は2026-08-13 production verifierでPASS。</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>修正なし: US-020から独立した補助機能として台帳追加。</t>
+          <t>PUBLIC_WEB_VERIFIED / AUTH_LIVE_UNVERIFIED: reset routeは外部JS/CSS、厳格CSP、Referrer-Policyと回復契約を実装・公開済み。本番Supabase Auth/SMTPのメール到達は変更も実行もしていない。</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PASS: Android SharedTagAuthViewModelTest継続。PASS Android physical UI: プロフィール/サインイン画面で確認メール再送とパスワード再設定ボタンを確認。live auth mailは外部メール環境待ち。 PASS public web: https://miyamibu.xyz/auth/reset-password はHTTP 200で到達し、パスワード入力/確認、8文字以上、確認一致、updateUser経路の本文を確認。 2026-07-03 07:12追加 iPhone physical via Appium/WDA: PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA): プロフィール/サインイン欄で「確認メール再送」「パスワード再設定」ボタン要素を確認。未入力状態では無効。証跡: artifacts/device-verification/2026-07-03-iphone-us001-016-resumed/iphone-us023-us024-us033-profile-scrolled.png/xml。実メール送信は本番Supabase auth/SMTP live未検証。</t>
+          <t>PASS public 2026-08-13: scripts/verify_public_web_release.shで/auth/reset-password HTTP 200、外部JS/CSS、inline styleなし、CSP契約を確認。PASS既存unit/browser contract。NOT VERIFIED: 本番メール到達・実recovery交換・updateUser。</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>US-020は基本サインイン系。メール補助は外部メール到達が別ゲート。 targeted unit pass 2026-06-29. reset-password public page source-confirmed 2026-06-29. reset-password public live HTTP 200確認 2026-07-03。 2026-07-03 03:54再確認: CoreDevice/devicectlでは iPhone 12 UDID 00008101-00066D96340A001E が wired/paired/unlocked/tunnel connected。xctraceにもDevices欄で表示。ただし Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 は応答なし。root の tunnel-creation PID 71658 はCPU 100%で通常権限kill不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。2026-07-03 04:00再確認: xctraceでは iPhone 12 UDID 00008101-00066D96340A001E が Devices Offline、Appium list-real-devices.mjs は usbmuxd 0件、Appium server 127.0.0.1:4723 は未起動、RemoteXPC 42314 はtimeout。root の tunnel-creation PID 71658 はCPU 100%で通常権限から復旧不可。Appium/WDA操作証跡は継続して NOT VERIFIED on physical iPhone。</t>
+          <t>public_webゲートは解消。残るsupabase_authは実メール送信/到達、redirect、recovery session、更新完了のproduction E2E。秘密値や実アカウントは操作していない。</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-07-03 07:12:00 +0900</t>
+          <t>2026-08-13 15:57:37 +0900</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LOCAL_PASS_WITH_STORE_DECLARATION_GAP: Android/iPhone実機データ取り扱い表示PASS、コード/公開WebローカルPASS、ストア申告未検証</t>
+          <t>PUBLIC_POLICY_VERIFIED_WITH_GOOGLE_DATA_SAFETY_AND_IOS_LISTING_GATES</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>store_console;public_web</t>
+          <t>store_console</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>物理端末でのAndroidプライバシーダイアログ/iOSデータ取り扱いシート表示とPlay Console/App Store最終申告一致は未検証。修正前のAndroidアプリ内privacy dialogは共有タグクラウド、問い合わせ、Standard/Pro購入を説明していなかった。修正前のiOSはPrivacyInfo.xcprivacyはあったが、アプリ内でユーザーが確認できる同等シートがなかった。live privacy pageの課金なし文言staleは2026-06-29本番deploy後に解消済み。</t>
+          <t>既存実機表示と公開Privacy契約はPASS。署名済みAndroid v21はcloud-enabledなのでGoogle Playのno-data回答と矛盾する。署名済みiOS 1.0.17 (19)はlocal-onlyのためApp Privacy no-dataは矛盾せず、代わりに公開cloud機能説明がbinaryと矛盾する。Consoleは未変更。</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PARTIAL_FIXED_LOCAL_AND_PUBLIC: Androidアプリ内privacy dialogを、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ送信、Standard/Pro Google Play Billing、広告/分析/クラッシュ収集なしの文言へ更新。iOSはRootViewにinfo.circle入口とPrivacyInfoSheetを追加し、端末内保存、メタデータ取得、共有タグクラウド、問い合わせ、Standard/Pro StoreKit、広告/分析なしを表示。web/invite-link production deployでpublic privacy staleを解消。未修正: store console最終申告一致、物理UI表示確認。</t>
+          <t>PARTIAL_FIXED_LOCAL_AND_PUBLIC / STORE_CONSOLES_UNCHANGED: public Privacyは公開済み。Google Data safety MajorとApp Store listing Majorをdocs化。Play ConsoleはC0がread-only確認、App Store Connectは未操作。Apple privacy Majorは反証済み。</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PASS local: ./gradlew assembleDebug 成功。PASS local: ./gradlew testDebugUnitTest --tests jp.mimac.urlsaver.ads.AdsConfigTest 成功。PASS local: iOS generic simulator build成功。PASS public: scripts/verify_public_web_release.sh 成功。NOTE: 最初の jp.mimac.urlsaver.AdsConfigTest 指定はテストフィルタ不一致で失敗し、正しい完全修飾名で再実行済み。 2026-07-03再確認: ./scripts/verify_public_web_release.sh PASS。</t>
+          <t>PASS public 2026-08-13: Privacy HTTP 200と既存mobile証拠。BLOCKED_EXTERNAL: Google Data safety修正、App Store listing/localization修正、各post-change public recheck。</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Android/iPhoneアプリ内データ取り扱い表示は実機確認済み。Google Play/App Storeのデータセーフティ/広告申告画面は未操作。 2026-07-03時点でも公開privacy/account deletion/AASA/assetlinksはPASS。</t>
+          <t>公開WebはPASS。C0の認証済みPlay Console read-only観測でStep 2/Step 5・account creation・deletion回答の矛盾を確認し、変更/保存は未実施。App Store Connectも未操作。iOS archive反証後もGoogle Major・App Store listing Majorが残りGO不可。</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-07-03 03:36:00 +0900</t>
+          <t>2026-08-13 17:09:21 +0900</t>
         </is>
       </c>
     </row>
@@ -6380,17 +6380,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>FOUNDATION_ONLY_NOT_USER_FACING</t>
+          <t>REMOVED_FROM_CANONICAL_USER_SURFACE_COMPATIBILITY_ONLY</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>store_console;public_web;design_required</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>機能基礎はあるが現行ユーザーUI未実装。iOS側にも同等UserLabelモデル/API/UIなし。旧UI復元対象ではなく、公開ユーザー機能にするなら新規仕様判断が必要。</t>
+          <t>解消済み: UserLabel table/column/APIは既存データ・migration互換のため保持するが、現行ユーザー機能ではないと正準仕様へ明記。iOS parityやUIを欠陥として追跡せず、再採用時は別要件とする。</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-06-29 01:49:20 +0900</t>
+          <t>2026-08-11 11:02:17 +0900</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>android_device;distribution_signing;public_privacy;store_console</t>
+          <t>android_device;distribution_signing;store_console</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>未署名AAB・Android物理E2E・iOS Distribution/TestFlight・公開Privacy反映・Store申告は外部ゲート。</t>
+          <t>Android物理E2E・current sourceとのdistribution対応・Google Data safetyは未解決。署名済みAndroid v21 cloud-enabled証拠に対しGoogle no-data回答が矛盾。iOS App Privacy Majorはlocal-only archiveで反証済みだが、App Store cloud機能説明はbinaryと不一致。</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>iOS saved-session plus unavailable config now fails closed. Android Release Ads references removed and ChatGPT share intent/cache/25MiB/10000-entry guards added. Redaction now occurs before excerpt clipping with boundary regression tests。未実施: Android物理端末/AVDで直接共有とchooser fallback、Release cold start。iOS最終送信は仕様上実施しない。</t>
+          <t>iOS saved-session plus unavailable config now fails closed. Android Release Ads references removed and ChatGPT share intent/cache/25MiB/10000-entry guards added. Redaction now occurs before excerpt clipping with boundary regression tests。PASS public 2026-08-13: scripts/verify_public_web_release.sh。未実施: Android物理端末/AVDで直接共有とchooser fallback、Release cold start、Store console correction。iOS最終送信は仕様上実施しない。</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6853,17 +6853,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Chapter 13 is a receiving-side use-case list・not 34 in-app AI features. Canonical fixture: docs/ai/chapter13-chatgpt-use-cases.md.</t>
+          <t>Chapter 13 is a receiving-side use-case list・not 34 in-app AI features. Canonical fixture: docs/ai/chapter13-chatgpt-use-cases.md. public_privacyゲートは解消。Google Data safetyとApp Store listing整合をstore_consoleで継続し、Apple privacy Majorは閉鎖。</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-07-18 00:00:00 +0900</t>
+          <t>2026-08-13 17:09:21 +0900</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U59"/>
+  <autoFilter ref="A1:U60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6874,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6902,220 +6902,174 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>LOCAL_ONLY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOCAL_ONLY</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>remaining_gate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>story_ids</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>remaining_gate</t>
+          <t>android_device</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>story_ids</t>
+          <t>US-013,US-021,US-025,CH-013</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>physical_android</t>
+          <t>iphone_device</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>US-013,US-021,US-025,US-037</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>physical_iphone</t>
+          <t>distribution_signing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t/>
+          <t>US-028,US-029,CH-013</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>render_media</t>
+          <t>supabase_auth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>US-016,US-017,US-018,US-019,US-020,US-022,US-023,US-024,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-032,US-033,AS-007,AS-008,US-039,AS-009</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>supabase_auth</t>
+          <t>store_console</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US-001,US-002,US-003,US-004,US-005,US-006,US-007,US-008,US-011,US-013,US-015,US-016,US-017,US-018,US-019,US-020,US-022,US-023,US-024,US-025,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-032,US-033,AS-007,US-036,AS-008,US-037,US-039,AS-009</t>
+          <t>US-029,US-033,AS-007,ES-006,US-040,CH-013</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>store_console</t>
+          <t>resend_live</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US-002,US-006,US-014,US-015,US-016,US-017,US-021,US-023,US-029,US-032,US-033,AS-007,ES-006,US-040,TS-001,CH-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>resend_live</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>AS-003,AS-006,AS-008,AS-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>public_web</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>US-017,US-028,US-035,US-036,ES-006,US-039,US-040,TS-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>design_required</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>US-035,TS-001</t>
         </is>
       </c>
     </row>

--- a/docs/qa/rinbam_canonical_story_status.xlsx
+++ b/docs/qa/rinbam_canonical_story_status.xlsx
@@ -3170,7 +3170,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>PARTIAL: local export testsと両実機の設定画面PASS、物理共有/ファイル保存E2Eは未検証</t>
+          <t>PARTIAL: local export testsと両実機の設定画面PASS。iPhoneは実書き出しからiOS共有シート表示・未送信で閉じるまでPASS。Android出力実行E2Eは未検証。</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>android_device;iphone_device</t>
+          <t>android_device</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>物理Android/iPhoneでの共有シート、ファイル保存、ファイル受け渡し先アプリでの実確認は未検証。iOS simulator test中にApp Group entitlement警告と重複display_name migrationログあり、テスト失敗はなし。</t>
+          <t>物理Androidでの書き出し実行、共有シート、ファイル保存、受け渡し先アプリ確認は未検証。iPhoneはUIActivityViewController表示まで実行済み。</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>修正なし: ローカルテスト上のエラー未検出。台帳code_basisに共有シート/保存先実装を補強。</t>
+          <t>DEVICE_EVIDENCE_UPDATED: iPhone物理実機でZIP書き出しとUIActivityViewController表示を確認。外部送信は行わず閉じてホーム復帰。</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PASS local retest: Android export targeted tests、iOS export/filter targeted tests成功。物理共有先は未実施。</t>
+          <t>PASS local retest: Android export targeted tests、iOS export/filter targeted tests成功。物理共有先は未実施。 PASS iPhone physical 2026-08-23/24: ZIP・共有シートを選び「書き出す」を実行、iOS UIActivityViewControllerでAirDrop/コピーを確認し、送信せず閉じてホームへ復帰。</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>PASS/PARTIAL(iPhone physical 00008101-00066D96340A001E via Appium/WDA session 8c957f69-e6f0-412a-9d20-816728e11a1b): エクスポート画面で「ZIP」「JSON」「共有シート」「ファイルに保存」「書き出す」を確認。UIActivityViewController/fileExporter実行は未実施。証跡: iphone-ui-loop-export-open-final.png/xml。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E, bundle com.mibu.codebridge.ios 1.0.18(20), Appium/WDA session b7d4dca2-079d-4186-bd43-866f79ecec8f): エクスポート画面でZIP・共有シートを選び「書き出す」を実行。iOS共有シートにAirDrop/コピーが表示され、外部送信せず閉じ、エクスポート画面とホームへ正常復帰。証跡: artifacts/device-verification/2026-08-23-final/iphone-appium/11-export-sheet.png/xml相当、12-system-share-sheet.png/xml、13-home-final.png/xml。</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>実ファイル生成、共有先アプリ、ファイル保存先確認は次ループで実施。</t>
+          <t>iPhoneの実ファイル生成と共有シート起動は物理PASS。外部送信は仕様・データ保護のため実施せず。Android物理出力E2Eのみ継続。</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-08-11 11:02:17 +0900</t>
+          <t>2026-08-24 19:59:34 +0900</t>
         </is>
       </c>
     </row>
@@ -5738,17 +5738,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>PASS_RESEND_SENT_WITH_DELIVERY_EVENT_GAP</t>
+          <t>PASS_LIVE_RESEND_DELIVERED_AND_AUDITED: 本番contact-support canaryが202 accepted、同一idempotency key再送で同一requestId、Resend email.delivered、outbox sent、message id保存、payload scrub、監査更新まで確認。</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BLOCKED_EXTERNAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>supabase_auth;resend_live</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5758,17 +5758,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Resend delivered/bounced/complained等の実webhookイベント反映は未確認。問い合わせ送信、Resend accepted相当のemail.sent、DB監査row、message id保存は確認済み。</t>
+          <t>確認した範囲ではなし。Resend署名済みemail.deliveredイベントが本番DBへ反映され、provider配送完了と監査更新を確認。</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>FIXED_LIVE: contact-support-resend-webhookを本番deploy。contact-support Functionをpublic.contact_support_requests契約へ修正し、問い合わせ本文/メール/名前の原文を監査DBへ保存しない形へ変更。Resend message idを保存し、webhookが後続更新できる状態にした。</t>
+          <t>FIXED_LIVE_AND_DELIVERY_VERIFIED</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PASS live send: contact-support POST returned 202 accepted requestId=56d99d04-bbea-4b48-be13-eef62cb1f8d4。PASS DB: delivery_status=sent, delivery_provider=resend, has_message_id=true, delivery_event_type=email.sent。PASS webhook smoke: unsigned webhook returns 401 Invalid webhook secret。15秒後の確認ではdelivered webhook未反映。</t>
+          <t>PASS live 2026-08-23/24: contact-support POSTは202 accepted、requestId=d5c3903e-c565-4021-9e0c-425f0f776ccc。同一Idempotency-Key再送も同一requestIdで二重送信なし。PASS linked DB: delivery_status=delivered、delivery_event_type=email.delivered、delivery_message_idあり、outbox state=sent、attempts=1、payload={}、payload_scrubbed_atあり。</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Resend配送完了truthはResend側webhook実イベントまたはResend API照会が必要。</t>
+          <t>本番Resend delivery truthを署名済みemail.delivered webhookの実DB反映で確認。問い合わせ本文・氏名・メールは合成canaryのみを使用し、outbox送信後scrub済み。</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-29 07:25:00 +0900</t>
+          <t>2026-08-24 19:57:29 +0900</t>
         </is>
       </c>
     </row>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>PARTIAL: Android実データ検索と両OSunit/UI操作PASS、iPhone実データ絞り込みE2Eは未検証</t>
+          <t>PASS: Android/iPhone実データ検索、両OS unit、検索表示・入力・絞り込み・終了後ホーム復帰を確認。</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>iphone_device</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>iPhone物理実機での実データ絞り込み、no-result、検索から詳細/戻るの連続操作は未検証。Appium/usbmuxd未復旧のため追加操作証跡なし。</t>
+          <t>確認した範囲ではなし。no-resultと検索結果から詳細遷移の追加回帰は将来拡張であり、正準受入の実データ絞り込みは両物理端末で確認済み。</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>FIXED_LOCAL: Android/iOSの検索対象を正準仕様へ拡張。AndroidはfetchedAuthorName/fetchedBody/bodySummary/description/memo/service labelを追加し、タグ割当参照をLOCAL_ONLY限定から可視タグ名照合用の全割当へ拡張。iOSは既存の本文/メモ/投稿主名検索にservice labelを追加。</t>
+          <t>FIXED_LOCAL_AND_BOTH_PHYSICAL_DEVICES_VERIFIED</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PASS local: Android MainListViewModelTestで本文/投稿内容、メモ、投稿主名、サービス名、割当共有タグ名検索を追加確認。PASS local: iOS ServiceFilterTestsで本文/投稿内容、メモ、投稿主名、サービス名検索を追加確認。PASS Android physical: IANA実データ検索で1件絞り込み確認。</t>
+          <t>PASS local: Android MainListViewModelTestで本文/投稿内容、メモ、投稿主名、サービス名、割当共有タグ名検索を追加確認。PASS local: iOS ServiceFilterTestsで本文/投稿内容、メモ、投稿主名、サービス名検索を追加確認。PASS Android physical: IANA実データ検索で1件絞り込み確認。 PASS iPhone physical 2026-08-23/24: 検索欄へexampleを入力し、example.comの実データ1件へ絞り込み。検索終了後に通常ホームと5アクションへ復帰。</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5992,17 +5992,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>PASS(iPhone physical 00008101-00066D96340A001E via Appium/WDA session cca5fad7-b2ae-491d-a4ac-95499e1ed33b): 検索ボタンからTextField表示、rinbamtest入力、クリアボタン表示、クリア後ホーム復帰を確認。証跡: artifacts/device-verification/2026-06-29/iphone-us037-search-open.png/source.xml, iphone-us037-search-input.png/source.xml, iphone-us037-search-cleared.png/source.xml。</t>
+          <t>PASS(iPhone physical 00008101-00066D96340A001E, bundle com.mibu.codebridge.ios 1.0.18(20), Appium/WDA session b7d4dca2-079d-4186-bd43-866f79ecec8f): 検索欄へexampleを入力し、example.comカードだけが表示される実データ絞り込みを確認。検索終了後に通常ホームと5アクションへ復帰。証跡: artifacts/device-verification/2026-08-23-final/iphone-appium/10-search-example.png/xml、13-home-final.png/xml。</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Androidでは既存IANAカードを使った実データ検索まで物理PASS。iPhone側の実データ絞り込みはAppium/usbmuxd未復旧のため未検証。共有タグ名検索の物理実データはSupabase/live共有タグ状態が必要。動画/メディア保存設定は今回後回し。</t>
+          <t>AndroidのIANA検索とiPhoneのexample検索で、両物理端末の実データ絞り込みを確認済み。共有タグ名検索のlive状態は共有タグ個別ストーリーで追跡する。</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:02:17 +0900</t>
+          <t>2026-08-24 19:59:34 +0900</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US-013,US-021,US-025,US-037</t>
+          <t>US-013,US-021</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US-016,US-017,US-018,US-019,US-020,US-022,US-023,US-024,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-032,US-033,AS-007,AS-008,US-039,AS-009</t>
+          <t>US-016,US-017,US-018,US-019,US-020,US-022,US-023,US-024,AS-001,AS-002,AS-003,AS-004,AS-005,AS-006,ES-005,US-032,US-033,AS-007,US-039,AS-009</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AS-003,AS-006,AS-008,AS-009</t>
+          <t>AS-003,AS-006,AS-009</t>
         </is>
       </c>
     </row>
